--- a/22-23_KBL_stats.xlsx
+++ b/22-23_KBL_stats.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30013"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/22-23_KBL_stats.xlsx
+++ b/22-23_KBL_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Project\2026\KBL Stats Analyzer 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5493F5-4F50-4858-B51C-3E635C633030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC32B80-7048-4826-ACB3-65D36B901D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
+    <workbookView xWindow="-28920" yWindow="1785" windowWidth="29040" windowHeight="15720" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1009,7 +1009,7 @@
     <numFmt numFmtId="180" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
     <numFmt numFmtId="181" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1082,6 +1082,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -1250,7 +1256,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1413,13 +1419,19 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2283,38 +2295,38 @@
       <c r="BQ2" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR2" s="35">
-        <v>36.049999999999997</v>
-      </c>
-      <c r="BS2" s="35">
-        <v>58.65</v>
-      </c>
-      <c r="BT2" s="35">
-        <v>22.6</v>
+      <c r="BR2" s="58">
+        <v>137.43</v>
+      </c>
+      <c r="BS2" s="58">
+        <v>179.63</v>
+      </c>
+      <c r="BT2" s="58">
+        <v>42.2</v>
       </c>
       <c r="BU2" s="35">
         <f t="shared" ref="BU2:BU8" si="0">BV2-BW2</f>
-        <v>2.773076923076923</v>
+        <v>10.571538461538463</v>
       </c>
       <c r="BV2" s="35">
         <f t="shared" ref="BV2:BV8" si="1">BS2/$D2</f>
-        <v>4.5115384615384615</v>
+        <v>13.817692307692308</v>
       </c>
       <c r="BW2" s="35">
         <f t="shared" ref="BW2:BW8" si="2">BT2/$D2</f>
-        <v>1.7384615384615385</v>
+        <v>3.2461538461538462</v>
       </c>
       <c r="BX2" s="36">
         <f t="shared" ref="BX2:BX8" si="3">BY2-BZ2</f>
-        <v>22.339271882261812</v>
+        <v>85.161890007745939</v>
       </c>
       <c r="BY2" s="36">
         <f t="shared" ref="BY2:BY8" si="4">BS2*2400/$G2</f>
-        <v>36.343919442292794</v>
+        <v>111.31216111541441</v>
       </c>
       <c r="BZ2" s="36">
         <f t="shared" ref="BZ2:BZ8" si="5">BT2*2400/$G2</f>
-        <v>14.004647560030984</v>
+        <v>26.150271107668473</v>
       </c>
       <c r="CA2" s="50">
         <v>4</v>
@@ -2543,11 +2555,11 @@
         <v>9.4389473684210525</v>
       </c>
       <c r="BV3" s="35">
-        <f t="shared" si="1"/>
+        <f>BS3/$D3</f>
         <v>11.117894736842105</v>
       </c>
       <c r="BW3" s="35">
-        <f t="shared" si="2"/>
+        <f>BT3/$D3</f>
         <v>1.6789473684210525</v>
       </c>
       <c r="BX3" s="36">
@@ -2555,11 +2567,11 @@
         <v>29.53719461981883</v>
       </c>
       <c r="BY3" s="36">
-        <f t="shared" si="4"/>
+        <f>BS3*2400/$G3</f>
         <v>34.79110623112819</v>
       </c>
       <c r="BZ3" s="36">
-        <f t="shared" si="5"/>
+        <f>BT3*2400/$G3</f>
         <v>5.25391161130936</v>
       </c>
       <c r="CA3" s="50">
@@ -2775,38 +2787,38 @@
       <c r="BQ4" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR4" s="35">
-        <v>1264.72</v>
-      </c>
-      <c r="BS4" s="35">
-        <v>1765.02</v>
-      </c>
-      <c r="BT4" s="35">
-        <v>500.3</v>
+      <c r="BR4" s="58">
+        <v>427.78</v>
+      </c>
+      <c r="BS4" s="58">
+        <v>571.98</v>
+      </c>
+      <c r="BT4" s="58">
+        <v>144.19999999999999</v>
       </c>
       <c r="BU4" s="35">
         <f t="shared" si="0"/>
-        <v>24.321538461538459</v>
+        <v>8.2265384615384622</v>
       </c>
       <c r="BV4" s="35">
         <f t="shared" si="1"/>
-        <v>33.942692307692305</v>
+        <v>10.999615384615385</v>
       </c>
       <c r="BW4" s="35">
         <f t="shared" si="2"/>
-        <v>9.6211538461538471</v>
+        <v>2.773076923076923</v>
       </c>
       <c r="BX4" s="36">
         <f t="shared" si="3"/>
-        <v>69.302890542947168</v>
+        <v>23.441070368509976</v>
       </c>
       <c r="BY4" s="36">
         <f t="shared" si="4"/>
-        <v>96.717840997305814</v>
+        <v>31.342801041143431</v>
       </c>
       <c r="BZ4" s="36">
         <f t="shared" si="5"/>
-        <v>27.414950454358646</v>
+        <v>7.9017306726334535</v>
       </c>
       <c r="CA4" s="50">
         <v>26</v>
@@ -3021,38 +3033,38 @@
       <c r="BQ5" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR5" s="35">
-        <v>1049.3599999999999</v>
-      </c>
-      <c r="BS5" s="35">
-        <v>1638.76</v>
-      </c>
-      <c r="BT5" s="35">
-        <v>589.4</v>
+      <c r="BR5" s="58">
+        <v>475.37</v>
+      </c>
+      <c r="BS5" s="58">
+        <v>683.87</v>
+      </c>
+      <c r="BT5" s="58">
+        <v>208.5</v>
       </c>
       <c r="BU5" s="35">
         <f t="shared" si="0"/>
-        <v>31.798787878787877</v>
+        <v>14.405151515151514</v>
       </c>
       <c r="BV5" s="35">
         <f t="shared" si="1"/>
-        <v>49.659393939393937</v>
+        <v>20.723333333333333</v>
       </c>
       <c r="BW5" s="35">
         <f t="shared" si="2"/>
-        <v>17.860606060606059</v>
+        <v>6.3181818181818183</v>
       </c>
       <c r="BX5" s="36">
         <f t="shared" si="3"/>
-        <v>79.903042609219824</v>
+        <v>36.196833655890096</v>
       </c>
       <c r="BY5" s="36">
         <f t="shared" si="4"/>
-        <v>124.78263904311684</v>
+        <v>52.07297185824423</v>
       </c>
       <c r="BZ5" s="36">
         <f t="shared" si="5"/>
-        <v>44.879596433897014</v>
+        <v>15.876138202354136</v>
       </c>
       <c r="CA5" s="47">
         <v>14</v>
@@ -3268,37 +3280,37 @@
         <v>253</v>
       </c>
       <c r="BR6" s="35">
-        <v>1142.72</v>
+        <v>365.88</v>
       </c>
       <c r="BS6" s="35">
-        <v>1515.32</v>
+        <v>448.88</v>
       </c>
       <c r="BT6" s="35">
-        <v>372.6</v>
+        <v>83</v>
       </c>
       <c r="BU6" s="35">
         <f t="shared" si="0"/>
-        <v>29.300512820512822</v>
+        <v>9.3815384615384616</v>
       </c>
       <c r="BV6" s="35">
         <f t="shared" si="1"/>
-        <v>38.854358974358973</v>
+        <v>11.509743589743589</v>
       </c>
       <c r="BW6" s="35">
         <f t="shared" si="2"/>
-        <v>9.5538461538461537</v>
+        <v>2.1282051282051282</v>
       </c>
       <c r="BX6" s="36">
         <f t="shared" si="3"/>
-        <v>90.422947576656767</v>
+        <v>28.95192878338279</v>
       </c>
       <c r="BY6" s="36">
         <f t="shared" si="4"/>
-        <v>119.90662710187932</v>
+        <v>35.519683481701286</v>
       </c>
       <c r="BZ6" s="36">
         <f t="shared" si="5"/>
-        <v>29.483679525222552</v>
+        <v>6.5677546983184962</v>
       </c>
       <c r="CA6" s="48">
         <v>21</v>
@@ -3534,38 +3546,38 @@
       <c r="BQ7" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR7" s="48">
-        <v>472.77</v>
-      </c>
-      <c r="BS7" s="48">
-        <v>669.37</v>
-      </c>
-      <c r="BT7" s="48">
-        <v>196.6</v>
+      <c r="BR7" s="57">
+        <v>513.49</v>
+      </c>
+      <c r="BS7" s="57">
+        <v>662.99</v>
+      </c>
+      <c r="BT7" s="57">
+        <v>149.5</v>
       </c>
       <c r="BU7" s="35">
         <f t="shared" si="0"/>
-        <v>9.8493750000000002</v>
+        <v>10.697708333333333</v>
       </c>
       <c r="BV7" s="35">
         <f t="shared" si="1"/>
-        <v>13.945208333333333</v>
+        <v>13.812291666666667</v>
       </c>
       <c r="BW7" s="35">
         <f t="shared" si="2"/>
-        <v>4.0958333333333332</v>
+        <v>3.1145833333333335</v>
       </c>
       <c r="BX7" s="36">
         <f t="shared" si="3"/>
-        <v>21.068181818181817</v>
+        <v>22.882798573975045</v>
       </c>
       <c r="BY7" s="36">
         <f t="shared" si="4"/>
-        <v>29.829322638146166</v>
+        <v>29.545008912655973</v>
       </c>
       <c r="BZ7" s="36">
         <f t="shared" si="5"/>
-        <v>8.7611408199643499</v>
+        <v>6.6622103386809268</v>
       </c>
       <c r="CA7" s="47">
         <v>23</v>
@@ -3801,38 +3813,38 @@
       <c r="BQ8" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR8" s="48">
-        <v>152.78</v>
-      </c>
-      <c r="BS8" s="48">
-        <v>201.48</v>
-      </c>
-      <c r="BT8" s="48">
-        <v>48.7</v>
+      <c r="BR8" s="57">
+        <v>59.02</v>
+      </c>
+      <c r="BS8" s="57">
+        <v>77.319999999999993</v>
+      </c>
+      <c r="BT8" s="57">
+        <v>18.3</v>
       </c>
       <c r="BU8" s="35">
         <f t="shared" si="0"/>
-        <v>13.889090909090909</v>
+        <v>5.3654545454545444</v>
       </c>
       <c r="BV8" s="35">
         <f t="shared" si="1"/>
-        <v>18.316363636363636</v>
+        <v>7.0290909090909084</v>
       </c>
       <c r="BW8" s="35">
         <f t="shared" si="2"/>
-        <v>4.4272727272727277</v>
+        <v>1.6636363636363638</v>
       </c>
       <c r="BX8" s="36">
         <f t="shared" si="3"/>
-        <v>70.029029793735674</v>
+        <v>27.052711993888458</v>
       </c>
       <c r="BY8" s="36">
         <f t="shared" si="4"/>
-        <v>92.351413292589768</v>
+        <v>35.440794499618022</v>
       </c>
       <c r="BZ8" s="36">
         <f t="shared" si="5"/>
-        <v>22.322383498854087</v>
+        <v>8.3880825057295638</v>
       </c>
       <c r="CA8" s="47">
         <v>3</v>
@@ -4068,38 +4080,38 @@
       <c r="BQ9" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR9" s="48">
-        <v>115.79</v>
-      </c>
-      <c r="BS9" s="48">
-        <v>156.09</v>
-      </c>
-      <c r="BT9" s="48">
-        <v>40.299999999999997</v>
+      <c r="BR9" s="57">
+        <v>115.7</v>
+      </c>
+      <c r="BS9" s="57">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="BT9" s="57">
+        <v>36.5</v>
       </c>
       <c r="BU9" s="35">
         <f>BV9-BW9</f>
-        <v>4.6315999999999997</v>
+        <v>4.6279999999999992</v>
       </c>
       <c r="BV9" s="35">
         <f t="shared" ref="BV9:BW10" si="27">BS9/$D9</f>
-        <v>6.2435999999999998</v>
+        <v>6.0879999999999992</v>
       </c>
       <c r="BW9" s="35">
         <f t="shared" si="27"/>
-        <v>1.6119999999999999</v>
+        <v>1.46</v>
       </c>
       <c r="BX9" s="36">
         <f>BY9-BZ9</f>
-        <v>27.11180487804878</v>
+        <v>27.090731707317076</v>
       </c>
       <c r="BY9" s="36">
         <f t="shared" ref="BY9:BZ10" si="28">BS9*2400/$G9</f>
-        <v>36.547902439024391</v>
+        <v>35.637073170731711</v>
       </c>
       <c r="BZ9" s="36">
         <f t="shared" si="28"/>
-        <v>9.4360975609756093</v>
+        <v>8.5463414634146346</v>
       </c>
       <c r="CA9" s="46">
         <v>10</v>
@@ -4335,38 +4347,38 @@
       <c r="BQ10" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR10" s="35">
-        <v>513.49</v>
-      </c>
-      <c r="BS10" s="35">
-        <v>662.99</v>
-      </c>
-      <c r="BT10" s="35">
-        <v>149.5</v>
+      <c r="BR10" s="57">
+        <v>129.87</v>
+      </c>
+      <c r="BS10" s="57">
+        <v>156.97</v>
+      </c>
+      <c r="BT10" s="57">
+        <v>27.1</v>
       </c>
       <c r="BU10" s="35">
         <f t="shared" ref="BU10:BU12" si="29">BV10-BW10</f>
-        <v>46.68090909090909</v>
+        <v>11.806363636363635</v>
       </c>
       <c r="BV10" s="35">
         <f t="shared" si="27"/>
-        <v>60.271818181818183</v>
+        <v>14.27</v>
       </c>
       <c r="BW10" s="35">
         <f t="shared" si="27"/>
-        <v>13.590909090909092</v>
+        <v>2.4636363636363638</v>
       </c>
       <c r="BX10" s="36">
         <f>BY10-BZ10</f>
-        <v>131.80491978609626</v>
+        <v>33.335614973262032</v>
       </c>
       <c r="BY10" s="36">
         <f t="shared" si="28"/>
-        <v>170.1792513368984</v>
+        <v>40.29176470588235</v>
       </c>
       <c r="BZ10" s="36">
         <f t="shared" si="28"/>
-        <v>38.37433155080214</v>
+        <v>6.9561497326203208</v>
       </c>
       <c r="CA10" s="46">
         <v>6</v>
@@ -4602,38 +4614,38 @@
       <c r="BQ11" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR11" s="35">
-        <v>59.02</v>
-      </c>
-      <c r="BS11" s="35">
-        <v>77.319999999999993</v>
-      </c>
-      <c r="BT11" s="35">
-        <v>18.3</v>
+      <c r="BR11" s="58">
+        <v>521.99</v>
+      </c>
+      <c r="BS11" s="58">
+        <v>614.19000000000005</v>
+      </c>
+      <c r="BT11" s="58">
+        <v>92.2</v>
       </c>
       <c r="BU11" s="35">
         <f t="shared" si="29"/>
-        <v>1.4395121951219512</v>
+        <v>12.731463414634149</v>
       </c>
       <c r="BV11" s="35">
         <f t="shared" ref="BV11:BV72" si="30">BS11/$D11</f>
-        <v>1.8858536585365853</v>
+        <v>14.980243902439026</v>
       </c>
       <c r="BW11" s="35">
         <f t="shared" ref="BW11:BW72" si="31">BT11/$D11</f>
-        <v>0.44634146341463415</v>
+        <v>2.2487804878048783</v>
       </c>
       <c r="BX11" s="36">
         <f t="shared" ref="BX11:BX72" si="32">BY11-BZ11</f>
-        <v>3.2227884965416811</v>
+        <v>28.503276301419731</v>
       </c>
       <c r="BY11" s="36">
         <f t="shared" ref="BY11:BY72" si="33">BS11*2400/$G11</f>
-        <v>4.2220604295595185</v>
+        <v>33.537859483072445</v>
       </c>
       <c r="BZ11" s="36">
         <f t="shared" ref="BZ11:BZ72" si="34">BT11*2400/$G11</f>
-        <v>0.99927193301783768</v>
+        <v>5.034583181652712</v>
       </c>
       <c r="CA11" s="46">
         <v>21</v>
@@ -4869,38 +4881,38 @@
       <c r="BQ12" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR12" s="35">
-        <v>115.7</v>
-      </c>
-      <c r="BS12" s="35">
-        <v>152.19999999999999</v>
-      </c>
-      <c r="BT12" s="35">
-        <v>36.5</v>
+      <c r="BR12" s="57">
+        <v>337.23</v>
+      </c>
+      <c r="BS12" s="57">
+        <v>471.23</v>
+      </c>
+      <c r="BT12" s="57">
+        <v>134</v>
       </c>
       <c r="BU12" s="35">
         <f t="shared" si="29"/>
-        <v>5.5095238095238086</v>
+        <v>16.058571428571426</v>
       </c>
       <c r="BV12" s="35">
         <f t="shared" si="30"/>
-        <v>7.2476190476190467</v>
+        <v>22.439523809523809</v>
       </c>
       <c r="BW12" s="35">
         <f t="shared" si="31"/>
-        <v>1.7380952380952381</v>
+        <v>6.3809523809523814</v>
       </c>
       <c r="BX12" s="36">
         <f t="shared" si="32"/>
-        <v>13.659976387249113</v>
+        <v>39.814639905548994</v>
       </c>
       <c r="BY12" s="36">
         <f t="shared" si="33"/>
-        <v>17.969303423848878</v>
+        <v>55.63518299881936</v>
       </c>
       <c r="BZ12" s="36">
         <f t="shared" si="34"/>
-        <v>4.3093270365997638</v>
+        <v>15.820543093270366</v>
       </c>
       <c r="CA12" s="47">
         <v>12</v>
@@ -5136,38 +5148,38 @@
       <c r="BQ13" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR13" s="35">
-        <v>129.87</v>
-      </c>
-      <c r="BS13" s="35">
-        <v>156.97</v>
-      </c>
-      <c r="BT13" s="35">
-        <v>27.1</v>
+      <c r="BR13" s="57">
+        <v>68.86</v>
+      </c>
+      <c r="BS13" s="57">
+        <v>117.26</v>
+      </c>
+      <c r="BT13" s="57">
+        <v>48.4</v>
       </c>
       <c r="BU13" s="35">
         <f t="shared" ref="BU13:BU72" si="35">BV13-BW13</f>
-        <v>10.8225</v>
+        <v>5.7383333333333333</v>
       </c>
       <c r="BV13" s="35">
         <f t="shared" si="30"/>
-        <v>13.080833333333333</v>
+        <v>9.7716666666666665</v>
       </c>
       <c r="BW13" s="35">
         <f t="shared" si="31"/>
-        <v>2.2583333333333333</v>
+        <v>4.0333333333333332</v>
       </c>
       <c r="BX13" s="36">
         <f t="shared" si="32"/>
-        <v>41.558400000000006</v>
+        <v>22.035200000000003</v>
       </c>
       <c r="BY13" s="36">
         <f t="shared" si="33"/>
-        <v>50.230400000000003</v>
+        <v>37.523200000000003</v>
       </c>
       <c r="BZ13" s="36">
         <f t="shared" si="34"/>
-        <v>8.6720000000000006</v>
+        <v>15.488</v>
       </c>
       <c r="CA13" s="47">
         <v>5</v>
@@ -5403,38 +5415,38 @@
       <c r="BQ14" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR14" s="35">
-        <v>521.99</v>
-      </c>
-      <c r="BS14" s="35">
-        <v>614.19000000000005</v>
-      </c>
-      <c r="BT14" s="35">
-        <v>92.2</v>
+      <c r="BR14" s="57">
+        <v>1740.33</v>
+      </c>
+      <c r="BS14" s="57">
+        <v>2230.13</v>
+      </c>
+      <c r="BT14" s="57">
+        <v>489.8</v>
       </c>
       <c r="BU14" s="35">
         <f t="shared" si="35"/>
-        <v>10.235098039215687</v>
+        <v>34.124117647058824</v>
       </c>
       <c r="BV14" s="35">
         <f t="shared" si="30"/>
-        <v>12.04294117647059</v>
+        <v>43.728039215686273</v>
       </c>
       <c r="BW14" s="35">
         <f t="shared" si="31"/>
-        <v>1.807843137254902</v>
+        <v>9.6039215686274506</v>
       </c>
       <c r="BX14" s="36">
         <f t="shared" si="32"/>
-        <v>14.932665832290366</v>
+        <v>49.78594671911317</v>
       </c>
       <c r="BY14" s="36">
         <f t="shared" si="33"/>
-        <v>17.570248524941896</v>
+        <v>63.797747183979972</v>
       </c>
       <c r="BZ14" s="36">
         <f t="shared" si="34"/>
-        <v>2.6375826926515287</v>
+        <v>14.011800464866798</v>
       </c>
       <c r="CA14" s="47">
         <v>28</v>
@@ -5670,38 +5682,38 @@
       <c r="BQ15" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR15" s="35">
-        <v>337.23</v>
-      </c>
-      <c r="BS15" s="35">
-        <v>471.23</v>
-      </c>
-      <c r="BT15" s="35">
-        <v>134</v>
+      <c r="BR15" s="57">
+        <v>89.93</v>
+      </c>
+      <c r="BS15" s="57">
+        <v>112.53</v>
+      </c>
+      <c r="BT15" s="57">
+        <v>22.6</v>
       </c>
       <c r="BU15" s="35">
         <f t="shared" si="35"/>
-        <v>18.734999999999999</v>
+        <v>4.9961111111111114</v>
       </c>
       <c r="BV15" s="35">
         <f t="shared" si="30"/>
-        <v>26.179444444444446</v>
+        <v>6.2516666666666669</v>
       </c>
       <c r="BW15" s="35">
         <f t="shared" si="31"/>
-        <v>7.4444444444444446</v>
+        <v>1.2555555555555555</v>
       </c>
       <c r="BX15" s="36">
         <f t="shared" si="32"/>
-        <v>102.1909090909091</v>
+        <v>27.251515151515154</v>
       </c>
       <c r="BY15" s="36">
         <f t="shared" si="33"/>
-        <v>142.79696969696971</v>
+        <v>34.1</v>
       </c>
       <c r="BZ15" s="36">
         <f t="shared" si="34"/>
-        <v>40.606060606060609</v>
+        <v>6.8484848484848486</v>
       </c>
       <c r="CA15" s="46">
         <v>10</v>
@@ -5937,38 +5949,38 @@
       <c r="BQ16" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR16" s="35">
-        <v>68.86</v>
-      </c>
-      <c r="BS16" s="35">
-        <v>117.26</v>
-      </c>
-      <c r="BT16" s="35">
-        <v>48.4</v>
+      <c r="BR16" s="58">
+        <v>188.93</v>
+      </c>
+      <c r="BS16" s="58">
+        <v>223.83</v>
+      </c>
+      <c r="BT16" s="58">
+        <v>34.9</v>
       </c>
       <c r="BU16" s="35">
         <f t="shared" si="35"/>
-        <v>2.3744827586206894</v>
+        <v>6.5148275862068967</v>
       </c>
       <c r="BV16" s="35">
         <f t="shared" si="30"/>
-        <v>4.0434482758620689</v>
+        <v>7.7182758620689658</v>
       </c>
       <c r="BW16" s="35">
         <f t="shared" si="31"/>
-        <v>1.6689655172413793</v>
+        <v>1.2034482758620688</v>
       </c>
       <c r="BX16" s="36">
         <f t="shared" si="32"/>
-        <v>8.9043103448275858</v>
+        <v>24.430603448275864</v>
       </c>
       <c r="BY16" s="36">
         <f t="shared" si="33"/>
-        <v>15.162931034482758</v>
+        <v>28.943534482758622</v>
       </c>
       <c r="BZ16" s="36">
         <f t="shared" si="34"/>
-        <v>6.2586206896551726</v>
+        <v>4.5129310344827589</v>
       </c>
       <c r="CA16" s="46">
         <v>14</v>
@@ -6204,38 +6216,38 @@
       <c r="BQ17" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR17" s="35">
-        <v>1740.33</v>
-      </c>
-      <c r="BS17" s="35">
-        <v>2230.13</v>
-      </c>
-      <c r="BT17" s="35">
-        <v>489.8</v>
+      <c r="BR17" s="57">
+        <v>84.16</v>
+      </c>
+      <c r="BS17" s="57">
+        <v>119.86</v>
+      </c>
+      <c r="BT17" s="57">
+        <v>35.700000000000003</v>
       </c>
       <c r="BU17" s="35">
         <f t="shared" si="35"/>
-        <v>116.02199999999999</v>
+        <v>5.6106666666666669</v>
       </c>
       <c r="BV17" s="35">
         <f t="shared" si="30"/>
-        <v>148.67533333333333</v>
+        <v>7.9906666666666668</v>
       </c>
       <c r="BW17" s="35">
         <f t="shared" si="31"/>
-        <v>32.653333333333336</v>
+        <v>2.3800000000000003</v>
       </c>
       <c r="BX17" s="36">
         <f t="shared" si="32"/>
-        <v>420.62356495468276</v>
+        <v>20.340785498489424</v>
       </c>
       <c r="BY17" s="36">
         <f t="shared" si="33"/>
-        <v>539.00422960725075</v>
+        <v>28.96918429003021</v>
       </c>
       <c r="BZ17" s="36">
         <f t="shared" si="34"/>
-        <v>118.38066465256797</v>
+        <v>8.6283987915407856</v>
       </c>
       <c r="CA17" s="47">
         <v>8</v>
@@ -6471,38 +6483,38 @@
       <c r="BQ18" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR18" s="35">
-        <v>89.93</v>
-      </c>
-      <c r="BS18" s="35">
-        <v>112.53</v>
-      </c>
-      <c r="BT18" s="35">
-        <v>22.6</v>
+      <c r="BR18" s="57">
+        <v>6.54</v>
+      </c>
+      <c r="BS18" s="57">
+        <v>7.54</v>
+      </c>
+      <c r="BT18" s="57">
+        <v>1</v>
       </c>
       <c r="BU18" s="35">
         <f t="shared" si="35"/>
-        <v>29.976666666666663</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="BV18" s="35">
         <f t="shared" si="30"/>
-        <v>37.51</v>
+        <v>2.5133333333333332</v>
       </c>
       <c r="BW18" s="35">
         <f t="shared" si="31"/>
-        <v>7.5333333333333341</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BX18" s="36">
         <f t="shared" si="32"/>
-        <v>441.37423312883436</v>
+        <v>32.098159509202453</v>
       </c>
       <c r="BY18" s="36">
         <f t="shared" si="33"/>
-        <v>552.29447852760734</v>
+        <v>37.006134969325153</v>
       </c>
       <c r="BZ18" s="36">
         <f t="shared" si="34"/>
-        <v>110.92024539877301</v>
+        <v>4.9079754601226995</v>
       </c>
       <c r="CA18" s="46">
         <v>2</v>
@@ -6738,38 +6750,38 @@
       <c r="BQ19" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR19" s="35">
-        <v>188.93</v>
-      </c>
-      <c r="BS19" s="35">
-        <v>223.83</v>
-      </c>
-      <c r="BT19" s="35">
-        <v>34.9</v>
+      <c r="BR19" s="57">
+        <v>1361.76</v>
+      </c>
+      <c r="BS19" s="57">
+        <v>1827.36</v>
+      </c>
+      <c r="BT19" s="57">
+        <v>465.6</v>
       </c>
       <c r="BU19" s="35">
         <f t="shared" si="35"/>
-        <v>3.6332692307692316</v>
+        <v>26.187692307692306</v>
       </c>
       <c r="BV19" s="35">
         <f t="shared" si="30"/>
-        <v>4.3044230769230776</v>
+        <v>35.14153846153846</v>
       </c>
       <c r="BW19" s="35">
         <f t="shared" si="31"/>
-        <v>0.6711538461538461</v>
+        <v>8.953846153846154</v>
       </c>
       <c r="BX19" s="36">
         <f t="shared" si="32"/>
-        <v>4.2702478716190759</v>
+        <v>30.778874406690271</v>
       </c>
       <c r="BY19" s="36">
         <f t="shared" si="33"/>
-        <v>5.0590672794394633</v>
+        <v>41.302493784374292</v>
       </c>
       <c r="BZ19" s="36">
         <f t="shared" si="34"/>
-        <v>0.78881940782038729</v>
+        <v>10.523619377684021</v>
       </c>
       <c r="CA19" s="46">
         <v>28</v>
@@ -7005,38 +7017,32 @@
       <c r="BQ20" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR20" s="35">
-        <v>84.16</v>
-      </c>
-      <c r="BS20" s="35">
-        <v>119.86</v>
-      </c>
-      <c r="BT20" s="35">
-        <v>35.700000000000003</v>
-      </c>
+      <c r="BR20" s="57"/>
+      <c r="BS20" s="57"/>
+      <c r="BT20" s="57"/>
       <c r="BU20" s="35">
         <f t="shared" si="35"/>
-        <v>3.5066666666666668</v>
+        <v>0</v>
       </c>
       <c r="BV20" s="35">
         <f t="shared" si="30"/>
-        <v>4.9941666666666666</v>
+        <v>0</v>
       </c>
       <c r="BW20" s="35">
         <f t="shared" si="31"/>
-        <v>1.4875</v>
+        <v>0</v>
       </c>
       <c r="BX20" s="36">
         <f t="shared" si="32"/>
-        <v>10.454658385093168</v>
+        <v>0</v>
       </c>
       <c r="BY20" s="36">
         <f t="shared" si="33"/>
-        <v>14.889440993788821</v>
+        <v>0</v>
       </c>
       <c r="BZ20" s="36">
         <f t="shared" si="34"/>
-        <v>4.4347826086956523</v>
+        <v>0</v>
       </c>
       <c r="CA20" s="47">
         <v>14</v>
@@ -7272,38 +7278,38 @@
       <c r="BQ21" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR21" s="35">
-        <v>6.54</v>
-      </c>
-      <c r="BS21" s="35">
-        <v>7.54</v>
-      </c>
-      <c r="BT21" s="35">
-        <v>1</v>
+      <c r="BR21" s="57">
+        <v>28.29</v>
+      </c>
+      <c r="BS21" s="57">
+        <v>37.29</v>
+      </c>
+      <c r="BT21" s="57">
+        <v>9</v>
       </c>
       <c r="BU21" s="35">
         <f t="shared" si="35"/>
-        <v>0.1308</v>
+        <v>0.56580000000000008</v>
       </c>
       <c r="BV21" s="35">
         <f t="shared" si="30"/>
-        <v>0.15079999999999999</v>
+        <v>0.74580000000000002</v>
       </c>
       <c r="BW21" s="35">
         <f t="shared" si="31"/>
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="BX21" s="36">
         <f t="shared" si="32"/>
-        <v>0.16444211629125197</v>
+        <v>0.71132530120481929</v>
       </c>
       <c r="BY21" s="36">
         <f t="shared" si="33"/>
-        <v>0.18958617077003667</v>
+        <v>0.93762179151388159</v>
       </c>
       <c r="BZ21" s="36">
         <f t="shared" si="34"/>
-        <v>2.5144054478784705E-2</v>
+        <v>0.22629649030906235</v>
       </c>
       <c r="CA21" s="47">
         <v>3</v>
@@ -7539,38 +7545,38 @@
       <c r="BQ22" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR22" s="35">
-        <v>1361.76</v>
-      </c>
-      <c r="BS22" s="35">
-        <v>1827.36</v>
-      </c>
-      <c r="BT22" s="35">
-        <v>465.6</v>
+      <c r="BR22" s="58">
+        <v>1049.3599999999999</v>
+      </c>
+      <c r="BS22" s="58">
+        <v>1638.76</v>
+      </c>
+      <c r="BT22" s="58">
+        <v>589.4</v>
       </c>
       <c r="BU22" s="35">
         <f t="shared" si="35"/>
-        <v>27.235199999999995</v>
+        <v>20.987199999999998</v>
       </c>
       <c r="BV22" s="35">
         <f t="shared" si="30"/>
-        <v>36.547199999999997</v>
+        <v>32.775199999999998</v>
       </c>
       <c r="BW22" s="35">
         <f t="shared" si="31"/>
-        <v>9.3120000000000012</v>
+        <v>11.788</v>
       </c>
       <c r="BX22" s="36">
         <f t="shared" si="32"/>
-        <v>34.240167627029862</v>
+        <v>26.385165007857516</v>
       </c>
       <c r="BY22" s="36">
         <f t="shared" si="33"/>
-        <v>45.947239392352017</v>
+        <v>41.205070717653221</v>
       </c>
       <c r="BZ22" s="36">
         <f t="shared" si="34"/>
-        <v>11.707071765322159</v>
+        <v>14.819905709795705</v>
       </c>
       <c r="CA22" s="46">
         <v>26</v>
@@ -7806,38 +7812,38 @@
       <c r="BQ23" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR23" s="35">
-        <v>28.29</v>
-      </c>
-      <c r="BS23" s="35">
-        <v>37.29</v>
-      </c>
-      <c r="BT23" s="35">
-        <v>9</v>
+      <c r="BR23" s="58">
+        <v>4.54</v>
+      </c>
+      <c r="BS23" s="58">
+        <v>13.14</v>
+      </c>
+      <c r="BT23" s="58">
+        <v>8.6</v>
       </c>
       <c r="BU23" s="35">
         <f t="shared" si="35"/>
-        <v>3.1433333333333335</v>
+        <v>0.50444444444444447</v>
       </c>
       <c r="BV23" s="35">
         <f t="shared" si="30"/>
-        <v>4.1433333333333335</v>
+        <v>1.46</v>
       </c>
       <c r="BW23" s="35">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0.95555555555555549</v>
       </c>
       <c r="BX23" s="36">
         <f t="shared" si="32"/>
-        <v>60.838709677419345</v>
+        <v>9.7634408602150522</v>
       </c>
       <c r="BY23" s="36">
         <f t="shared" si="33"/>
-        <v>80.193548387096769</v>
+        <v>28.258064516129032</v>
       </c>
       <c r="BZ23" s="36">
         <f t="shared" si="34"/>
-        <v>19.35483870967742</v>
+        <v>18.49462365591398</v>
       </c>
       <c r="CA23" s="46">
         <v>5</v>
@@ -8073,6 +8079,9 @@
       <c r="BQ24" s="17" t="s">
         <v>253</v>
       </c>
+      <c r="BR24" s="58"/>
+      <c r="BS24" s="58"/>
+      <c r="BT24" s="58"/>
       <c r="CA24" s="54">
         <v>12</v>
       </c>
@@ -8307,38 +8316,38 @@
       <c r="BQ25" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR25" s="35">
-        <v>4.54</v>
-      </c>
-      <c r="BS25" s="35">
-        <v>13.14</v>
-      </c>
-      <c r="BT25" s="35">
-        <v>8.6</v>
+      <c r="BR25" s="58">
+        <v>11.49</v>
+      </c>
+      <c r="BS25" s="58">
+        <v>15.79</v>
+      </c>
+      <c r="BT25" s="58">
+        <v>4.3</v>
       </c>
       <c r="BU25" s="35">
         <f t="shared" si="35"/>
-        <v>1.5133333333333332</v>
+        <v>3.8299999999999992</v>
       </c>
       <c r="BV25" s="35">
         <f t="shared" si="30"/>
-        <v>4.38</v>
+        <v>5.2633333333333328</v>
       </c>
       <c r="BW25" s="35">
         <f t="shared" si="31"/>
-        <v>2.8666666666666667</v>
+        <v>1.4333333333333333</v>
       </c>
       <c r="BX25" s="36">
         <f t="shared" si="32"/>
-        <v>7.2206759443339941</v>
+        <v>18.274353876739561</v>
       </c>
       <c r="BY25" s="36">
         <f t="shared" si="33"/>
-        <v>20.898608349900595</v>
+        <v>25.113320079522861</v>
       </c>
       <c r="BZ25" s="36">
         <f t="shared" si="34"/>
-        <v>13.677932405566601</v>
+        <v>6.8389662027833005</v>
       </c>
       <c r="CA25" s="46">
         <v>2</v>
@@ -8574,38 +8583,38 @@
       <c r="BQ26" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR26" s="35">
-        <v>475.37</v>
-      </c>
-      <c r="BS26" s="35">
-        <v>683.87</v>
-      </c>
-      <c r="BT26" s="35">
-        <v>208.5</v>
+      <c r="BR26" s="57">
+        <v>464.42</v>
+      </c>
+      <c r="BS26" s="57">
+        <v>604.72</v>
+      </c>
+      <c r="BT26" s="57">
+        <v>140.30000000000001</v>
       </c>
       <c r="BU26" s="35">
         <f t="shared" si="35"/>
-        <v>9.5074000000000005</v>
+        <v>9.2883999999999993</v>
       </c>
       <c r="BV26" s="35">
         <f t="shared" si="30"/>
-        <v>13.6774</v>
+        <v>12.0944</v>
       </c>
       <c r="BW26" s="35">
         <f t="shared" si="31"/>
-        <v>4.17</v>
+        <v>2.806</v>
       </c>
       <c r="BX26" s="36">
         <f t="shared" si="32"/>
-        <v>24.855947712418303</v>
+        <v>24.283398692810458</v>
       </c>
       <c r="BY26" s="36">
         <f t="shared" si="33"/>
-        <v>35.757908496732028</v>
+        <v>31.619346405228757</v>
       </c>
       <c r="BZ26" s="36">
         <f t="shared" si="34"/>
-        <v>10.901960784313726</v>
+        <v>7.3359477124183003</v>
       </c>
       <c r="CA26" s="47">
         <v>25</v>
@@ -8841,38 +8850,38 @@
       <c r="BQ27" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR27" s="35">
-        <v>11.49</v>
-      </c>
-      <c r="BS27" s="35">
-        <v>15.79</v>
-      </c>
-      <c r="BT27" s="35">
-        <v>4.3</v>
+      <c r="BR27" s="57">
+        <v>545.66999999999996</v>
+      </c>
+      <c r="BS27" s="57">
+        <v>718.17</v>
+      </c>
+      <c r="BT27" s="57">
+        <v>172.5</v>
       </c>
       <c r="BU27" s="35">
         <f t="shared" si="35"/>
-        <v>0.24978260869565216</v>
+        <v>11.862391304347826</v>
       </c>
       <c r="BV27" s="35">
         <f t="shared" si="30"/>
-        <v>0.3432608695652174</v>
+        <v>15.612391304347826</v>
       </c>
       <c r="BW27" s="35">
         <f t="shared" si="31"/>
-        <v>9.3478260869565219E-2</v>
+        <v>3.75</v>
       </c>
       <c r="BX27" s="36">
         <f t="shared" si="32"/>
-        <v>0.53051173528280104</v>
+        <v>25.194459407464407</v>
       </c>
       <c r="BY27" s="36">
         <f t="shared" si="33"/>
-        <v>0.72904963447479798</v>
+        <v>33.159061177375911</v>
       </c>
       <c r="BZ27" s="36">
         <f t="shared" si="34"/>
-        <v>0.19853789919199691</v>
+        <v>7.9646017699115044</v>
       </c>
       <c r="CA27" s="47">
         <v>24</v>
@@ -9108,38 +9117,38 @@
       <c r="BQ28" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR28" s="35">
-        <v>464.42</v>
-      </c>
-      <c r="BS28" s="35">
-        <v>604.72</v>
-      </c>
-      <c r="BT28" s="35">
-        <v>140.30000000000001</v>
+      <c r="BR28" s="57">
+        <v>420.94</v>
+      </c>
+      <c r="BS28" s="57">
+        <v>561.84</v>
+      </c>
+      <c r="BT28" s="57">
+        <v>140.9</v>
       </c>
       <c r="BU28" s="35">
         <f t="shared" si="35"/>
-        <v>14.981290322580644</v>
+        <v>13.578709677419356</v>
       </c>
       <c r="BV28" s="35">
         <f t="shared" si="30"/>
-        <v>19.507096774193549</v>
+        <v>18.123870967741937</v>
       </c>
       <c r="BW28" s="35">
         <f t="shared" si="31"/>
-        <v>4.5258064516129037</v>
+        <v>4.5451612903225804</v>
       </c>
       <c r="BX28" s="36">
         <f t="shared" si="32"/>
-        <v>26.712553324066533</v>
+        <v>24.211666586780424</v>
       </c>
       <c r="BY28" s="36">
         <f t="shared" si="33"/>
-        <v>34.782341945070222</v>
+        <v>32.3159660643244</v>
       </c>
       <c r="BZ28" s="36">
         <f t="shared" si="34"/>
-        <v>8.0697886210036902</v>
+        <v>8.1042994775439769</v>
       </c>
       <c r="CA28" s="47">
         <v>17</v>
@@ -9375,38 +9384,38 @@
       <c r="BQ29" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR29" s="35">
-        <v>545.66999999999996</v>
-      </c>
-      <c r="BS29" s="35">
-        <v>718.17</v>
-      </c>
-      <c r="BT29" s="35">
-        <v>172.5</v>
+      <c r="BR29" s="57">
+        <v>17.7</v>
+      </c>
+      <c r="BS29" s="57">
+        <v>23.8</v>
+      </c>
+      <c r="BT29" s="57">
+        <v>6.1</v>
       </c>
       <c r="BU29" s="35">
         <f t="shared" si="35"/>
-        <v>109.13399999999999</v>
+        <v>3.54</v>
       </c>
       <c r="BV29" s="35">
         <f t="shared" si="30"/>
-        <v>143.63399999999999</v>
+        <v>4.76</v>
       </c>
       <c r="BW29" s="35">
         <f t="shared" si="31"/>
-        <v>34.5</v>
+        <v>1.22</v>
       </c>
       <c r="BX29" s="36">
         <f t="shared" si="32"/>
-        <v>557.28</v>
+        <v>18.076595744680851</v>
       </c>
       <c r="BY29" s="36">
         <f t="shared" si="33"/>
-        <v>733.45021276595742</v>
+        <v>24.306382978723406</v>
       </c>
       <c r="BZ29" s="36">
         <f t="shared" si="34"/>
-        <v>176.17021276595744</v>
+        <v>6.2297872340425533</v>
       </c>
       <c r="CA29" s="52">
         <v>2</v>
@@ -9642,38 +9651,38 @@
       <c r="BQ30" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR30" s="35">
-        <v>420.94</v>
-      </c>
-      <c r="BS30" s="35">
-        <v>561.84</v>
-      </c>
-      <c r="BT30" s="35">
-        <v>140.9</v>
+      <c r="BR30" s="57">
+        <v>609.5</v>
+      </c>
+      <c r="BS30" s="57">
+        <v>802</v>
+      </c>
+      <c r="BT30" s="57">
+        <v>192.5</v>
       </c>
       <c r="BU30" s="35">
         <f t="shared" si="35"/>
-        <v>15.590370370370373</v>
+        <v>22.574074074074073</v>
       </c>
       <c r="BV30" s="35">
         <f t="shared" si="30"/>
-        <v>20.808888888888891</v>
+        <v>29.703703703703702</v>
       </c>
       <c r="BW30" s="35">
         <f t="shared" si="31"/>
-        <v>5.2185185185185183</v>
+        <v>7.1296296296296298</v>
       </c>
       <c r="BX30" s="36">
         <f t="shared" si="32"/>
-        <v>28.826570792672484</v>
+        <v>41.739428180106145</v>
       </c>
       <c r="BY30" s="36">
         <f t="shared" si="33"/>
-        <v>38.475603492552644</v>
+        <v>54.922102379729502</v>
       </c>
       <c r="BZ30" s="36">
         <f t="shared" si="34"/>
-        <v>9.6490326998801574</v>
+        <v>13.182674199623353</v>
       </c>
       <c r="CA30" s="48">
         <v>7</v>
@@ -9909,38 +9918,38 @@
       <c r="BQ31" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR31" s="35">
-        <v>17.7</v>
-      </c>
-      <c r="BS31" s="35">
-        <v>23.8</v>
-      </c>
-      <c r="BT31" s="35">
-        <v>6.1</v>
+      <c r="BR31" s="57">
+        <v>1416.05</v>
+      </c>
+      <c r="BS31" s="57">
+        <v>1822.05</v>
+      </c>
+      <c r="BT31" s="57">
+        <v>406</v>
       </c>
       <c r="BU31" s="35">
         <f t="shared" si="35"/>
-        <v>0.34705882352941175</v>
+        <v>27.765686274509804</v>
       </c>
       <c r="BV31" s="35">
         <f t="shared" si="30"/>
-        <v>0.46666666666666667</v>
+        <v>35.726470588235294</v>
       </c>
       <c r="BW31" s="35">
         <f t="shared" si="31"/>
-        <v>0.11960784313725489</v>
+        <v>7.9607843137254903</v>
       </c>
       <c r="BX31" s="36">
         <f t="shared" si="32"/>
-        <v>0.57168234486656699</v>
+        <v>45.736202511203516</v>
       </c>
       <c r="BY31" s="36">
         <f t="shared" si="33"/>
-        <v>0.76870281400137264</v>
+        <v>58.849368161815171</v>
       </c>
       <c r="BZ31" s="36">
         <f t="shared" si="34"/>
-        <v>0.19702046913480561</v>
+        <v>13.113165650611652</v>
       </c>
       <c r="CA31" s="50">
         <v>17</v>
@@ -10176,38 +10185,38 @@
       <c r="BQ32" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR32" s="35">
-        <v>609.5</v>
-      </c>
-      <c r="BS32" s="35">
-        <v>802</v>
-      </c>
-      <c r="BT32" s="35">
-        <v>192.5</v>
+      <c r="BR32" s="58">
+        <v>7.11</v>
+      </c>
+      <c r="BS32" s="58">
+        <v>10.91</v>
+      </c>
+      <c r="BT32" s="58">
+        <v>3.8</v>
       </c>
       <c r="BU32" s="35">
         <f t="shared" si="35"/>
-        <v>203.16666666666663</v>
+        <v>2.37</v>
       </c>
       <c r="BV32" s="35">
         <f t="shared" si="30"/>
-        <v>267.33333333333331</v>
+        <v>3.6366666666666667</v>
       </c>
       <c r="BW32" s="35">
         <f t="shared" si="31"/>
-        <v>64.166666666666671</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="BX32" s="36">
         <f t="shared" si="32"/>
-        <v>1557.8274760383388</v>
+        <v>18.172523961661341</v>
       </c>
       <c r="BY32" s="36">
         <f t="shared" si="33"/>
-        <v>2049.8402555910543</v>
+        <v>27.884984025559106</v>
       </c>
       <c r="BZ32" s="36">
         <f t="shared" si="34"/>
-        <v>492.01277955271564</v>
+        <v>9.7124600638977636</v>
       </c>
       <c r="CA32" s="50">
         <v>1</v>
@@ -10443,38 +10452,38 @@
       <c r="BQ33" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR33" s="35">
-        <v>1416.05</v>
-      </c>
-      <c r="BS33" s="35">
-        <v>1822.05</v>
-      </c>
-      <c r="BT33" s="35">
-        <v>406</v>
+      <c r="BR33" s="58">
+        <v>229.27</v>
+      </c>
+      <c r="BS33" s="58">
+        <v>287.77</v>
+      </c>
+      <c r="BT33" s="58">
+        <v>58.5</v>
       </c>
       <c r="BU33" s="35">
         <f t="shared" si="35"/>
-        <v>39.334722222222219</v>
+        <v>6.368611111111111</v>
       </c>
       <c r="BV33" s="35">
         <f t="shared" si="30"/>
-        <v>50.612499999999997</v>
+        <v>7.993611111111111</v>
       </c>
       <c r="BW33" s="35">
         <f t="shared" si="31"/>
-        <v>11.277777777777779</v>
+        <v>1.625</v>
       </c>
       <c r="BX33" s="36">
         <f t="shared" si="32"/>
-        <v>119.80118443316411</v>
+        <v>19.396785109983082</v>
       </c>
       <c r="BY33" s="36">
         <f t="shared" si="33"/>
-        <v>154.14974619289339</v>
+        <v>24.346023688663283</v>
       </c>
       <c r="BZ33" s="36">
         <f t="shared" si="34"/>
-        <v>34.348561759729272</v>
+        <v>4.9492385786802027</v>
       </c>
       <c r="CA33" s="50">
         <v>14</v>
@@ -10710,38 +10719,38 @@
       <c r="BQ34" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR34" s="35">
-        <v>7.11</v>
-      </c>
-      <c r="BS34" s="35">
-        <v>10.91</v>
-      </c>
-      <c r="BT34" s="35">
-        <v>3.8</v>
+      <c r="BR34" s="57">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BS34" s="57">
+        <v>1.07</v>
+      </c>
+      <c r="BT34" s="57">
+        <v>1</v>
       </c>
       <c r="BU34" s="35">
         <f t="shared" si="35"/>
-        <v>7.11</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="BV34" s="35">
         <f t="shared" si="30"/>
-        <v>10.91</v>
+        <v>1.07</v>
       </c>
       <c r="BW34" s="35">
         <f t="shared" si="31"/>
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="BX34" s="36">
         <f t="shared" si="32"/>
-        <v>66.396887159533065</v>
+        <v>0.65369649805447416</v>
       </c>
       <c r="BY34" s="36">
         <f t="shared" si="33"/>
-        <v>101.88326848249027</v>
+        <v>9.9922178988326849</v>
       </c>
       <c r="BZ34" s="36">
         <f t="shared" si="34"/>
-        <v>35.4863813229572</v>
+        <v>9.3385214007782107</v>
       </c>
       <c r="CA34" s="50">
         <v>1</v>
@@ -10977,38 +10986,38 @@
       <c r="BQ35" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR35" s="35">
-        <v>229.27</v>
-      </c>
-      <c r="BS35" s="35">
-        <v>287.77</v>
-      </c>
-      <c r="BT35" s="35">
-        <v>58.5</v>
+      <c r="BR35" s="57">
+        <v>669.98</v>
+      </c>
+      <c r="BS35" s="57">
+        <v>939.48</v>
+      </c>
+      <c r="BT35" s="57">
+        <v>269.5</v>
       </c>
       <c r="BU35" s="35">
         <f t="shared" si="35"/>
-        <v>4.4090384615384615</v>
+        <v>12.884230769230772</v>
       </c>
       <c r="BV35" s="35">
         <f t="shared" si="30"/>
-        <v>5.5340384615384615</v>
+        <v>18.066923076923079</v>
       </c>
       <c r="BW35" s="35">
         <f t="shared" si="31"/>
-        <v>1.125</v>
+        <v>5.1826923076923075</v>
       </c>
       <c r="BX35" s="36">
         <f t="shared" si="32"/>
-        <v>9.3809328968903447</v>
+        <v>27.413256955810148</v>
       </c>
       <c r="BY35" s="36">
         <f t="shared" si="33"/>
-        <v>11.77454991816694</v>
+        <v>38.440261865793779</v>
       </c>
       <c r="BZ35" s="36">
         <f t="shared" si="34"/>
-        <v>2.3936170212765959</v>
+        <v>11.027004909983633</v>
       </c>
       <c r="CA35" s="48">
         <v>16</v>
@@ -11244,38 +11253,38 @@
       <c r="BQ36" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR36" s="35">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BS36" s="35">
-        <v>1.07</v>
-      </c>
-      <c r="BT36" s="35">
-        <v>1</v>
+      <c r="BR36" s="57">
+        <v>476.73</v>
+      </c>
+      <c r="BS36" s="57">
+        <v>646.92999999999995</v>
+      </c>
+      <c r="BT36" s="57">
+        <v>170.2</v>
       </c>
       <c r="BU36" s="35">
         <f t="shared" si="35"/>
-        <v>1.4000000000000019E-3</v>
+        <v>9.5345999999999993</v>
       </c>
       <c r="BV36" s="35">
         <f t="shared" si="30"/>
-        <v>2.1400000000000002E-2</v>
+        <v>12.938599999999999</v>
       </c>
       <c r="BW36" s="35">
         <f t="shared" si="31"/>
-        <v>0.02</v>
+        <v>3.4039999999999999</v>
       </c>
       <c r="BX36" s="36">
         <f t="shared" si="32"/>
-        <v>3.6761487964989056E-3</v>
+        <v>25.036148796498903</v>
       </c>
       <c r="BY36" s="36">
         <f t="shared" si="33"/>
-        <v>5.6192560175054702E-2</v>
+        <v>33.974442013129099</v>
       </c>
       <c r="BZ36" s="36">
         <f t="shared" si="34"/>
-        <v>5.2516411378555797E-2</v>
+        <v>8.9382932166301963</v>
       </c>
       <c r="CA36" s="48">
         <v>17</v>
@@ -11511,38 +11520,38 @@
       <c r="BQ37" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR37" s="35">
-        <v>669.98</v>
-      </c>
-      <c r="BS37" s="35">
-        <v>939.48</v>
-      </c>
-      <c r="BT37" s="35">
-        <v>269.5</v>
+      <c r="BR37" s="58">
+        <v>43.37</v>
+      </c>
+      <c r="BS37" s="58">
+        <v>58.27</v>
+      </c>
+      <c r="BT37" s="58">
+        <v>14.9</v>
       </c>
       <c r="BU37" s="35">
         <f t="shared" si="35"/>
-        <v>223.32666666666671</v>
+        <v>14.456666666666669</v>
       </c>
       <c r="BV37" s="35">
         <f t="shared" si="30"/>
-        <v>313.16000000000003</v>
+        <v>19.423333333333336</v>
       </c>
       <c r="BW37" s="35">
         <f t="shared" si="31"/>
-        <v>89.833333333333329</v>
+        <v>4.9666666666666668</v>
       </c>
       <c r="BX37" s="36">
         <f t="shared" si="32"/>
-        <v>356.8468708388815</v>
+        <v>23.099866844207725</v>
       </c>
       <c r="BY37" s="36">
         <f t="shared" si="33"/>
-        <v>500.38881491344875</v>
+        <v>31.035952063914781</v>
       </c>
       <c r="BZ37" s="36">
         <f t="shared" si="34"/>
-        <v>143.54194407456725</v>
+        <v>7.9360852197070573</v>
       </c>
       <c r="CA37" s="48">
         <v>1</v>
@@ -11778,38 +11787,38 @@
       <c r="BQ38" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR38" s="35">
-        <v>476.73</v>
-      </c>
-      <c r="BS38" s="35">
-        <v>646.92999999999995</v>
-      </c>
-      <c r="BT38" s="35">
-        <v>170.2</v>
+      <c r="BR38" s="57">
+        <v>44.55</v>
+      </c>
+      <c r="BS38" s="57">
+        <v>75.75</v>
+      </c>
+      <c r="BT38" s="57">
+        <v>31.2</v>
       </c>
       <c r="BU38" s="35">
         <f t="shared" si="35"/>
-        <v>68.104285714285709</v>
+        <v>6.3642857142857139</v>
       </c>
       <c r="BV38" s="35">
         <f t="shared" si="30"/>
-        <v>92.418571428571425</v>
+        <v>10.821428571428571</v>
       </c>
       <c r="BW38" s="35">
         <f t="shared" si="31"/>
-        <v>24.314285714285713</v>
+        <v>4.4571428571428573</v>
       </c>
       <c r="BX38" s="36">
         <f t="shared" si="32"/>
-        <v>165.77108084613153</v>
+        <v>15.491161982034194</v>
       </c>
       <c r="BY38" s="36">
         <f t="shared" si="33"/>
-        <v>224.95392639814543</v>
+        <v>26.34019124891336</v>
       </c>
       <c r="BZ38" s="36">
         <f t="shared" si="34"/>
-        <v>59.182845552013909</v>
+        <v>10.849029266879166</v>
       </c>
       <c r="CA38" s="50">
         <v>1</v>
@@ -12045,38 +12054,38 @@
       <c r="BQ39" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR39" s="35">
-        <v>43.37</v>
-      </c>
-      <c r="BS39" s="35">
-        <v>58.27</v>
-      </c>
-      <c r="BT39" s="35">
-        <v>14.9</v>
+      <c r="BR39" s="57">
+        <v>212.07</v>
+      </c>
+      <c r="BS39" s="57">
+        <v>294.77</v>
+      </c>
+      <c r="BT39" s="57">
+        <v>82.7</v>
       </c>
       <c r="BU39" s="35">
         <f t="shared" si="35"/>
-        <v>1.2755882352941177</v>
+        <v>6.2373529411764705</v>
       </c>
       <c r="BV39" s="35">
         <f t="shared" si="30"/>
-        <v>1.7138235294117647</v>
+        <v>8.6697058823529414</v>
       </c>
       <c r="BW39" s="35">
         <f t="shared" si="31"/>
-        <v>0.43823529411764706</v>
+        <v>2.4323529411764708</v>
       </c>
       <c r="BX39" s="36">
         <f t="shared" si="32"/>
-        <v>5.2421434327155527</v>
+        <v>25.632957292506042</v>
       </c>
       <c r="BY39" s="36">
         <f t="shared" si="33"/>
-        <v>7.043110394842869</v>
+        <v>35.628928283642225</v>
       </c>
       <c r="BZ39" s="36">
         <f t="shared" si="34"/>
-        <v>1.8009669621273168</v>
+        <v>9.9959709911361809</v>
       </c>
       <c r="CA39" s="48">
         <v>8</v>
@@ -12312,38 +12321,38 @@
       <c r="BQ40" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR40" s="35">
-        <v>44.55</v>
-      </c>
-      <c r="BS40" s="35">
-        <v>75.75</v>
-      </c>
-      <c r="BT40" s="35">
-        <v>31.2</v>
+      <c r="BR40" s="58">
+        <v>389.56</v>
+      </c>
+      <c r="BS40" s="58">
+        <v>495.86</v>
+      </c>
+      <c r="BT40" s="58">
+        <v>106.3</v>
       </c>
       <c r="BU40" s="35">
         <f t="shared" si="35"/>
-        <v>1.65</v>
+        <v>14.42814814814815</v>
       </c>
       <c r="BV40" s="35">
         <f t="shared" si="30"/>
-        <v>2.8055555555555554</v>
+        <v>18.365185185185187</v>
       </c>
       <c r="BW40" s="35">
         <f t="shared" si="31"/>
-        <v>1.1555555555555554</v>
+        <v>3.9370370370370371</v>
       </c>
       <c r="BX40" s="36">
         <f t="shared" si="32"/>
-        <v>4.9009900990099018</v>
+        <v>42.855885588558863</v>
       </c>
       <c r="BY40" s="36">
         <f t="shared" si="33"/>
-        <v>8.3333333333333339</v>
+        <v>54.550055005500553</v>
       </c>
       <c r="BZ40" s="36">
         <f t="shared" si="34"/>
-        <v>3.4323432343234321</v>
+        <v>11.694169416941694</v>
       </c>
       <c r="CA40" s="50">
         <v>11</v>
@@ -12579,38 +12588,38 @@
       <c r="BQ41" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR41" s="35">
-        <v>212.07</v>
-      </c>
-      <c r="BS41" s="35">
-        <v>294.77</v>
-      </c>
-      <c r="BT41" s="35">
-        <v>82.7</v>
+      <c r="BR41" s="57">
+        <v>1298.82</v>
+      </c>
+      <c r="BS41" s="57">
+        <v>1911.72</v>
+      </c>
+      <c r="BT41" s="57">
+        <v>612.9</v>
       </c>
       <c r="BU41" s="35">
         <f t="shared" si="35"/>
-        <v>4.158235294117647</v>
+        <v>25.467058823529413</v>
       </c>
       <c r="BV41" s="35">
         <f t="shared" si="30"/>
-        <v>5.779803921568627</v>
+        <v>37.484705882352941</v>
       </c>
       <c r="BW41" s="35">
         <f t="shared" si="31"/>
-        <v>1.6215686274509804</v>
+        <v>12.017647058823529</v>
       </c>
       <c r="BX41" s="36">
         <f t="shared" si="32"/>
-        <v>5.1708625419079555</v>
+        <v>31.6688814385858</v>
       </c>
       <c r="BY41" s="36">
         <f t="shared" si="33"/>
-        <v>7.18732093873819</v>
+        <v>46.613105760438891</v>
       </c>
       <c r="BZ41" s="36">
         <f t="shared" si="34"/>
-        <v>2.0164583968302345</v>
+        <v>14.944224321853094</v>
       </c>
       <c r="CA41" s="50">
         <v>17</v>
@@ -12846,38 +12855,38 @@
       <c r="BQ42" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR42" s="35">
-        <v>389.56</v>
-      </c>
-      <c r="BS42" s="35">
-        <v>495.86</v>
-      </c>
-      <c r="BT42" s="35">
-        <v>106.3</v>
+      <c r="BR42" s="57">
+        <v>953.57</v>
+      </c>
+      <c r="BS42" s="57">
+        <v>1247.07</v>
+      </c>
+      <c r="BT42" s="57">
+        <v>293.5</v>
       </c>
       <c r="BU42" s="35">
         <f t="shared" si="35"/>
-        <v>8.2885106382978719</v>
+        <v>20.288723404255318</v>
       </c>
       <c r="BV42" s="35">
         <f t="shared" si="30"/>
-        <v>10.550212765957447</v>
+        <v>26.533404255319148</v>
       </c>
       <c r="BW42" s="35">
         <f t="shared" si="31"/>
-        <v>2.2617021276595746</v>
+        <v>6.2446808510638299</v>
       </c>
       <c r="BX42" s="36">
         <f t="shared" si="32"/>
-        <v>12.850404090384298</v>
+        <v>31.455385122876464</v>
       </c>
       <c r="BY42" s="36">
         <f t="shared" si="33"/>
-        <v>16.356919016988289</v>
+        <v>41.13706086095992</v>
       </c>
       <c r="BZ42" s="36">
         <f t="shared" si="34"/>
-        <v>3.5065149266039914</v>
+        <v>9.6816757380834577</v>
       </c>
       <c r="CA42" s="50">
         <v>15</v>
@@ -13113,38 +13122,38 @@
       <c r="BQ43" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR43" s="35">
-        <v>1298.82</v>
-      </c>
-      <c r="BS43" s="35">
-        <v>1911.72</v>
-      </c>
-      <c r="BT43" s="35">
-        <v>612.9</v>
+      <c r="BR43" s="58">
+        <v>121.05</v>
+      </c>
+      <c r="BS43" s="58">
+        <v>186.35</v>
+      </c>
+      <c r="BT43" s="58">
+        <v>65.3</v>
       </c>
       <c r="BU43" s="35">
         <f t="shared" si="35"/>
-        <v>51.952800000000003</v>
+        <v>4.8419999999999996</v>
       </c>
       <c r="BV43" s="35">
         <f t="shared" si="30"/>
-        <v>76.468800000000002</v>
+        <v>7.4539999999999997</v>
       </c>
       <c r="BW43" s="35">
         <f t="shared" si="31"/>
-        <v>24.515999999999998</v>
+        <v>2.6120000000000001</v>
       </c>
       <c r="BX43" s="36">
         <f t="shared" si="32"/>
-        <v>191.53105990783408</v>
+        <v>17.850691244239634</v>
       </c>
       <c r="BY43" s="36">
         <f t="shared" si="33"/>
-        <v>281.91262672811058</v>
+        <v>27.480184331797236</v>
       </c>
       <c r="BZ43" s="36">
         <f t="shared" si="34"/>
-        <v>90.381566820276504</v>
+        <v>9.6294930875576039</v>
       </c>
       <c r="CA43" s="48">
         <v>6</v>
@@ -13380,38 +13389,38 @@
       <c r="BQ44" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR44" s="35">
-        <v>953.57</v>
-      </c>
-      <c r="BS44" s="35">
-        <v>1247.07</v>
-      </c>
-      <c r="BT44" s="35">
-        <v>293.5</v>
+      <c r="BR44" s="57">
+        <v>266.11</v>
+      </c>
+      <c r="BS44" s="57">
+        <v>383.11</v>
+      </c>
+      <c r="BT44" s="57">
+        <v>117</v>
       </c>
       <c r="BU44" s="35">
         <f t="shared" si="35"/>
-        <v>21.672045454545451</v>
+        <v>6.0479545454545454</v>
       </c>
       <c r="BV44" s="35">
         <f t="shared" si="30"/>
-        <v>28.342499999999998</v>
+        <v>8.7070454545454545</v>
       </c>
       <c r="BW44" s="35">
         <f t="shared" si="31"/>
-        <v>6.6704545454545459</v>
+        <v>2.6590909090909092</v>
       </c>
       <c r="BX44" s="36">
         <f t="shared" si="32"/>
-        <v>73.257618437900135</v>
+        <v>20.443790012804094</v>
       </c>
       <c r="BY44" s="36">
         <f t="shared" si="33"/>
-        <v>95.805633802816899</v>
+        <v>29.43226632522407</v>
       </c>
       <c r="BZ44" s="36">
         <f t="shared" si="34"/>
-        <v>22.548015364916772</v>
+        <v>8.9884763124199747</v>
       </c>
       <c r="CA44" s="48">
         <v>14</v>
@@ -13647,38 +13656,38 @@
       <c r="BQ45" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR45" s="35">
-        <v>121.05</v>
-      </c>
-      <c r="BS45" s="35">
-        <v>186.35</v>
-      </c>
-      <c r="BT45" s="35">
-        <v>65.3</v>
+      <c r="BR45" s="58">
+        <v>666.28</v>
+      </c>
+      <c r="BS45" s="58">
+        <v>962.48</v>
+      </c>
+      <c r="BT45" s="58">
+        <v>296.2</v>
       </c>
       <c r="BU45" s="35">
         <f t="shared" si="35"/>
-        <v>3.0262499999999997</v>
+        <v>16.657000000000004</v>
       </c>
       <c r="BV45" s="35">
         <f t="shared" si="30"/>
-        <v>4.6587499999999995</v>
+        <v>24.062000000000001</v>
       </c>
       <c r="BW45" s="35">
         <f t="shared" si="31"/>
-        <v>1.6324999999999998</v>
+        <v>7.4049999999999994</v>
       </c>
       <c r="BX45" s="36">
         <f t="shared" si="32"/>
-        <v>4.9509202453987733</v>
+        <v>27.250715746421271</v>
       </c>
       <c r="BY45" s="36">
         <f t="shared" si="33"/>
-        <v>7.6216768916155422</v>
+        <v>39.365235173824132</v>
       </c>
       <c r="BZ45" s="36">
         <f t="shared" si="34"/>
-        <v>2.6707566462167689</v>
+        <v>12.114519427402863</v>
       </c>
       <c r="CA45" s="48">
         <v>13</v>
@@ -13914,38 +13923,38 @@
       <c r="BQ46" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR46" s="35">
-        <v>266.11</v>
-      </c>
-      <c r="BS46" s="35">
-        <v>383.11</v>
-      </c>
-      <c r="BT46" s="35">
-        <v>117</v>
+      <c r="BR46" s="57">
+        <v>324.27</v>
+      </c>
+      <c r="BS46" s="57">
+        <v>430.57</v>
+      </c>
+      <c r="BT46" s="57">
+        <v>106.3</v>
       </c>
       <c r="BU46" s="35">
         <f t="shared" si="35"/>
-        <v>8.3159375000000004</v>
+        <v>10.133437499999999</v>
       </c>
       <c r="BV46" s="35">
         <f t="shared" si="30"/>
-        <v>11.9721875</v>
+        <v>13.4553125</v>
       </c>
       <c r="BW46" s="35">
         <f t="shared" si="31"/>
-        <v>3.65625</v>
+        <v>3.3218749999999999</v>
       </c>
       <c r="BX46" s="36">
         <f t="shared" si="32"/>
-        <v>19.264720077220076</v>
+        <v>23.475144787644787</v>
       </c>
       <c r="BY46" s="36">
         <f t="shared" si="33"/>
-        <v>27.734797297297298</v>
+        <v>31.170608108108109</v>
       </c>
       <c r="BZ46" s="36">
         <f t="shared" si="34"/>
-        <v>8.4700772200772203</v>
+        <v>7.69546332046332</v>
       </c>
       <c r="CA46" s="50">
         <v>15</v>
@@ -14181,38 +14190,38 @@
       <c r="BQ47" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR47" s="35">
-        <v>666.28</v>
-      </c>
-      <c r="BS47" s="35">
-        <v>962.48</v>
-      </c>
-      <c r="BT47" s="35">
-        <v>296.2</v>
+      <c r="BR47" s="58">
+        <v>478.35</v>
+      </c>
+      <c r="BS47" s="58">
+        <v>585.85</v>
+      </c>
+      <c r="BT47" s="58">
+        <v>107.5</v>
       </c>
       <c r="BU47" s="35">
         <f t="shared" si="35"/>
-        <v>18.507777777777779</v>
+        <v>13.287500000000001</v>
       </c>
       <c r="BV47" s="35">
         <f t="shared" si="30"/>
-        <v>26.735555555555557</v>
+        <v>16.273611111111112</v>
       </c>
       <c r="BW47" s="35">
         <f t="shared" si="31"/>
-        <v>8.2277777777777779</v>
+        <v>2.9861111111111112</v>
       </c>
       <c r="BX47" s="36">
         <f t="shared" si="32"/>
-        <v>31.909961685823756</v>
+        <v>22.90948275862069</v>
       </c>
       <c r="BY47" s="36">
         <f t="shared" si="33"/>
-        <v>46.095785440613028</v>
+        <v>28.057950191570882</v>
       </c>
       <c r="BZ47" s="36">
         <f t="shared" si="34"/>
-        <v>14.185823754789272</v>
+        <v>5.1484674329501914</v>
       </c>
       <c r="CA47" s="50">
         <v>10</v>
@@ -14715,38 +14724,32 @@
       <c r="BQ49" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR49" s="35">
-        <v>152.78</v>
-      </c>
-      <c r="BS49" s="35">
-        <v>201.48</v>
-      </c>
-      <c r="BT49" s="35">
-        <v>48.7</v>
-      </c>
+      <c r="BR49" s="35"/>
+      <c r="BS49" s="35"/>
+      <c r="BT49" s="35"/>
       <c r="BU49" s="35">
         <f t="shared" si="35"/>
-        <v>38.194999999999993</v>
+        <v>0</v>
       </c>
       <c r="BV49" s="35">
-        <f t="shared" si="30"/>
-        <v>50.37</v>
+        <f>BS49/$D49</f>
+        <v>0</v>
       </c>
       <c r="BW49" s="35">
-        <f t="shared" si="31"/>
-        <v>12.175000000000001</v>
+        <f>BT49/$D49</f>
+        <v>0</v>
       </c>
       <c r="BX49" s="36">
         <f t="shared" si="32"/>
-        <v>133.23837209302326</v>
+        <v>0</v>
       </c>
       <c r="BY49" s="36">
-        <f t="shared" si="33"/>
-        <v>175.7093023255814</v>
+        <f>BS49*2400/$G49</f>
+        <v>0</v>
       </c>
       <c r="BZ49" s="36">
-        <f t="shared" si="34"/>
-        <v>42.470930232558139</v>
+        <f>BT49*2400/$G49</f>
+        <v>0</v>
       </c>
       <c r="CA49" s="48">
         <v>1</v>
@@ -14983,37 +14986,37 @@
         <v>254</v>
       </c>
       <c r="BR50" s="35">
-        <v>411.32</v>
+        <v>152.78</v>
       </c>
       <c r="BS50" s="35">
-        <v>531.62</v>
+        <v>201.48</v>
       </c>
       <c r="BT50" s="35">
-        <v>120.3</v>
+        <v>48.7</v>
       </c>
       <c r="BU50" s="35">
         <f t="shared" si="35"/>
-        <v>15.82</v>
+        <v>5.8761538461538461</v>
       </c>
       <c r="BV50" s="35">
         <f t="shared" si="30"/>
-        <v>20.446923076923078</v>
+        <v>7.7492307692307687</v>
       </c>
       <c r="BW50" s="35">
         <f t="shared" si="31"/>
-        <v>4.6269230769230765</v>
+        <v>1.8730769230769231</v>
       </c>
       <c r="BX50" s="36">
         <f t="shared" si="32"/>
-        <v>70.968224299065426</v>
+        <v>26.360316319194826</v>
       </c>
       <c r="BY50" s="36">
         <f t="shared" si="33"/>
-        <v>91.724514737598852</v>
+        <v>34.762904385334295</v>
       </c>
       <c r="BZ50" s="36">
         <f t="shared" si="34"/>
-        <v>20.75629043853343</v>
+        <v>8.4025880661394687</v>
       </c>
       <c r="CA50" s="50">
         <v>28</v>
@@ -15250,37 +15253,37 @@
         <v>254</v>
       </c>
       <c r="BR51" s="35">
-        <v>33.03</v>
+        <v>411.32</v>
       </c>
       <c r="BS51" s="35">
-        <v>43.03</v>
+        <v>531.62</v>
       </c>
       <c r="BT51" s="35">
-        <v>10</v>
+        <v>120.3</v>
       </c>
       <c r="BU51" s="35">
         <f t="shared" si="35"/>
-        <v>0.73399999999999999</v>
+        <v>9.1404444444444444</v>
       </c>
       <c r="BV51" s="35">
         <f t="shared" si="30"/>
-        <v>0.9562222222222222</v>
+        <v>11.813777777777778</v>
       </c>
       <c r="BW51" s="35">
         <f t="shared" si="31"/>
-        <v>0.22222222222222221</v>
+        <v>2.6733333333333333</v>
       </c>
       <c r="BX51" s="36">
         <f t="shared" si="32"/>
-        <v>3.2804469273743022</v>
+        <v>40.851148355058967</v>
       </c>
       <c r="BY51" s="36">
         <f t="shared" si="33"/>
-        <v>4.2736188702669153</v>
+        <v>52.799006828057109</v>
       </c>
       <c r="BZ51" s="36">
         <f t="shared" si="34"/>
-        <v>0.99317194289261324</v>
+        <v>11.947858472998139</v>
       </c>
       <c r="CA51" s="48">
         <v>6</v>
@@ -15517,37 +15520,37 @@
         <v>253</v>
       </c>
       <c r="BR52" s="35">
-        <v>140.66</v>
+        <v>33.03</v>
       </c>
       <c r="BS52" s="35">
-        <v>183.76</v>
+        <v>43.03</v>
       </c>
       <c r="BT52" s="35">
-        <v>43.1</v>
+        <v>10</v>
       </c>
       <c r="BU52" s="35">
         <f t="shared" si="35"/>
-        <v>17.5825</v>
+        <v>4.1287500000000001</v>
       </c>
       <c r="BV52" s="35">
         <f t="shared" si="30"/>
-        <v>22.97</v>
+        <v>5.3787500000000001</v>
       </c>
       <c r="BW52" s="35">
         <f t="shared" si="31"/>
-        <v>5.3875000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="BX52" s="36">
         <f t="shared" si="32"/>
-        <v>85.076612903225794</v>
+        <v>19.97782258064516</v>
       </c>
       <c r="BY52" s="36">
         <f t="shared" si="33"/>
-        <v>111.14516129032258</v>
+        <v>26.026209677419356</v>
       </c>
       <c r="BZ52" s="36">
         <f t="shared" si="34"/>
-        <v>26.068548387096776</v>
+        <v>6.0483870967741939</v>
       </c>
       <c r="CA52" s="48">
         <v>14</v>
@@ -15784,37 +15787,37 @@
         <v>255</v>
       </c>
       <c r="BR53" s="35">
-        <v>214.44</v>
+        <v>140.66</v>
       </c>
       <c r="BS53" s="35">
-        <v>298.64</v>
+        <v>183.76</v>
       </c>
       <c r="BT53" s="35">
-        <v>84.2</v>
+        <v>43.1</v>
       </c>
       <c r="BU53" s="35">
         <f t="shared" si="35"/>
-        <v>10.21142857142857</v>
+        <v>6.6980952380952381</v>
       </c>
       <c r="BV53" s="35">
         <f t="shared" si="30"/>
-        <v>14.220952380952379</v>
+        <v>8.7504761904761903</v>
       </c>
       <c r="BW53" s="35">
         <f t="shared" si="31"/>
-        <v>4.0095238095238095</v>
+        <v>2.0523809523809526</v>
       </c>
       <c r="BX53" s="36">
         <f t="shared" si="32"/>
-        <v>33.896858328393598</v>
+        <v>22.234341039320292</v>
       </c>
       <c r="BY53" s="36">
         <f t="shared" si="33"/>
-        <v>47.206480932622014</v>
+        <v>29.047223868800632</v>
       </c>
       <c r="BZ53" s="36">
         <f t="shared" si="34"/>
-        <v>13.309622604228414</v>
+        <v>6.8128828294803396</v>
       </c>
       <c r="CA53" s="48">
         <v>29</v>
@@ -16051,37 +16054,37 @@
         <v>255</v>
       </c>
       <c r="BR54" s="35">
-        <v>711.93</v>
+        <v>214.44</v>
       </c>
       <c r="BS54" s="35">
-        <v>961.83</v>
+        <v>298.64</v>
       </c>
       <c r="BT54" s="35">
-        <v>249.9</v>
+        <v>84.2</v>
       </c>
       <c r="BU54" s="35">
         <f t="shared" si="35"/>
-        <v>16.556511627906978</v>
+        <v>4.9869767441860464</v>
       </c>
       <c r="BV54" s="35">
         <f t="shared" si="30"/>
-        <v>22.368139534883721</v>
+        <v>6.9451162790697669</v>
       </c>
       <c r="BW54" s="35">
         <f t="shared" si="31"/>
-        <v>5.811627906976744</v>
+        <v>1.9581395348837209</v>
       </c>
       <c r="BX54" s="36">
         <f t="shared" si="32"/>
-        <v>67.120993086109365</v>
+        <v>20.217473287240729</v>
       </c>
       <c r="BY54" s="36">
         <f t="shared" si="33"/>
-        <v>90.68164676304211</v>
+        <v>28.155876807039597</v>
       </c>
       <c r="BZ54" s="36">
         <f t="shared" si="34"/>
-        <v>23.560653676932748</v>
+        <v>7.9384035197988689</v>
       </c>
       <c r="CA54" s="48">
         <v>36</v>
@@ -16318,37 +16321,37 @@
         <v>253</v>
       </c>
       <c r="BR55" s="35">
-        <v>0.53</v>
+        <v>711.93</v>
       </c>
       <c r="BS55" s="35">
-        <v>1.43</v>
+        <v>961.83</v>
       </c>
       <c r="BT55" s="35">
-        <v>0.9</v>
+        <v>249.9</v>
       </c>
       <c r="BU55" s="35">
         <f t="shared" si="35"/>
-        <v>9.8148148148148144E-3</v>
+        <v>13.183888888888889</v>
       </c>
       <c r="BV55" s="35">
         <f t="shared" si="30"/>
-        <v>2.6481481481481481E-2</v>
+        <v>17.811666666666667</v>
       </c>
       <c r="BW55" s="35">
         <f t="shared" si="31"/>
-        <v>1.6666666666666666E-2</v>
+        <v>4.6277777777777782</v>
       </c>
       <c r="BX55" s="36">
         <f t="shared" si="32"/>
-        <v>1.9531969780726001E-2</v>
+        <v>26.236594803758983</v>
       </c>
       <c r="BY55" s="36">
         <f t="shared" si="33"/>
-        <v>5.2699465634789021E-2</v>
+        <v>35.446102819237147</v>
       </c>
       <c r="BZ55" s="36">
         <f t="shared" si="34"/>
-        <v>3.316749585406302E-2</v>
+        <v>9.2095080154781641</v>
       </c>
       <c r="CA55" s="48">
         <v>1</v>
@@ -16585,37 +16588,37 @@
         <v>254</v>
       </c>
       <c r="BR56" s="35">
-        <v>2083.98</v>
+        <v>0.53</v>
       </c>
       <c r="BS56" s="35">
-        <v>2820.18</v>
+        <v>1.43</v>
       </c>
       <c r="BT56" s="35">
-        <v>736.2</v>
+        <v>0.9</v>
       </c>
       <c r="BU56" s="35">
         <f t="shared" si="35"/>
-        <v>1041.9899999999998</v>
+        <v>0.26499999999999996</v>
       </c>
       <c r="BV56" s="35">
         <f t="shared" si="30"/>
-        <v>1410.09</v>
+        <v>0.71499999999999997</v>
       </c>
       <c r="BW56" s="35">
         <f t="shared" si="31"/>
-        <v>368.1</v>
+        <v>0.45</v>
       </c>
       <c r="BX56" s="36">
         <f t="shared" si="32"/>
-        <v>48091.846153846156</v>
+        <v>12.23076923076923</v>
       </c>
       <c r="BY56" s="36">
         <f t="shared" si="33"/>
-        <v>65081.076923076922</v>
+        <v>33</v>
       </c>
       <c r="BZ56" s="36">
         <f t="shared" si="34"/>
-        <v>16989.23076923077</v>
+        <v>20.76923076923077</v>
       </c>
       <c r="CA56" s="48">
         <v>36</v>
@@ -16852,37 +16855,37 @@
         <v>253</v>
       </c>
       <c r="BR57" s="35">
-        <v>37.85</v>
+        <v>2083.98</v>
       </c>
       <c r="BS57" s="35">
-        <v>46.55</v>
+        <v>2820.18</v>
       </c>
       <c r="BT57" s="35">
-        <v>8.6999999999999993</v>
+        <v>736.2</v>
       </c>
       <c r="BU57" s="35">
         <f t="shared" si="35"/>
-        <v>0.70092592592592584</v>
+        <v>38.592222222222219</v>
       </c>
       <c r="BV57" s="35">
         <f t="shared" si="30"/>
-        <v>0.86203703703703694</v>
+        <v>52.225555555555552</v>
       </c>
       <c r="BW57" s="35">
         <f t="shared" si="31"/>
-        <v>0.16111111111111109</v>
+        <v>13.633333333333335</v>
       </c>
       <c r="BX57" s="36">
         <f t="shared" si="32"/>
-        <v>0.84832184680898748</v>
+        <v>46.707681963355185</v>
       </c>
       <c r="BY57" s="36">
         <f t="shared" si="33"/>
-        <v>1.0433126015576848</v>
+        <v>63.20793410657253</v>
       </c>
       <c r="BZ57" s="36">
         <f t="shared" si="34"/>
-        <v>0.19499075474869726</v>
+        <v>16.500252143217349</v>
       </c>
       <c r="CA57" s="50">
         <v>4</v>
@@ -17118,38 +17121,38 @@
       <c r="BQ58" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR58" s="35">
-        <v>14.82</v>
-      </c>
-      <c r="BS58" s="35">
-        <v>23.82</v>
-      </c>
-      <c r="BT58" s="35">
-        <v>9</v>
+      <c r="BR58" s="57">
+        <v>37.85</v>
+      </c>
+      <c r="BS58" s="57">
+        <v>46.55</v>
+      </c>
+      <c r="BT58" s="57">
+        <v>8.6999999999999993</v>
       </c>
       <c r="BU58" s="35">
         <f t="shared" si="35"/>
-        <v>1.8525</v>
+        <v>4.7312499999999993</v>
       </c>
       <c r="BV58" s="35">
         <f t="shared" si="30"/>
-        <v>2.9775</v>
+        <v>5.8187499999999996</v>
       </c>
       <c r="BW58" s="35">
         <f t="shared" si="31"/>
-        <v>1.125</v>
+        <v>1.0874999999999999</v>
       </c>
       <c r="BX58" s="36">
         <f t="shared" si="32"/>
-        <v>10.923832923832926</v>
+        <v>27.899262899262897</v>
       </c>
       <c r="BY58" s="36">
         <f t="shared" si="33"/>
-        <v>17.557739557739559</v>
+        <v>34.31203931203931</v>
       </c>
       <c r="BZ58" s="36">
         <f t="shared" si="34"/>
-        <v>6.6339066339066335</v>
+        <v>6.4127764127764131</v>
       </c>
       <c r="CA58" s="50">
         <v>1</v>
@@ -17385,13 +17388,13 @@
       <c r="BQ59" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR59" s="35">
+      <c r="BR59" s="57">
         <v>919.21</v>
       </c>
-      <c r="BS59" s="35">
+      <c r="BS59" s="57">
         <v>1101.4100000000001</v>
       </c>
-      <c r="BT59" s="35">
+      <c r="BT59" s="57">
         <v>182.2</v>
       </c>
       <c r="BU59" s="35">
@@ -17652,13 +17655,13 @@
       <c r="BQ60" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR60" s="35">
+      <c r="BR60" s="57">
         <v>538</v>
       </c>
-      <c r="BS60" s="35">
+      <c r="BS60" s="57">
         <v>691</v>
       </c>
-      <c r="BT60" s="35">
+      <c r="BT60" s="57">
         <v>153</v>
       </c>
       <c r="BU60" s="35">
@@ -17919,13 +17922,13 @@
       <c r="BQ61" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR61" s="35">
+      <c r="BR61" s="57">
         <v>281.27</v>
       </c>
-      <c r="BS61" s="35">
+      <c r="BS61" s="57">
         <v>338.87</v>
       </c>
-      <c r="BT61" s="35">
+      <c r="BT61" s="57">
         <v>57.6</v>
       </c>
       <c r="BU61" s="35">
@@ -18186,13 +18189,13 @@
       <c r="BQ62" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR62" s="35">
+      <c r="BR62" s="57">
         <v>629.61</v>
       </c>
-      <c r="BS62" s="35">
+      <c r="BS62" s="57">
         <v>895.71</v>
       </c>
-      <c r="BT62" s="35">
+      <c r="BT62" s="57">
         <v>266.10000000000002</v>
       </c>
       <c r="BU62" s="35">
@@ -18453,13 +18456,13 @@
       <c r="BQ63" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR63" s="35">
+      <c r="BR63" s="58">
         <v>956.81</v>
       </c>
-      <c r="BS63" s="35">
+      <c r="BS63" s="58">
         <v>1202.71</v>
       </c>
-      <c r="BT63" s="35">
+      <c r="BT63" s="58">
         <v>245.9</v>
       </c>
       <c r="BU63" s="35">
@@ -18720,13 +18723,13 @@
       <c r="BQ64" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR64" s="35">
+      <c r="BR64" s="58">
         <v>115.79</v>
       </c>
-      <c r="BS64" s="35">
+      <c r="BS64" s="58">
         <v>156.09</v>
       </c>
-      <c r="BT64" s="35">
+      <c r="BT64" s="58">
         <v>40.299999999999997</v>
       </c>
       <c r="BU64" s="35">
@@ -34893,9 +34896,15 @@
       <c r="BQ125" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR125" s="35"/>
-      <c r="BS125" s="35"/>
-      <c r="BT125" s="35"/>
+      <c r="BR125" s="35">
+        <v>1846.56</v>
+      </c>
+      <c r="BS125" s="35">
+        <v>2364.96</v>
+      </c>
+      <c r="BT125" s="35">
+        <v>518.4</v>
+      </c>
       <c r="BU125" s="35"/>
       <c r="BV125" s="35"/>
       <c r="BW125" s="35"/>
@@ -35137,37 +35146,37 @@
         <v>254</v>
       </c>
       <c r="BR126" s="35">
-        <v>1846.56</v>
+        <v>118.21</v>
       </c>
       <c r="BS126" s="35">
-        <v>2364.96</v>
+        <v>152.61000000000001</v>
       </c>
       <c r="BT126" s="35">
-        <v>518.4</v>
+        <v>34.4</v>
       </c>
       <c r="BU126" s="35">
         <f t="shared" si="58"/>
-        <v>63.674482758620684</v>
+        <v>4.0762068965517253</v>
       </c>
       <c r="BV126" s="35">
         <f t="shared" si="59"/>
-        <v>81.550344827586201</v>
+        <v>5.2624137931034491</v>
       </c>
       <c r="BW126" s="35">
         <f t="shared" si="60"/>
-        <v>17.875862068965517</v>
+        <v>1.1862068965517241</v>
       </c>
       <c r="BX126" s="36">
         <f t="shared" si="61"/>
-        <v>357.88936445126382</v>
+        <v>22.91076475813616</v>
       </c>
       <c r="BY126" s="36">
         <f t="shared" si="62"/>
-        <v>458.36259387870467</v>
+        <v>29.57796979730276</v>
       </c>
       <c r="BZ126" s="36">
         <f t="shared" si="63"/>
-        <v>100.47322942744084</v>
+        <v>6.6672050391665998</v>
       </c>
       <c r="CA126" s="48">
         <v>19</v>
@@ -35404,37 +35413,37 @@
         <v>253</v>
       </c>
       <c r="BR127" s="35">
-        <v>118.21</v>
+        <v>122.88</v>
       </c>
       <c r="BS127" s="35">
-        <v>152.61000000000001</v>
+        <v>216.38</v>
       </c>
       <c r="BT127" s="35">
-        <v>34.4</v>
+        <v>93.5</v>
       </c>
       <c r="BU127" s="35">
         <f t="shared" si="58"/>
-        <v>4.3781481481481492</v>
+        <v>4.5511111111111111</v>
       </c>
       <c r="BV127" s="35">
         <f t="shared" si="59"/>
-        <v>5.6522222222222229</v>
+        <v>8.0140740740740739</v>
       </c>
       <c r="BW127" s="35">
         <f t="shared" si="60"/>
-        <v>1.2740740740740739</v>
+        <v>3.4629629629629628</v>
       </c>
       <c r="BX127" s="36">
         <f t="shared" si="61"/>
-        <v>17.030073833963627</v>
+        <v>17.702863317125882</v>
       </c>
       <c r="BY127" s="36">
         <f t="shared" si="62"/>
-        <v>21.985953538627772</v>
+        <v>31.173059607419415</v>
       </c>
       <c r="BZ127" s="36">
         <f t="shared" si="63"/>
-        <v>4.9558797046641452</v>
+        <v>13.470196290293535</v>
       </c>
       <c r="CA127" s="50">
         <v>15</v>
@@ -35671,37 +35680,37 @@
         <v>255</v>
       </c>
       <c r="BR128" s="35">
-        <v>122.88</v>
+        <v>380.34</v>
       </c>
       <c r="BS128" s="35">
-        <v>216.38</v>
+        <v>507.64</v>
       </c>
       <c r="BT128" s="35">
-        <v>93.5</v>
+        <v>127.3</v>
       </c>
       <c r="BU128" s="35">
         <f t="shared" si="58"/>
-        <v>2.4576000000000002</v>
+        <v>7.6067999999999998</v>
       </c>
       <c r="BV128" s="35">
         <f t="shared" si="59"/>
-        <v>4.3276000000000003</v>
+        <v>10.152799999999999</v>
       </c>
       <c r="BW128" s="35">
         <f t="shared" si="60"/>
-        <v>1.87</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="BX128" s="36">
         <f t="shared" si="61"/>
-        <v>6.0494769230769236</v>
+        <v>18.724430769230771</v>
       </c>
       <c r="BY128" s="36">
         <f t="shared" si="62"/>
-        <v>10.652553846153847</v>
+        <v>24.991507692307692</v>
       </c>
       <c r="BZ128" s="36">
         <f t="shared" si="63"/>
-        <v>4.6030769230769231</v>
+        <v>6.2670769230769228</v>
       </c>
       <c r="CA128" s="48">
         <v>31</v>
@@ -35938,37 +35947,37 @@
         <v>255</v>
       </c>
       <c r="BR129" s="35">
-        <v>380.34</v>
+        <v>0.12</v>
       </c>
       <c r="BS129" s="35">
-        <v>507.64</v>
+        <v>2.12</v>
       </c>
       <c r="BT129" s="35">
-        <v>127.3</v>
+        <v>2</v>
       </c>
       <c r="BU129" s="35">
         <f t="shared" si="58"/>
-        <v>380.34</v>
+        <v>0.12000000000000011</v>
       </c>
       <c r="BV129" s="35">
         <f t="shared" si="59"/>
-        <v>507.64</v>
+        <v>2.12</v>
       </c>
       <c r="BW129" s="35">
         <f t="shared" si="60"/>
-        <v>127.3</v>
+        <v>2</v>
       </c>
       <c r="BX129" s="36">
         <f t="shared" si="61"/>
-        <v>6167.6756756756758</v>
+        <v>1.9459459459459438</v>
       </c>
       <c r="BY129" s="36">
         <f t="shared" si="62"/>
-        <v>8232</v>
+        <v>34.378378378378379</v>
       </c>
       <c r="BZ129" s="36">
         <f t="shared" si="63"/>
-        <v>2064.3243243243242</v>
+        <v>32.432432432432435</v>
       </c>
       <c r="CA129" s="48">
         <v>1</v>
@@ -36205,37 +36214,37 @@
         <v>255</v>
       </c>
       <c r="BR130" s="35">
-        <v>0.12</v>
+        <v>245.91</v>
       </c>
       <c r="BS130" s="35">
-        <v>2.12</v>
+        <v>326.01</v>
       </c>
       <c r="BT130" s="35">
-        <v>2</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="BU130" s="35">
         <f t="shared" si="58"/>
-        <v>3.636363636363632E-3</v>
+        <v>7.4518181818181812</v>
       </c>
       <c r="BV130" s="35">
         <f t="shared" si="59"/>
-        <v>6.424242424242424E-2</v>
+        <v>9.8790909090909089</v>
       </c>
       <c r="BW130" s="35">
         <f t="shared" si="60"/>
-        <v>6.0606060606060608E-2</v>
+        <v>2.4272727272727272</v>
       </c>
       <c r="BX130" s="36">
         <f t="shared" si="61"/>
-        <v>1.2432012432012418E-2</v>
+        <v>25.476301476301476</v>
       </c>
       <c r="BY130" s="36">
         <f t="shared" si="62"/>
-        <v>0.21963221963221963</v>
+        <v>33.774669774669775</v>
       </c>
       <c r="BZ130" s="36">
         <f t="shared" si="63"/>
-        <v>0.20720020720020721</v>
+        <v>8.2983682983682989</v>
       </c>
       <c r="CA130" s="50">
         <v>23</v>
@@ -36472,37 +36481,37 @@
         <v>255</v>
       </c>
       <c r="BR131" s="35">
-        <v>245.91</v>
+        <v>91.9</v>
       </c>
       <c r="BS131" s="35">
-        <v>326.01</v>
+        <v>124.9</v>
       </c>
       <c r="BT131" s="35">
-        <v>80.099999999999994</v>
+        <v>33</v>
       </c>
       <c r="BU131" s="35">
         <f t="shared" si="58"/>
-        <v>9.1077777777777769</v>
+        <v>3.4037037037037035</v>
       </c>
       <c r="BV131" s="35">
         <f t="shared" si="59"/>
-        <v>12.074444444444444</v>
+        <v>4.6259259259259258</v>
       </c>
       <c r="BW131" s="35">
         <f t="shared" si="60"/>
-        <v>2.9666666666666663</v>
+        <v>1.2222222222222223</v>
       </c>
       <c r="BX131" s="36">
         <f t="shared" si="61"/>
-        <v>74.858447488584474</v>
+        <v>27.975646879756471</v>
       </c>
       <c r="BY131" s="36">
         <f t="shared" si="62"/>
-        <v>99.242009132420094</v>
+        <v>38.021308980213092</v>
       </c>
       <c r="BZ131" s="36">
         <f t="shared" si="63"/>
-        <v>24.383561643835616</v>
+        <v>10.045662100456621</v>
       </c>
       <c r="CA131" s="50">
         <v>17</v>
@@ -36739,37 +36748,37 @@
         <v>254</v>
       </c>
       <c r="BR132" s="35">
-        <v>91.9</v>
+        <v>1167.83</v>
       </c>
       <c r="BS132" s="35">
-        <v>124.9</v>
+        <v>1675.63</v>
       </c>
       <c r="BT132" s="35">
-        <v>33</v>
+        <v>507.8</v>
       </c>
       <c r="BU132" s="35">
         <f t="shared" si="58"/>
-        <v>1.8019607843137257</v>
+        <v>22.898627450980396</v>
       </c>
       <c r="BV132" s="35">
         <f t="shared" si="59"/>
-        <v>2.4490196078431374</v>
+        <v>32.855490196078435</v>
       </c>
       <c r="BW132" s="35">
         <f t="shared" si="60"/>
-        <v>0.6470588235294118</v>
+        <v>9.9568627450980394</v>
       </c>
       <c r="BX132" s="36">
         <f t="shared" si="61"/>
-        <v>2.4698491618234959</v>
+        <v>31.385897134410591</v>
       </c>
       <c r="BY132" s="36">
         <f t="shared" si="62"/>
-        <v>3.3567373265696911</v>
+        <v>45.033224711929321</v>
       </c>
       <c r="BZ132" s="36">
         <f t="shared" si="63"/>
-        <v>0.88688816474619547</v>
+        <v>13.647327577518729</v>
       </c>
       <c r="CA132" s="48">
         <v>33</v>
@@ -37006,37 +37015,37 @@
         <v>255</v>
       </c>
       <c r="BR133" s="35">
-        <v>1167.83</v>
+        <v>0.44</v>
       </c>
       <c r="BS133" s="35">
-        <v>1675.63</v>
+        <v>0.44</v>
       </c>
       <c r="BT133" s="35">
-        <v>507.8</v>
+        <v>0</v>
       </c>
       <c r="BU133" s="35">
         <f t="shared" si="58"/>
-        <v>1167.8300000000002</v>
+        <v>0.44</v>
       </c>
       <c r="BV133" s="35">
         <f t="shared" si="59"/>
-        <v>1675.63</v>
+        <v>0.44</v>
       </c>
       <c r="BW133" s="35">
         <f t="shared" si="60"/>
-        <v>507.8</v>
+        <v>0</v>
       </c>
       <c r="BX133" s="36">
         <f t="shared" si="61"/>
-        <v>26441.433962264156</v>
+        <v>9.9622641509433958</v>
       </c>
       <c r="BY133" s="36">
         <f t="shared" si="62"/>
-        <v>37938.792452830196</v>
+        <v>9.9622641509433958</v>
       </c>
       <c r="BZ133" s="36">
         <f t="shared" si="63"/>
-        <v>11497.358490566037</v>
+        <v>0</v>
       </c>
       <c r="CA133" s="50">
         <v>1</v>
@@ -37273,21 +37282,21 @@
         <v>255</v>
       </c>
       <c r="BR134" s="35">
-        <v>0.44</v>
+        <v>0.1</v>
       </c>
       <c r="BS134" s="35">
-        <v>0.44</v>
+        <v>0.1</v>
       </c>
       <c r="BT134" s="35">
         <v>0</v>
       </c>
       <c r="BU134" s="35">
         <f t="shared" si="58"/>
-        <v>0.44</v>
+        <v>0.1</v>
       </c>
       <c r="BV134" s="35">
         <f t="shared" si="59"/>
-        <v>0.44</v>
+        <v>0.1</v>
       </c>
       <c r="BW134" s="35">
         <f t="shared" si="60"/>
@@ -37295,11 +37304,11 @@
       </c>
       <c r="BX134" s="36">
         <f t="shared" si="61"/>
-        <v>45.913043478260867</v>
+        <v>10.434782608695652</v>
       </c>
       <c r="BY134" s="36">
         <f t="shared" si="62"/>
-        <v>45.913043478260867</v>
+        <v>10.434782608695652</v>
       </c>
       <c r="BZ134" s="36">
         <f t="shared" si="63"/>
@@ -37540,37 +37549,37 @@
         <v>253</v>
       </c>
       <c r="BR135" s="35">
-        <v>0.1</v>
+        <v>967.3</v>
       </c>
       <c r="BS135" s="35">
-        <v>0.1</v>
+        <v>1387</v>
       </c>
       <c r="BT135" s="35">
-        <v>0</v>
+        <v>419.7</v>
       </c>
       <c r="BU135" s="35">
         <f t="shared" si="58"/>
-        <v>1.8518518518518519E-3</v>
+        <v>17.912962962962965</v>
       </c>
       <c r="BV135" s="35">
         <f t="shared" si="59"/>
-        <v>1.8518518518518519E-3</v>
+        <v>25.685185185185187</v>
       </c>
       <c r="BW135" s="35">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>7.7722222222222221</v>
       </c>
       <c r="BX135" s="36">
         <f t="shared" si="61"/>
-        <v>2.7249812657537979E-3</v>
+        <v>26.358743783636491</v>
       </c>
       <c r="BY135" s="36">
         <f t="shared" si="62"/>
-        <v>2.7249812657537979E-3</v>
+        <v>37.795490156005179</v>
       </c>
       <c r="BZ135" s="36">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>11.43674637236869</v>
       </c>
       <c r="CA135" s="50">
         <v>34</v>
@@ -37807,37 +37816,37 @@
         <v>255</v>
       </c>
       <c r="BR136" s="35">
-        <v>967.3</v>
+        <v>418.86</v>
       </c>
       <c r="BS136" s="35">
-        <v>1387</v>
+        <v>575.05999999999995</v>
       </c>
       <c r="BT136" s="35">
-        <v>419.7</v>
+        <v>156.19999999999999</v>
       </c>
       <c r="BU136" s="35">
         <f t="shared" si="58"/>
-        <v>19.740816326530613</v>
+        <v>8.5481632653061226</v>
       </c>
       <c r="BV136" s="35">
         <f t="shared" si="59"/>
-        <v>28.306122448979593</v>
+        <v>11.735918367346938</v>
       </c>
       <c r="BW136" s="35">
         <f t="shared" si="60"/>
-        <v>8.5653061224489786</v>
+        <v>3.1877551020408159</v>
       </c>
       <c r="BX136" s="36">
         <f t="shared" si="61"/>
-        <v>56.068590749909433</v>
+        <v>24.278806907378328</v>
       </c>
       <c r="BY136" s="36">
         <f t="shared" si="62"/>
-        <v>80.396087429054461</v>
+        <v>33.33278589542325</v>
       </c>
       <c r="BZ136" s="36">
         <f t="shared" si="63"/>
-        <v>24.327496679145032</v>
+        <v>9.0539789880449213</v>
       </c>
       <c r="CA136" s="48">
         <v>31</v>
@@ -38074,37 +38083,37 @@
         <v>253</v>
       </c>
       <c r="BR137" s="35">
-        <v>418.86</v>
+        <v>861.06</v>
       </c>
       <c r="BS137" s="35">
-        <v>575.05999999999995</v>
+        <v>1199.6600000000001</v>
       </c>
       <c r="BT137" s="35">
-        <v>156.19999999999999</v>
+        <v>338.6</v>
       </c>
       <c r="BU137" s="35">
         <f t="shared" ref="BU137:BU200" si="86">BV137-BW137</f>
-        <v>9.5195454545454545</v>
+        <v>19.569545454545455</v>
       </c>
       <c r="BV137" s="35">
         <f t="shared" ref="BV137:BV200" si="87">BS137/$D137</f>
-        <v>13.069545454545453</v>
+        <v>27.265000000000001</v>
       </c>
       <c r="BW137" s="35">
         <f t="shared" ref="BW137:BW200" si="88">BT137/$D137</f>
-        <v>3.55</v>
+        <v>7.6954545454545462</v>
       </c>
       <c r="BX137" s="36">
         <f t="shared" ref="BX137:BX200" si="89">BY137-BZ137</f>
-        <v>14.234834324553947</v>
+        <v>29.26287170773152</v>
       </c>
       <c r="BY137" s="36">
         <f t="shared" ref="BY137:BY200" si="90">BS137*2400/$G137</f>
-        <v>19.543245539507218</v>
+        <v>40.770093457943922</v>
       </c>
       <c r="BZ137" s="36">
         <f t="shared" ref="BZ137:BZ200" si="91">BT137*2400/$G137</f>
-        <v>5.3084112149532707</v>
+        <v>11.507221750212404</v>
       </c>
       <c r="CA137" s="50">
         <v>26</v>
@@ -38341,37 +38350,37 @@
         <v>253</v>
       </c>
       <c r="BR138" s="35">
-        <v>861.06</v>
+        <v>629.29999999999995</v>
       </c>
       <c r="BS138" s="35">
-        <v>1199.6600000000001</v>
+        <v>838.9</v>
       </c>
       <c r="BT138" s="35">
-        <v>338.6</v>
+        <v>209.6</v>
       </c>
       <c r="BU138" s="35">
         <f t="shared" si="86"/>
-        <v>19.569545454545455</v>
+        <v>14.302272727272728</v>
       </c>
       <c r="BV138" s="35">
         <f t="shared" si="87"/>
-        <v>27.265000000000001</v>
+        <v>19.065909090909091</v>
       </c>
       <c r="BW138" s="35">
         <f t="shared" si="88"/>
-        <v>7.6954545454545462</v>
+        <v>4.7636363636363637</v>
       </c>
       <c r="BX138" s="36">
         <f t="shared" si="89"/>
-        <v>49.0772299800513</v>
+        <v>35.867768595041319</v>
       </c>
       <c r="BY138" s="36">
         <f t="shared" si="90"/>
-        <v>68.376175548589345</v>
+        <v>47.81419207751496</v>
       </c>
       <c r="BZ138" s="36">
         <f t="shared" si="91"/>
-        <v>19.298945568538045</v>
+        <v>11.946423482473639</v>
       </c>
       <c r="CA138" s="48">
         <v>26</v>
@@ -38608,37 +38617,37 @@
         <v>254</v>
       </c>
       <c r="BR139" s="35">
-        <v>629.29999999999995</v>
+        <v>371</v>
       </c>
       <c r="BS139" s="35">
-        <v>838.9</v>
+        <v>502</v>
       </c>
       <c r="BT139" s="35">
-        <v>209.6</v>
+        <v>131</v>
       </c>
       <c r="BU139" s="35">
         <f t="shared" si="86"/>
-        <v>31.465</v>
+        <v>18.55</v>
       </c>
       <c r="BV139" s="35">
         <f t="shared" si="87"/>
-        <v>41.945</v>
+        <v>25.1</v>
       </c>
       <c r="BW139" s="35">
         <f t="shared" si="88"/>
-        <v>10.48</v>
+        <v>6.55</v>
       </c>
       <c r="BX139" s="36">
         <f t="shared" si="89"/>
-        <v>68.775956284152997</v>
+        <v>40.546448087431699</v>
       </c>
       <c r="BY139" s="36">
         <f t="shared" si="90"/>
-        <v>91.683060109289613</v>
+        <v>54.863387978142079</v>
       </c>
       <c r="BZ139" s="36">
         <f t="shared" si="91"/>
-        <v>22.907103825136613</v>
+        <v>14.316939890710383</v>
       </c>
       <c r="CA139" s="48">
         <v>13</v>
@@ -38875,37 +38884,37 @@
         <v>253</v>
       </c>
       <c r="BR140" s="35">
-        <v>371</v>
+        <v>1.99</v>
       </c>
       <c r="BS140" s="35">
-        <v>502</v>
+        <v>7.59</v>
       </c>
       <c r="BT140" s="35">
-        <v>131</v>
+        <v>5.6</v>
       </c>
       <c r="BU140" s="35">
         <f t="shared" si="86"/>
-        <v>92.75</v>
+        <v>0.49750000000000005</v>
       </c>
       <c r="BV140" s="35">
         <f t="shared" si="87"/>
-        <v>125.5</v>
+        <v>1.8975</v>
       </c>
       <c r="BW140" s="35">
         <f t="shared" si="88"/>
-        <v>32.75</v>
+        <v>1.4</v>
       </c>
       <c r="BX140" s="36">
         <f t="shared" si="89"/>
-        <v>2318.75</v>
+        <v>12.4375</v>
       </c>
       <c r="BY140" s="36">
         <f t="shared" si="90"/>
-        <v>3137.5</v>
+        <v>47.4375</v>
       </c>
       <c r="BZ140" s="36">
         <f t="shared" si="91"/>
-        <v>818.75</v>
+        <v>35</v>
       </c>
       <c r="CA140" s="50">
         <v>3</v>
@@ -39142,37 +39151,37 @@
         <v>254</v>
       </c>
       <c r="BR141" s="35">
-        <v>1.99</v>
+        <v>270.64999999999998</v>
       </c>
       <c r="BS141" s="35">
-        <v>7.59</v>
+        <v>342.05</v>
       </c>
       <c r="BT141" s="35">
-        <v>5.6</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="BU141" s="35">
         <f t="shared" si="86"/>
-        <v>9.4761904761904769E-2</v>
+        <v>12.888095238095238</v>
       </c>
       <c r="BV141" s="35">
         <f t="shared" si="87"/>
-        <v>0.36142857142857143</v>
+        <v>16.288095238095238</v>
       </c>
       <c r="BW141" s="35">
         <f t="shared" si="88"/>
-        <v>0.26666666666666666</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="BX141" s="36">
         <f t="shared" si="89"/>
-        <v>0.21156146179401991</v>
+        <v>28.773421926910295</v>
       </c>
       <c r="BY141" s="36">
         <f t="shared" si="90"/>
-        <v>0.80691029900332223</v>
+        <v>36.364119601328902</v>
       </c>
       <c r="BZ141" s="36">
         <f t="shared" si="91"/>
-        <v>0.59534883720930232</v>
+        <v>7.590697674418605</v>
       </c>
       <c r="CA141" s="50">
         <v>15</v>
@@ -39409,37 +39418,37 @@
         <v>253</v>
       </c>
       <c r="BR142" s="35">
-        <v>270.64999999999998</v>
+        <v>843.17</v>
       </c>
       <c r="BS142" s="35">
-        <v>342.05</v>
+        <v>1026.47</v>
       </c>
       <c r="BT142" s="35">
-        <v>71.400000000000006</v>
+        <v>183.3</v>
       </c>
       <c r="BU142" s="35">
         <f t="shared" si="86"/>
-        <v>5.7585106382978726</v>
+        <v>17.939787234042555</v>
       </c>
       <c r="BV142" s="35">
         <f t="shared" si="87"/>
-        <v>7.2776595744680854</v>
+        <v>21.839787234042554</v>
       </c>
       <c r="BW142" s="35">
         <f t="shared" si="88"/>
-        <v>1.5191489361702128</v>
+        <v>3.9000000000000004</v>
       </c>
       <c r="BX142" s="36">
         <f t="shared" si="89"/>
-        <v>11.136523393968487</v>
+        <v>34.694189654876816</v>
       </c>
       <c r="BY142" s="36">
         <f t="shared" si="90"/>
-        <v>14.074442368028528</v>
+        <v>42.236494247946922</v>
       </c>
       <c r="BZ142" s="36">
         <f t="shared" si="91"/>
-        <v>2.9379189740600409</v>
+        <v>7.5423045930701047</v>
       </c>
       <c r="CA142" s="50">
         <v>28</v>
@@ -39676,37 +39685,37 @@
         <v>253</v>
       </c>
       <c r="BR143" s="35">
-        <v>843.17</v>
+        <v>262.52</v>
       </c>
       <c r="BS143" s="35">
-        <v>1026.47</v>
+        <v>347.22</v>
       </c>
       <c r="BT143" s="35">
-        <v>183.3</v>
+        <v>84.7</v>
       </c>
       <c r="BU143" s="35">
         <f t="shared" si="86"/>
-        <v>27.199032258064513</v>
+        <v>8.4683870967741939</v>
       </c>
       <c r="BV143" s="35">
         <f t="shared" si="87"/>
-        <v>33.111935483870965</v>
+        <v>11.200645161290323</v>
       </c>
       <c r="BW143" s="35">
         <f t="shared" si="88"/>
-        <v>5.9129032258064518</v>
+        <v>2.7322580645161292</v>
       </c>
       <c r="BX143" s="36">
         <f t="shared" si="89"/>
-        <v>117.61743679163034</v>
+        <v>36.620052310374895</v>
       </c>
       <c r="BY143" s="36">
         <f t="shared" si="90"/>
-        <v>143.18674803836095</v>
+        <v>48.435222319093292</v>
       </c>
       <c r="BZ143" s="36">
         <f t="shared" si="91"/>
-        <v>25.569311246730603</v>
+        <v>11.815170008718395</v>
       </c>
       <c r="CA143" s="48">
         <v>18</v>
@@ -39943,37 +39952,37 @@
         <v>254</v>
       </c>
       <c r="BR144" s="35">
-        <v>262.52</v>
+        <v>791.75</v>
       </c>
       <c r="BS144" s="35">
-        <v>347.22</v>
+        <v>1107.05</v>
       </c>
       <c r="BT144" s="35">
-        <v>84.7</v>
+        <v>315.3</v>
       </c>
       <c r="BU144" s="35">
         <f t="shared" si="86"/>
-        <v>6.5630000000000006</v>
+        <v>19.793749999999999</v>
       </c>
       <c r="BV144" s="35">
         <f t="shared" si="87"/>
-        <v>8.6805000000000003</v>
+        <v>27.67625</v>
       </c>
       <c r="BW144" s="35">
         <f t="shared" si="88"/>
-        <v>2.1175000000000002</v>
+        <v>7.8825000000000003</v>
       </c>
       <c r="BX144" s="36">
         <f t="shared" si="89"/>
-        <v>9.5810218978102206</v>
+        <v>28.895985401459853</v>
       </c>
       <c r="BY144" s="36">
         <f t="shared" si="90"/>
-        <v>12.672262773722629</v>
+        <v>40.403284671532845</v>
       </c>
       <c r="BZ144" s="36">
         <f t="shared" si="91"/>
-        <v>3.0912408759124088</v>
+        <v>11.507299270072993</v>
       </c>
       <c r="CA144" s="50">
         <v>19</v>
@@ -40210,37 +40219,37 @@
         <v>253</v>
       </c>
       <c r="BR145" s="35">
-        <v>791.75</v>
+        <v>1027.77</v>
       </c>
       <c r="BS145" s="35">
-        <v>1107.05</v>
+        <v>1320.37</v>
       </c>
       <c r="BT145" s="35">
-        <v>315.3</v>
+        <v>292.60000000000002</v>
       </c>
       <c r="BU145" s="35">
         <f t="shared" si="86"/>
-        <v>16.158163265306122</v>
+        <v>20.974897959183672</v>
       </c>
       <c r="BV145" s="35">
         <f t="shared" si="87"/>
-        <v>22.592857142857142</v>
+        <v>26.946326530612243</v>
       </c>
       <c r="BW145" s="35">
         <f t="shared" si="88"/>
-        <v>6.4346938775510205</v>
+        <v>5.9714285714285715</v>
       </c>
       <c r="BX145" s="36">
         <f t="shared" si="89"/>
-        <v>27.175607453913592</v>
+        <v>35.276632867582904</v>
       </c>
       <c r="BY145" s="36">
         <f t="shared" si="90"/>
-        <v>37.997797577335071</v>
+        <v>45.319680219670204</v>
       </c>
       <c r="BZ145" s="36">
         <f t="shared" si="91"/>
-        <v>10.822190123421478</v>
+        <v>10.043047352087296</v>
       </c>
       <c r="CA145" s="48">
         <v>20</v>
@@ -40477,37 +40486,37 @@
         <v>254</v>
       </c>
       <c r="BR146" s="35">
-        <v>1027.77</v>
+        <v>472.77</v>
       </c>
       <c r="BS146" s="35">
-        <v>1320.37</v>
+        <v>669.37</v>
       </c>
       <c r="BT146" s="35">
-        <v>292.60000000000002</v>
+        <v>196.6</v>
       </c>
       <c r="BU146" s="35">
         <f t="shared" si="86"/>
-        <v>22.839333333333329</v>
+        <v>10.506</v>
       </c>
       <c r="BV146" s="35">
         <f t="shared" si="87"/>
-        <v>29.341555555555551</v>
+        <v>14.874888888888888</v>
       </c>
       <c r="BW146" s="35">
         <f t="shared" si="88"/>
-        <v>6.5022222222222226</v>
+        <v>4.3688888888888888</v>
       </c>
       <c r="BX146" s="36">
         <f t="shared" si="89"/>
-        <v>52.353772683858629</v>
+        <v>24.082521489971349</v>
       </c>
       <c r="BY146" s="36">
         <f t="shared" si="90"/>
-        <v>67.258580070041376</v>
+        <v>34.097166507481695</v>
       </c>
       <c r="BZ146" s="36">
         <f t="shared" si="91"/>
-        <v>14.904807386182744</v>
+        <v>10.014645017510347</v>
       </c>
       <c r="CA146" s="50">
         <v>18</v>
@@ -40744,37 +40753,37 @@
         <v>255</v>
       </c>
       <c r="BR147" s="35">
-        <v>472.77</v>
+        <v>1.23</v>
       </c>
       <c r="BS147" s="35">
-        <v>669.37</v>
+        <v>2.13</v>
       </c>
       <c r="BT147" s="35">
-        <v>196.6</v>
+        <v>0.9</v>
       </c>
       <c r="BU147" s="35">
         <f t="shared" si="86"/>
-        <v>236.38499999999999</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="BV147" s="35">
         <f t="shared" si="87"/>
-        <v>334.685</v>
+        <v>1.0649999999999999</v>
       </c>
       <c r="BW147" s="35">
         <f t="shared" si="88"/>
-        <v>98.3</v>
+        <v>0.45</v>
       </c>
       <c r="BX147" s="36">
         <f t="shared" si="89"/>
-        <v>4171.5</v>
+        <v>10.852941176470587</v>
       </c>
       <c r="BY147" s="36">
         <f t="shared" si="90"/>
-        <v>5906.2058823529414</v>
+        <v>18.794117647058822</v>
       </c>
       <c r="BZ147" s="36">
         <f t="shared" si="91"/>
-        <v>1734.7058823529412</v>
+        <v>7.9411764705882355</v>
       </c>
       <c r="CA147" s="48">
         <v>1</v>
@@ -41011,37 +41020,37 @@
         <v>253</v>
       </c>
       <c r="BR148" s="35">
-        <v>1.23</v>
+        <v>469.11</v>
       </c>
       <c r="BS148" s="35">
-        <v>2.13</v>
+        <v>707.31</v>
       </c>
       <c r="BT148" s="35">
-        <v>0.9</v>
+        <v>238.2</v>
       </c>
       <c r="BU148" s="35">
         <f t="shared" si="86"/>
-        <v>4.9199999999999994E-2</v>
+        <v>18.764399999999998</v>
       </c>
       <c r="BV148" s="35">
         <f t="shared" si="87"/>
-        <v>8.5199999999999998E-2</v>
+        <v>28.292399999999997</v>
       </c>
       <c r="BW148" s="35">
         <f t="shared" si="88"/>
-        <v>3.6000000000000004E-2</v>
+        <v>9.5279999999999987</v>
       </c>
       <c r="BX148" s="36">
         <f t="shared" si="89"/>
-        <v>8.1546961325966866E-2</v>
+        <v>31.101215469613255</v>
       </c>
       <c r="BY148" s="36">
         <f t="shared" si="90"/>
-        <v>0.14121546961325968</v>
+        <v>46.893480662983421</v>
       </c>
       <c r="BZ148" s="36">
         <f t="shared" si="91"/>
-        <v>5.9668508287292817E-2</v>
+        <v>15.792265193370167</v>
       </c>
       <c r="CA148" s="50">
         <v>10</v>
@@ -41278,37 +41287,37 @@
         <v>255</v>
       </c>
       <c r="BR149" s="35">
-        <v>469.11</v>
+        <v>594.35</v>
       </c>
       <c r="BS149" s="35">
-        <v>707.31</v>
+        <v>867.45</v>
       </c>
       <c r="BT149" s="35">
-        <v>238.2</v>
+        <v>273.10000000000002</v>
       </c>
       <c r="BU149" s="35">
         <f t="shared" si="86"/>
-        <v>16.176206896551722</v>
+        <v>20.494827586206895</v>
       </c>
       <c r="BV149" s="35">
         <f t="shared" si="87"/>
-        <v>24.389999999999997</v>
+        <v>29.912068965517243</v>
       </c>
       <c r="BW149" s="35">
         <f t="shared" si="88"/>
-        <v>8.2137931034482747</v>
+        <v>9.4172413793103456</v>
       </c>
       <c r="BX149" s="36">
         <f t="shared" si="89"/>
-        <v>31.384718311822255</v>
+        <v>39.763610514871914</v>
       </c>
       <c r="BY149" s="36">
         <f t="shared" si="90"/>
-        <v>47.320937752627316</v>
+        <v>58.034733643687453</v>
       </c>
       <c r="BZ149" s="36">
         <f t="shared" si="91"/>
-        <v>15.936219440805063</v>
+        <v>18.271123128815542</v>
       </c>
       <c r="CA149" s="48">
         <v>14</v>
@@ -41545,37 +41554,37 @@
         <v>254</v>
       </c>
       <c r="BR150" s="35">
-        <v>594.35</v>
+        <v>158.66999999999999</v>
       </c>
       <c r="BS150" s="35">
-        <v>867.45</v>
+        <v>218.87</v>
       </c>
       <c r="BT150" s="35">
-        <v>273.10000000000002</v>
+        <v>60.2</v>
       </c>
       <c r="BU150" s="35">
         <f t="shared" si="86"/>
-        <v>49.529166666666669</v>
+        <v>13.2225</v>
       </c>
       <c r="BV150" s="35">
         <f t="shared" si="87"/>
-        <v>72.287500000000009</v>
+        <v>18.239166666666666</v>
       </c>
       <c r="BW150" s="35">
         <f t="shared" si="88"/>
-        <v>22.758333333333336</v>
+        <v>5.0166666666666666</v>
       </c>
       <c r="BX150" s="36">
         <f t="shared" si="89"/>
-        <v>142.01911589008361</v>
+        <v>37.913978494623656</v>
       </c>
       <c r="BY150" s="36">
         <f t="shared" si="90"/>
-        <v>207.27598566308242</v>
+        <v>52.298685782556753</v>
       </c>
       <c r="BZ150" s="36">
         <f t="shared" si="91"/>
-        <v>65.256869772998812</v>
+        <v>14.384707287933095</v>
       </c>
       <c r="CA150" s="48">
         <v>6</v>
@@ -41812,37 +41821,37 @@
         <v>253</v>
       </c>
       <c r="BR151" s="35">
-        <v>158.66999999999999</v>
+        <v>1158.8599999999999</v>
       </c>
       <c r="BS151" s="35">
-        <v>218.87</v>
+        <v>1448.66</v>
       </c>
       <c r="BT151" s="35">
-        <v>60.2</v>
+        <v>289.8</v>
       </c>
       <c r="BU151" s="35">
         <f t="shared" si="86"/>
-        <v>2.9937735849056608</v>
+        <v>21.865283018867927</v>
       </c>
       <c r="BV151" s="35">
         <f t="shared" si="87"/>
-        <v>4.1296226415094344</v>
+        <v>27.333207547169813</v>
       </c>
       <c r="BW151" s="35">
         <f t="shared" si="88"/>
-        <v>1.1358490566037736</v>
+        <v>5.4679245283018867</v>
       </c>
       <c r="BX151" s="36">
         <f t="shared" si="89"/>
-        <v>5.2676368062856191</v>
+        <v>38.472638742876114</v>
       </c>
       <c r="BY151" s="36">
         <f t="shared" si="90"/>
-        <v>7.2661981962042823</v>
+        <v>48.093620317600838</v>
       </c>
       <c r="BZ151" s="36">
         <f t="shared" si="91"/>
-        <v>1.9985613899186632</v>
+        <v>9.6209815747247269</v>
       </c>
       <c r="CA151" s="48">
         <v>21</v>
@@ -42079,37 +42088,37 @@
         <v>254</v>
       </c>
       <c r="BR152" s="35">
-        <v>1158.8599999999999</v>
+        <v>68.72</v>
       </c>
       <c r="BS152" s="35">
-        <v>1448.66</v>
+        <v>85.62</v>
       </c>
       <c r="BT152" s="35">
-        <v>289.8</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="BU152" s="35">
         <f t="shared" si="86"/>
-        <v>193.14333333333335</v>
+        <v>11.453333333333335</v>
       </c>
       <c r="BV152" s="35">
         <f t="shared" si="87"/>
-        <v>241.44333333333336</v>
+        <v>14.270000000000001</v>
       </c>
       <c r="BW152" s="35">
         <f t="shared" si="88"/>
-        <v>48.300000000000004</v>
+        <v>2.8166666666666664</v>
       </c>
       <c r="BX152" s="36">
         <f t="shared" si="89"/>
-        <v>561.87151515151515</v>
+        <v>33.31878787878788</v>
       </c>
       <c r="BY152" s="36">
         <f t="shared" si="90"/>
-        <v>702.38060606060606</v>
+        <v>41.512727272727275</v>
       </c>
       <c r="BZ152" s="36">
         <f t="shared" si="91"/>
-        <v>140.5090909090909</v>
+        <v>8.1939393939393934</v>
       </c>
       <c r="CA152" s="48">
         <v>0</v>
@@ -42346,37 +42355,37 @@
         <v>253</v>
       </c>
       <c r="BR153" s="35">
-        <v>68.72</v>
+        <v>3.36</v>
       </c>
       <c r="BS153" s="35">
-        <v>85.62</v>
+        <v>4.26</v>
       </c>
       <c r="BT153" s="35">
-        <v>16.899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="BU153" s="35">
         <f t="shared" si="86"/>
-        <v>34.36</v>
+        <v>1.68</v>
       </c>
       <c r="BV153" s="35">
         <f t="shared" si="87"/>
-        <v>42.81</v>
+        <v>2.13</v>
       </c>
       <c r="BW153" s="35">
         <f t="shared" si="88"/>
-        <v>8.4499999999999993</v>
+        <v>0.45</v>
       </c>
       <c r="BX153" s="36">
         <f t="shared" si="89"/>
-        <v>303.1764705882353</v>
+        <v>14.823529411764705</v>
       </c>
       <c r="BY153" s="36">
         <f t="shared" si="90"/>
-        <v>377.73529411764707</v>
+        <v>18.794117647058822</v>
       </c>
       <c r="BZ153" s="36">
         <f t="shared" si="91"/>
-        <v>74.558823529411768</v>
+        <v>3.9705882352941178</v>
       </c>
       <c r="CA153" s="50">
         <v>0</v>
@@ -42613,37 +42622,37 @@
         <v>253</v>
       </c>
       <c r="BR154" s="35">
-        <v>3.36</v>
+        <v>288.47000000000003</v>
       </c>
       <c r="BS154" s="35">
-        <v>4.26</v>
+        <v>389.77</v>
       </c>
       <c r="BT154" s="35">
-        <v>0.9</v>
+        <v>101.3</v>
       </c>
       <c r="BU154" s="35">
         <f t="shared" si="86"/>
-        <v>0.10181818181818181</v>
+        <v>8.7415151515151504</v>
       </c>
       <c r="BV154" s="35">
         <f t="shared" si="87"/>
-        <v>0.12909090909090909</v>
+        <v>11.811212121212121</v>
       </c>
       <c r="BW154" s="35">
         <f t="shared" si="88"/>
-        <v>2.7272727272727275E-2</v>
+        <v>3.0696969696969698</v>
       </c>
       <c r="BX154" s="36">
         <f t="shared" si="89"/>
-        <v>0.25114453891432309</v>
+        <v>21.561805101373444</v>
       </c>
       <c r="BY154" s="36">
         <f t="shared" si="90"/>
-        <v>0.3184153975520882</v>
+        <v>29.133513968046341</v>
       </c>
       <c r="BZ154" s="36">
         <f t="shared" si="91"/>
-        <v>6.7270858637765107E-2</v>
+        <v>7.5717088666728953</v>
       </c>
       <c r="CA154" s="48">
         <v>13</v>
@@ -42880,37 +42889,37 @@
         <v>253</v>
       </c>
       <c r="BR155" s="35">
-        <v>288.47000000000003</v>
+        <v>293.89999999999998</v>
       </c>
       <c r="BS155" s="35">
-        <v>389.77</v>
+        <v>429.3</v>
       </c>
       <c r="BT155" s="35">
-        <v>101.3</v>
+        <v>135.4</v>
       </c>
       <c r="BU155" s="35">
         <f t="shared" si="86"/>
-        <v>8.4844117647058823</v>
+        <v>8.6441176470588239</v>
       </c>
       <c r="BV155" s="35">
         <f t="shared" si="87"/>
-        <v>11.463823529411764</v>
+        <v>12.626470588235295</v>
       </c>
       <c r="BW155" s="35">
         <f t="shared" si="88"/>
-        <v>2.9794117647058824</v>
+        <v>3.9823529411764707</v>
       </c>
       <c r="BX155" s="36">
         <f t="shared" si="89"/>
-        <v>28.047642197374813</v>
+        <v>28.575595527467186</v>
       </c>
       <c r="BY155" s="36">
         <f t="shared" si="90"/>
-        <v>37.896937287311616</v>
+        <v>41.74039863879436</v>
       </c>
       <c r="BZ155" s="36">
         <f t="shared" si="91"/>
-        <v>9.8492950899368008</v>
+        <v>13.164803111327176</v>
       </c>
       <c r="CA155" s="48">
         <v>16</v>
@@ -43147,37 +43156,37 @@
         <v>255</v>
       </c>
       <c r="BR156" s="35">
-        <v>293.89999999999998</v>
+        <v>40.46</v>
       </c>
       <c r="BS156" s="35">
-        <v>429.3</v>
+        <v>56.86</v>
       </c>
       <c r="BT156" s="35">
-        <v>135.4</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="BU156" s="35">
         <f t="shared" si="86"/>
-        <v>41.98571428571428</v>
+        <v>5.78</v>
       </c>
       <c r="BV156" s="35">
         <f t="shared" si="87"/>
-        <v>61.328571428571429</v>
+        <v>8.1228571428571428</v>
       </c>
       <c r="BW156" s="35">
         <f t="shared" si="88"/>
-        <v>19.342857142857145</v>
+        <v>2.3428571428571425</v>
       </c>
       <c r="BX156" s="36">
         <f t="shared" si="89"/>
-        <v>179.61802902979372</v>
+        <v>24.727272727272727</v>
       </c>
       <c r="BY156" s="36">
         <f t="shared" si="90"/>
-        <v>262.36822001527884</v>
+        <v>34.750190985485105</v>
       </c>
       <c r="BZ156" s="36">
         <f t="shared" si="91"/>
-        <v>82.750190985485105</v>
+        <v>10.022918258212377</v>
       </c>
       <c r="CA156" s="50">
         <v>2</v>
@@ -43414,37 +43423,37 @@
         <v>255</v>
       </c>
       <c r="BR157" s="35">
-        <v>40.46</v>
+        <v>128.01</v>
       </c>
       <c r="BS157" s="35">
-        <v>56.86</v>
+        <v>174.31</v>
       </c>
       <c r="BT157" s="35">
-        <v>16.399999999999999</v>
+        <v>46.3</v>
       </c>
       <c r="BU157" s="35">
         <f t="shared" si="86"/>
-        <v>1.5561538461538462</v>
+        <v>4.923461538461539</v>
       </c>
       <c r="BV157" s="35">
         <f t="shared" si="87"/>
-        <v>2.186923076923077</v>
+        <v>6.7042307692307697</v>
       </c>
       <c r="BW157" s="35">
         <f t="shared" si="88"/>
-        <v>0.63076923076923075</v>
+        <v>1.7807692307692307</v>
       </c>
       <c r="BX157" s="36">
         <f t="shared" si="89"/>
-        <v>8.8292416803055112</v>
+        <v>27.934533551554829</v>
       </c>
       <c r="BY157" s="36">
         <f t="shared" si="90"/>
-        <v>12.408074195308238</v>
+        <v>38.03818876159302</v>
       </c>
       <c r="BZ157" s="36">
         <f t="shared" si="91"/>
-        <v>3.5788325150027278</v>
+        <v>10.103655210038189</v>
       </c>
       <c r="CA157" s="50">
         <v>10</v>
@@ -43681,37 +43690,37 @@
         <v>253</v>
       </c>
       <c r="BR158" s="35">
-        <v>128.01</v>
+        <v>1.25</v>
       </c>
       <c r="BS158" s="35">
-        <v>174.31</v>
+        <v>15.55</v>
       </c>
       <c r="BT158" s="35">
-        <v>46.3</v>
+        <v>14.3</v>
       </c>
       <c r="BU158" s="35">
         <f t="shared" si="86"/>
-        <v>32.002499999999998</v>
+        <v>0.3125</v>
       </c>
       <c r="BV158" s="35">
         <f t="shared" si="87"/>
-        <v>43.577500000000001</v>
+        <v>3.8875000000000002</v>
       </c>
       <c r="BW158" s="35">
         <f t="shared" si="88"/>
-        <v>11.574999999999999</v>
+        <v>3.5750000000000002</v>
       </c>
       <c r="BX158" s="36">
         <f t="shared" si="89"/>
-        <v>181.57446808510639</v>
+        <v>1.7730496453900706</v>
       </c>
       <c r="BY158" s="36">
         <f t="shared" si="90"/>
-        <v>247.24822695035462</v>
+        <v>22.056737588652481</v>
       </c>
       <c r="BZ158" s="36">
         <f t="shared" si="91"/>
-        <v>65.673758865248232</v>
+        <v>20.283687943262411</v>
       </c>
       <c r="CA158" s="48">
         <v>0</v>
@@ -43948,37 +43957,37 @@
         <v>253</v>
       </c>
       <c r="BR159" s="35">
-        <v>1.25</v>
+        <v>38.840000000000003</v>
       </c>
       <c r="BS159" s="35">
-        <v>15.55</v>
+        <v>67.34</v>
       </c>
       <c r="BT159" s="35">
-        <v>14.3</v>
+        <v>28.5</v>
       </c>
       <c r="BU159" s="35">
         <f t="shared" si="86"/>
-        <v>9.6153846153846034E-2</v>
+        <v>2.9876923076923081</v>
       </c>
       <c r="BV159" s="35">
         <f t="shared" si="87"/>
-        <v>1.1961538461538461</v>
+        <v>5.1800000000000006</v>
       </c>
       <c r="BW159" s="35">
         <f t="shared" si="88"/>
-        <v>1.1000000000000001</v>
+        <v>2.1923076923076925</v>
       </c>
       <c r="BX159" s="36">
         <f t="shared" si="89"/>
-        <v>0.47483380816714149</v>
+        <v>14.754036087369421</v>
       </c>
       <c r="BY159" s="36">
         <f t="shared" si="90"/>
-        <v>5.9069325735992404</v>
+        <v>25.580246913580247</v>
       </c>
       <c r="BZ159" s="36">
         <f t="shared" si="91"/>
-        <v>5.4320987654320989</v>
+        <v>10.826210826210826</v>
       </c>
       <c r="CA159" s="50">
         <v>5</v>
@@ -44215,37 +44224,37 @@
         <v>255</v>
       </c>
       <c r="BR160" s="35">
-        <v>38.840000000000003</v>
+        <v>1291.54</v>
       </c>
       <c r="BS160" s="35">
-        <v>67.34</v>
+        <v>1810.64</v>
       </c>
       <c r="BT160" s="35">
-        <v>28.5</v>
+        <v>519.1</v>
       </c>
       <c r="BU160" s="35">
         <f t="shared" si="86"/>
-        <v>0.73283018867924543</v>
+        <v>24.368679245283019</v>
       </c>
       <c r="BV160" s="35">
         <f t="shared" si="87"/>
-        <v>1.2705660377358492</v>
+        <v>34.163018867924528</v>
       </c>
       <c r="BW160" s="35">
         <f t="shared" si="88"/>
-        <v>0.53773584905660377</v>
+        <v>9.7943396226415107</v>
       </c>
       <c r="BX160" s="36">
         <f t="shared" si="89"/>
-        <v>0.96108877203835463</v>
+        <v>31.958923600371172</v>
       </c>
       <c r="BY160" s="36">
         <f t="shared" si="90"/>
-        <v>1.6663161150634087</v>
+        <v>44.803959171048561</v>
       </c>
       <c r="BZ160" s="36">
         <f t="shared" si="91"/>
-        <v>0.70522734302505408</v>
+        <v>12.845035570677389</v>
       </c>
       <c r="CA160" s="50">
         <v>22</v>
@@ -44482,37 +44491,37 @@
         <v>255</v>
       </c>
       <c r="BR161" s="35">
-        <v>1291.54</v>
+        <v>7.2</v>
       </c>
       <c r="BS161" s="35">
-        <v>1810.64</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="BT161" s="35">
-        <v>519.1</v>
+        <v>2.5</v>
       </c>
       <c r="BU161" s="35">
         <f t="shared" si="86"/>
-        <v>430.51333333333343</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="BV161" s="35">
         <f t="shared" si="87"/>
-        <v>603.54666666666674</v>
+        <v>3.2333333333333329</v>
       </c>
       <c r="BW161" s="35">
         <f t="shared" si="88"/>
-        <v>173.03333333333333</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="BX161" s="36">
         <f t="shared" si="89"/>
-        <v>5870.636363636364</v>
+        <v>32.727272727272734</v>
       </c>
       <c r="BY161" s="36">
         <f t="shared" si="90"/>
-        <v>8230.181818181818</v>
+        <v>44.090909090909093</v>
       </c>
       <c r="BZ161" s="36">
         <f t="shared" si="91"/>
-        <v>2359.5454545454545</v>
+        <v>11.363636363636363</v>
       </c>
       <c r="CA161" s="50">
         <v>0</v>
@@ -44749,37 +44758,37 @@
         <v>254</v>
       </c>
       <c r="BR162" s="35">
-        <v>7.2</v>
+        <v>151.38999999999999</v>
       </c>
       <c r="BS162" s="35">
-        <v>9.6999999999999993</v>
+        <v>253.69</v>
       </c>
       <c r="BT162" s="35">
-        <v>2.5</v>
+        <v>102.3</v>
       </c>
       <c r="BU162" s="35">
         <f t="shared" si="86"/>
-        <v>0.27692307692307688</v>
+        <v>5.8226923076923089</v>
       </c>
       <c r="BV162" s="35">
         <f t="shared" si="87"/>
-        <v>0.37307692307692303</v>
+        <v>9.7573076923076929</v>
       </c>
       <c r="BW162" s="35">
         <f t="shared" si="88"/>
-        <v>9.6153846153846159E-2</v>
+        <v>3.9346153846153844</v>
       </c>
       <c r="BX162" s="36">
         <f t="shared" si="89"/>
-        <v>0.97024143739472213</v>
+        <v>20.400673778775968</v>
       </c>
       <c r="BY162" s="36">
         <f t="shared" si="90"/>
-        <v>1.3071308253790006</v>
+        <v>34.186187535092643</v>
       </c>
       <c r="BZ162" s="36">
         <f t="shared" si="91"/>
-        <v>0.33688938798427848</v>
+        <v>13.785513756316677</v>
       </c>
       <c r="CA162" s="50">
         <v>11</v>
@@ -45016,37 +45025,37 @@
         <v>255</v>
       </c>
       <c r="BR163" s="35">
-        <v>151.38999999999999</v>
+        <v>48.28</v>
       </c>
       <c r="BS163" s="35">
-        <v>253.69</v>
+        <v>64.58</v>
       </c>
       <c r="BT163" s="35">
-        <v>102.3</v>
+        <v>16.3</v>
       </c>
       <c r="BU163" s="35">
         <f t="shared" si="86"/>
-        <v>18.923749999999998</v>
+        <v>6.0350000000000001</v>
       </c>
       <c r="BV163" s="35">
         <f t="shared" si="87"/>
-        <v>31.71125</v>
+        <v>8.0724999999999998</v>
       </c>
       <c r="BW163" s="35">
         <f t="shared" si="88"/>
-        <v>12.7875</v>
+        <v>2.0375000000000001</v>
       </c>
       <c r="BX163" s="36">
         <f t="shared" si="89"/>
-        <v>91.382293762575472</v>
+        <v>29.142857142857142</v>
       </c>
       <c r="BY163" s="36">
         <f t="shared" si="90"/>
-        <v>153.13279678068412</v>
+        <v>38.981891348088531</v>
       </c>
       <c r="BZ163" s="36">
         <f t="shared" si="91"/>
-        <v>61.750503018108652</v>
+        <v>9.8390342052313891</v>
       </c>
       <c r="CA163" s="48">
         <v>2</v>
@@ -45283,37 +45292,37 @@
         <v>253</v>
       </c>
       <c r="BR164" s="35">
-        <v>48.28</v>
+        <v>284.41000000000003</v>
       </c>
       <c r="BS164" s="35">
-        <v>64.58</v>
+        <v>427.21</v>
       </c>
       <c r="BT164" s="35">
-        <v>16.3</v>
+        <v>142.80000000000001</v>
       </c>
       <c r="BU164" s="35">
         <f t="shared" si="86"/>
-        <v>1.42</v>
+        <v>8.3649999999999984</v>
       </c>
       <c r="BV164" s="35">
         <f t="shared" si="87"/>
-        <v>1.8994117647058824</v>
+        <v>12.565</v>
       </c>
       <c r="BW164" s="35">
         <f t="shared" si="88"/>
-        <v>0.47941176470588237</v>
+        <v>4.2</v>
       </c>
       <c r="BX164" s="36">
         <f t="shared" si="89"/>
-        <v>3.981308411214953</v>
+        <v>23.453271028037385</v>
       </c>
       <c r="BY164" s="36">
         <f t="shared" si="90"/>
-        <v>5.3254535459043426</v>
+        <v>35.228971962616825</v>
       </c>
       <c r="BZ164" s="36">
         <f t="shared" si="91"/>
-        <v>1.3441451346893898</v>
+        <v>11.77570093457944</v>
       </c>
       <c r="CA164" s="48">
         <v>14</v>
@@ -45550,37 +45559,37 @@
         <v>255</v>
       </c>
       <c r="BR165" s="35">
-        <v>284.41000000000003</v>
+        <v>713.65</v>
       </c>
       <c r="BS165" s="35">
-        <v>427.21</v>
+        <v>933.45</v>
       </c>
       <c r="BT165" s="35">
-        <v>142.80000000000001</v>
+        <v>219.8</v>
       </c>
       <c r="BU165" s="35">
         <f t="shared" si="86"/>
-        <v>5.5766666666666662</v>
+        <v>13.993137254901963</v>
       </c>
       <c r="BV165" s="35">
         <f t="shared" si="87"/>
-        <v>8.3766666666666669</v>
+        <v>18.30294117647059</v>
       </c>
       <c r="BW165" s="35">
         <f t="shared" si="88"/>
-        <v>2.8000000000000003</v>
+        <v>4.3098039215686272</v>
       </c>
       <c r="BX165" s="36">
         <f t="shared" si="89"/>
-        <v>9.3594405594405607</v>
+        <v>23.484985602632662</v>
       </c>
       <c r="BY165" s="36">
         <f t="shared" si="90"/>
-        <v>14.058741258741259</v>
+        <v>30.718222953517071</v>
       </c>
       <c r="BZ165" s="36">
         <f t="shared" si="91"/>
-        <v>4.6993006993006992</v>
+        <v>7.2332373508844094</v>
       </c>
       <c r="CA165" s="48">
         <v>19</v>
@@ -45817,37 +45826,37 @@
         <v>253</v>
       </c>
       <c r="BR166" s="35">
-        <v>713.65</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="BS166" s="35">
-        <v>933.45</v>
+        <v>24.66</v>
       </c>
       <c r="BT166" s="35">
-        <v>219.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="BU166" s="35">
         <f t="shared" si="86"/>
-        <v>79.294444444444451</v>
+        <v>2.2288888888888891</v>
       </c>
       <c r="BV166" s="35">
         <f t="shared" si="87"/>
-        <v>103.71666666666667</v>
+        <v>2.74</v>
       </c>
       <c r="BW166" s="35">
         <f t="shared" si="88"/>
-        <v>24.422222222222224</v>
+        <v>0.51111111111111107</v>
       </c>
       <c r="BX166" s="36">
         <f t="shared" si="89"/>
-        <v>932.87581699346413</v>
+        <v>26.222222222222221</v>
       </c>
       <c r="BY166" s="36">
         <f t="shared" si="90"/>
-        <v>1220.1960784313726</v>
+        <v>32.235294117647058</v>
       </c>
       <c r="BZ166" s="36">
         <f t="shared" si="91"/>
-        <v>287.32026143790847</v>
+        <v>6.0130718954248366</v>
       </c>
       <c r="CA166" s="50">
         <v>4</v>
@@ -46084,37 +46093,37 @@
         <v>253</v>
       </c>
       <c r="BR167" s="35">
-        <v>20.059999999999999</v>
+        <v>100.7</v>
       </c>
       <c r="BS167" s="35">
-        <v>24.66</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="BT167" s="35">
-        <v>4.5999999999999996</v>
+        <v>50.5</v>
       </c>
       <c r="BU167" s="35">
         <f t="shared" si="86"/>
-        <v>1.1144444444444446</v>
+        <v>5.5944444444444432</v>
       </c>
       <c r="BV167" s="35">
         <f t="shared" si="87"/>
-        <v>1.37</v>
+        <v>8.3999999999999986</v>
       </c>
       <c r="BW167" s="35">
         <f t="shared" si="88"/>
-        <v>0.25555555555555554</v>
+        <v>2.8055555555555554</v>
       </c>
       <c r="BX167" s="36">
         <f t="shared" si="89"/>
-        <v>3.9980069755854508</v>
+        <v>20.069755854509218</v>
       </c>
       <c r="BY167" s="36">
         <f t="shared" si="90"/>
-        <v>4.9147982062780269</v>
+        <v>30.134529147982065</v>
       </c>
       <c r="BZ167" s="36">
         <f t="shared" si="91"/>
-        <v>0.91679123069257595</v>
+        <v>10.064773293472845</v>
       </c>
       <c r="CA167" s="50">
         <v>8</v>
@@ -46351,37 +46360,37 @@
         <v>255</v>
       </c>
       <c r="BR168" s="35">
-        <v>100.7</v>
+        <v>176.25</v>
       </c>
       <c r="BS168" s="35">
-        <v>151.19999999999999</v>
+        <v>243.75</v>
       </c>
       <c r="BT168" s="35">
-        <v>50.5</v>
+        <v>67.5</v>
       </c>
       <c r="BU168" s="35">
         <f t="shared" si="86"/>
-        <v>3.2483870967741932</v>
+        <v>5.685483870967742</v>
       </c>
       <c r="BV168" s="35">
         <f t="shared" si="87"/>
-        <v>4.8774193548387093</v>
+        <v>7.862903225806452</v>
       </c>
       <c r="BW168" s="35">
         <f t="shared" si="88"/>
-        <v>1.6290322580645162</v>
+        <v>2.1774193548387095</v>
       </c>
       <c r="BX168" s="36">
         <f t="shared" si="89"/>
-        <v>14.02181480621954</v>
+        <v>24.541656996983061</v>
       </c>
       <c r="BY168" s="36">
         <f t="shared" si="90"/>
-        <v>21.053608725922487</v>
+        <v>33.940589463912744</v>
       </c>
       <c r="BZ168" s="36">
         <f t="shared" si="91"/>
-        <v>7.0317939197029471</v>
+        <v>9.3989324669296828</v>
       </c>
       <c r="CA168" s="48">
         <v>14</v>
@@ -46618,37 +46627,37 @@
         <v>253</v>
       </c>
       <c r="BR169" s="35">
-        <v>176.25</v>
+        <v>473.88</v>
       </c>
       <c r="BS169" s="35">
-        <v>243.75</v>
+        <v>679.78</v>
       </c>
       <c r="BT169" s="35">
-        <v>67.5</v>
+        <v>205.9</v>
       </c>
       <c r="BU169" s="35">
         <f t="shared" si="86"/>
-        <v>4.5192307692307692</v>
+        <v>12.150769230769228</v>
       </c>
       <c r="BV169" s="35">
         <f t="shared" si="87"/>
-        <v>6.25</v>
+        <v>17.430256410256408</v>
       </c>
       <c r="BW169" s="35">
         <f t="shared" si="88"/>
-        <v>1.7307692307692308</v>
+        <v>5.2794871794871794</v>
       </c>
       <c r="BX169" s="36">
         <f t="shared" si="89"/>
-        <v>8.5201522750619354</v>
+        <v>22.907970270106954</v>
       </c>
       <c r="BY169" s="36">
         <f t="shared" si="90"/>
-        <v>11.783189316575019</v>
+        <v>32.861441778959453</v>
       </c>
       <c r="BZ169" s="36">
         <f t="shared" si="91"/>
-        <v>3.2630370415130825</v>
+        <v>9.9534715088524983</v>
       </c>
       <c r="CA169" s="50">
         <v>16</v>
@@ -46885,37 +46894,37 @@
         <v>255</v>
       </c>
       <c r="BR170" s="35">
-        <v>473.88</v>
+        <v>191.33</v>
       </c>
       <c r="BS170" s="35">
-        <v>679.78</v>
+        <v>260.93</v>
       </c>
       <c r="BT170" s="35">
-        <v>205.9</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="BU170" s="35">
         <f t="shared" si="86"/>
-        <v>36.452307692307691</v>
+        <v>14.71769230769231</v>
       </c>
       <c r="BV170" s="35">
         <f t="shared" si="87"/>
-        <v>52.290769230769229</v>
+        <v>20.071538461538463</v>
       </c>
       <c r="BW170" s="35">
         <f t="shared" si="88"/>
-        <v>15.838461538461539</v>
+        <v>5.3538461538461535</v>
       </c>
       <c r="BX170" s="36">
         <f t="shared" si="89"/>
-        <v>93.069721767594103</v>
+        <v>37.577086743044191</v>
       </c>
       <c r="BY170" s="36">
         <f t="shared" si="90"/>
-        <v>133.50834697217675</v>
+        <v>51.246481178396074</v>
       </c>
       <c r="BZ170" s="36">
         <f t="shared" si="91"/>
-        <v>40.43862520458265</v>
+        <v>13.669394435351883</v>
       </c>
       <c r="CA170" s="50">
         <v>7</v>
@@ -47152,37 +47161,37 @@
         <v>254</v>
       </c>
       <c r="BR171" s="35">
-        <v>191.33</v>
+        <v>1823.84</v>
       </c>
       <c r="BS171" s="35">
-        <v>260.93</v>
+        <v>2283.34</v>
       </c>
       <c r="BT171" s="35">
-        <v>69.599999999999994</v>
+        <v>459.5</v>
       </c>
       <c r="BU171" s="35">
         <f t="shared" si="86"/>
-        <v>3.5431481481481484</v>
+        <v>33.774814814814818</v>
       </c>
       <c r="BV171" s="35">
         <f t="shared" si="87"/>
-        <v>4.8320370370370371</v>
+        <v>42.284074074074077</v>
       </c>
       <c r="BW171" s="35">
         <f t="shared" si="88"/>
-        <v>1.2888888888888888</v>
+        <v>8.5092592592592595</v>
       </c>
       <c r="BX171" s="36">
         <f t="shared" si="89"/>
-        <v>5.0376513954713014</v>
+        <v>48.021063717746188</v>
       </c>
       <c r="BY171" s="36">
         <f t="shared" si="90"/>
-        <v>6.8701948393891525</v>
+        <v>60.119536598209585</v>
       </c>
       <c r="BZ171" s="36">
         <f t="shared" si="91"/>
-        <v>1.8325434439178514</v>
+        <v>12.098472880463401</v>
       </c>
       <c r="CA171" s="48">
         <v>24</v>
@@ -47419,37 +47428,37 @@
         <v>254</v>
       </c>
       <c r="BR172" s="35">
-        <v>1823.84</v>
+        <v>503.84</v>
       </c>
       <c r="BS172" s="35">
-        <v>2283.34</v>
+        <v>753.94</v>
       </c>
       <c r="BT172" s="35">
-        <v>459.5</v>
+        <v>250.1</v>
       </c>
       <c r="BU172" s="35">
         <f t="shared" si="86"/>
-        <v>47.995789473684212</v>
+        <v>13.258947368421055</v>
       </c>
       <c r="BV172" s="35">
         <f t="shared" si="87"/>
-        <v>60.087894736842109</v>
+        <v>19.840526315789475</v>
       </c>
       <c r="BW172" s="35">
         <f t="shared" si="88"/>
-        <v>12.092105263157896</v>
+        <v>6.5815789473684205</v>
       </c>
       <c r="BX172" s="36">
         <f t="shared" si="89"/>
-        <v>167.42717258261933</v>
+        <v>46.252141982864146</v>
       </c>
       <c r="BY172" s="36">
         <f t="shared" si="90"/>
-        <v>209.60893512851897</v>
+        <v>69.211138310893517</v>
       </c>
       <c r="BZ172" s="36">
         <f t="shared" si="91"/>
-        <v>42.18176254589963</v>
+        <v>22.958996328029375</v>
       </c>
       <c r="CA172" s="50">
         <v>17</v>
@@ -47686,37 +47695,37 @@
         <v>253</v>
       </c>
       <c r="BR173" s="35">
-        <v>503.84</v>
+        <v>388.95</v>
       </c>
       <c r="BS173" s="35">
-        <v>753.94</v>
+        <v>510.85</v>
       </c>
       <c r="BT173" s="35">
-        <v>250.1</v>
+        <v>121.9</v>
       </c>
       <c r="BU173" s="35">
         <f t="shared" si="86"/>
-        <v>11.196444444444447</v>
+        <v>8.6433333333333326</v>
       </c>
       <c r="BV173" s="35">
         <f t="shared" si="87"/>
-        <v>16.754222222222225</v>
+        <v>11.352222222222222</v>
       </c>
       <c r="BW173" s="35">
         <f t="shared" si="88"/>
-        <v>5.5577777777777779</v>
+        <v>2.7088888888888891</v>
       </c>
       <c r="BX173" s="36">
         <f t="shared" si="89"/>
-        <v>31.029407236335651</v>
+        <v>23.953810623556585</v>
       </c>
       <c r="BY173" s="36">
         <f t="shared" si="90"/>
-        <v>46.432024634334113</v>
+        <v>31.461123941493458</v>
       </c>
       <c r="BZ173" s="36">
         <f t="shared" si="91"/>
-        <v>15.40261739799846</v>
+        <v>7.507313317936875</v>
       </c>
       <c r="CA173" s="50">
         <v>21</v>
@@ -47953,37 +47962,37 @@
         <v>255</v>
       </c>
       <c r="BR174" s="35">
-        <v>388.95</v>
+        <v>34.29</v>
       </c>
       <c r="BS174" s="35">
-        <v>510.85</v>
+        <v>46.09</v>
       </c>
       <c r="BT174" s="35">
-        <v>121.9</v>
+        <v>11.8</v>
       </c>
       <c r="BU174" s="35">
         <f t="shared" si="86"/>
-        <v>43.216666666666669</v>
+        <v>3.8100000000000005</v>
       </c>
       <c r="BV174" s="35">
         <f t="shared" si="87"/>
-        <v>56.761111111111113</v>
+        <v>5.1211111111111114</v>
       </c>
       <c r="BW174" s="35">
         <f t="shared" si="88"/>
-        <v>13.544444444444444</v>
+        <v>1.3111111111111111</v>
       </c>
       <c r="BX174" s="36">
         <f t="shared" si="89"/>
-        <v>275.85106382978722</v>
+        <v>24.319148936170215</v>
       </c>
       <c r="BY174" s="36">
         <f t="shared" si="90"/>
-        <v>362.30496453900707</v>
+        <v>32.687943262411352</v>
       </c>
       <c r="BZ174" s="36">
         <f t="shared" si="91"/>
-        <v>86.453900709219852</v>
+        <v>8.3687943262411348</v>
       </c>
       <c r="CA174" s="48">
         <v>3</v>
@@ -48220,37 +48229,37 @@
         <v>254</v>
       </c>
       <c r="BR175" s="35">
-        <v>34.29</v>
+        <v>235</v>
       </c>
       <c r="BS175" s="35">
-        <v>46.09</v>
+        <v>306.39999999999998</v>
       </c>
       <c r="BT175" s="35">
-        <v>11.8</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="BU175" s="35">
         <f t="shared" si="86"/>
-        <v>1.0390909090909091</v>
+        <v>7.1212121212121193</v>
       </c>
       <c r="BV175" s="35">
         <f t="shared" si="87"/>
-        <v>1.3966666666666667</v>
+        <v>9.2848484848484834</v>
       </c>
       <c r="BW175" s="35">
         <f t="shared" si="88"/>
-        <v>0.3575757575757576</v>
+        <v>2.163636363636364</v>
       </c>
       <c r="BX175" s="36">
         <f t="shared" si="89"/>
-        <v>3.2987012987012991</v>
+        <v>22.607022607022607</v>
       </c>
       <c r="BY175" s="36">
         <f t="shared" si="90"/>
-        <v>4.4338624338624344</v>
+        <v>29.475709475709476</v>
       </c>
       <c r="BZ175" s="36">
         <f t="shared" si="91"/>
-        <v>1.1351611351611353</v>
+        <v>6.8686868686868685</v>
       </c>
       <c r="CA175" s="50">
         <v>14</v>
@@ -48487,37 +48496,37 @@
         <v>255</v>
       </c>
       <c r="BR176" s="35">
-        <v>235</v>
+        <v>13.6</v>
       </c>
       <c r="BS176" s="35">
-        <v>306.39999999999998</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="BT176" s="35">
-        <v>71.400000000000006</v>
+        <v>6.8</v>
       </c>
       <c r="BU176" s="35">
         <f t="shared" si="86"/>
-        <v>46.999999999999993</v>
+        <v>2.72</v>
       </c>
       <c r="BV176" s="35">
         <f t="shared" si="87"/>
-        <v>61.279999999999994</v>
+        <v>4.08</v>
       </c>
       <c r="BW176" s="35">
         <f t="shared" si="88"/>
-        <v>14.280000000000001</v>
+        <v>1.3599999999999999</v>
       </c>
       <c r="BX176" s="36">
         <f t="shared" si="89"/>
-        <v>367.42671009771982</v>
+        <v>21.263843648208471</v>
       </c>
       <c r="BY176" s="36">
         <f t="shared" si="90"/>
-        <v>479.06188925081432</v>
+        <v>31.895765472312704</v>
       </c>
       <c r="BZ176" s="36">
         <f t="shared" si="91"/>
-        <v>111.63517915309447</v>
+        <v>10.631921824104234</v>
       </c>
       <c r="CA176" s="50">
         <v>0</v>
@@ -48754,37 +48763,37 @@
         <v>255</v>
       </c>
       <c r="BR177" s="35">
-        <v>13.6</v>
+        <v>498.88</v>
       </c>
       <c r="BS177" s="35">
-        <v>20.399999999999999</v>
+        <v>652.78</v>
       </c>
       <c r="BT177" s="35">
-        <v>6.8</v>
+        <v>153.9</v>
       </c>
       <c r="BU177" s="35">
         <f t="shared" si="86"/>
-        <v>0.25185185185185188</v>
+        <v>9.2385185185185179</v>
       </c>
       <c r="BV177" s="35">
         <f t="shared" si="87"/>
-        <v>0.37777777777777777</v>
+        <v>12.088518518518518</v>
       </c>
       <c r="BW177" s="35">
         <f t="shared" si="88"/>
-        <v>0.12592592592592591</v>
+        <v>2.85</v>
       </c>
       <c r="BX177" s="36">
         <f t="shared" si="89"/>
-        <v>0.58570198105081817</v>
+        <v>21.48492678725237</v>
       </c>
       <c r="BY177" s="36">
         <f t="shared" si="90"/>
-        <v>0.87855297157622736</v>
+        <v>28.112833763996555</v>
       </c>
       <c r="BZ177" s="36">
         <f t="shared" si="91"/>
-        <v>0.29285099052540914</v>
+        <v>6.6279069767441863</v>
       </c>
       <c r="CA177" s="50">
         <v>24</v>
@@ -49021,37 +49030,37 @@
         <v>253</v>
       </c>
       <c r="BR178" s="35">
-        <v>498.88</v>
+        <v>1142.72</v>
       </c>
       <c r="BS178" s="35">
-        <v>652.78</v>
+        <v>1515.32</v>
       </c>
       <c r="BT178" s="35">
-        <v>153.9</v>
+        <v>372.6</v>
       </c>
       <c r="BU178" s="35">
         <f t="shared" si="86"/>
-        <v>10.181224489795916</v>
+        <v>23.320816326530611</v>
       </c>
       <c r="BV178" s="35">
         <f t="shared" si="87"/>
-        <v>13.322040816326529</v>
+        <v>30.924897959183671</v>
       </c>
       <c r="BW178" s="35">
         <f t="shared" si="88"/>
-        <v>3.1408163265306124</v>
+        <v>7.6040816326530614</v>
       </c>
       <c r="BX178" s="36">
         <f t="shared" si="89"/>
-        <v>12.601825051836105</v>
+        <v>28.865373483070378</v>
       </c>
       <c r="BY178" s="36">
         <f t="shared" si="90"/>
-        <v>16.489374914483587</v>
+        <v>38.277336308427444</v>
       </c>
       <c r="BZ178" s="36">
         <f t="shared" si="91"/>
-        <v>3.8875498626474827</v>
+        <v>9.4119628253570635</v>
       </c>
       <c r="CA178" s="48">
         <v>23</v>
@@ -49287,6 +49296,15 @@
       <c r="BQ179" s="17" t="s">
         <v>253</v>
       </c>
+      <c r="BR179">
+        <v>365.88</v>
+      </c>
+      <c r="BS179">
+        <v>448.88</v>
+      </c>
+      <c r="BT179">
+        <v>83</v>
+      </c>
       <c r="CA179" s="55">
         <v>7</v>
       </c>
@@ -49522,37 +49540,37 @@
         <v>254</v>
       </c>
       <c r="BR180" s="35">
-        <v>365.88</v>
+        <v>144.16</v>
       </c>
       <c r="BS180" s="35">
-        <v>448.88</v>
+        <v>174.46</v>
       </c>
       <c r="BT180" s="35">
-        <v>83</v>
+        <v>30.3</v>
       </c>
       <c r="BU180" s="35">
         <f t="shared" si="86"/>
-        <v>14.072307692307692</v>
+        <v>5.5446153846153843</v>
       </c>
       <c r="BV180" s="35">
         <f t="shared" si="87"/>
-        <v>17.264615384615386</v>
+        <v>6.71</v>
       </c>
       <c r="BW180" s="35">
         <f t="shared" si="88"/>
-        <v>3.1923076923076925</v>
+        <v>1.1653846153846155</v>
       </c>
       <c r="BX180" s="36">
         <f t="shared" si="89"/>
-        <v>60.963065815051365</v>
+        <v>24.019994445987226</v>
       </c>
       <c r="BY180" s="36">
         <f t="shared" si="90"/>
-        <v>74.792557622882526</v>
+        <v>29.068592057761734</v>
       </c>
       <c r="BZ180" s="36">
         <f t="shared" si="91"/>
-        <v>13.829491807831158</v>
+        <v>5.0485976117745075</v>
       </c>
       <c r="CA180" s="48">
         <v>11</v>
@@ -49789,37 +49807,37 @@
         <v>255</v>
       </c>
       <c r="BR181" s="35">
-        <v>144.16</v>
+        <v>311.06</v>
       </c>
       <c r="BS181" s="35">
-        <v>174.46</v>
+        <v>422.06</v>
       </c>
       <c r="BT181" s="35">
-        <v>30.3</v>
+        <v>111</v>
       </c>
       <c r="BU181" s="35">
         <f t="shared" si="86"/>
-        <v>4.1188571428571432</v>
+        <v>8.8874285714285719</v>
       </c>
       <c r="BV181" s="35">
         <f t="shared" si="87"/>
-        <v>4.9845714285714289</v>
+        <v>12.058857142857143</v>
       </c>
       <c r="BW181" s="35">
         <f t="shared" si="88"/>
-        <v>0.86571428571428577</v>
+        <v>3.1714285714285713</v>
       </c>
       <c r="BX181" s="36">
         <f t="shared" si="89"/>
-        <v>10.995836643890037</v>
+        <v>23.726171937072941</v>
       </c>
       <c r="BY181" s="36">
         <f t="shared" si="90"/>
-        <v>13.306976005085016</v>
+        <v>32.192722072143653</v>
       </c>
       <c r="BZ181" s="36">
         <f t="shared" si="91"/>
-        <v>2.3111393611949786</v>
+        <v>8.4665501350707135</v>
       </c>
       <c r="CA181" s="50">
         <v>16</v>
@@ -50056,37 +50074,37 @@
         <v>253</v>
       </c>
       <c r="BR182" s="35">
-        <v>311.06</v>
+        <v>988.45</v>
       </c>
       <c r="BS182" s="35">
-        <v>422.06</v>
+        <v>1308.8499999999999</v>
       </c>
       <c r="BT182" s="35">
-        <v>111</v>
+        <v>320.39999999999998</v>
       </c>
       <c r="BU182" s="35">
         <f t="shared" si="86"/>
-        <v>5.7603703703703708</v>
+        <v>18.304629629629627</v>
       </c>
       <c r="BV182" s="35">
         <f t="shared" si="87"/>
-        <v>7.8159259259259262</v>
+        <v>24.23796296296296</v>
       </c>
       <c r="BW182" s="35">
         <f t="shared" si="88"/>
-        <v>2.0555555555555554</v>
+        <v>5.9333333333333327</v>
       </c>
       <c r="BX182" s="36">
         <f t="shared" si="89"/>
-        <v>8.6785240984864345</v>
+        <v>27.577596428820534</v>
       </c>
       <c r="BY182" s="36">
         <f t="shared" si="90"/>
-        <v>11.775406291413825</v>
+        <v>36.516705028946085</v>
       </c>
       <c r="BZ182" s="36">
         <f t="shared" si="91"/>
-        <v>3.0968821929273909</v>
+        <v>8.9391086001255484</v>
       </c>
       <c r="CA182" s="48">
         <v>24</v>
@@ -50323,37 +50341,37 @@
         <v>255</v>
       </c>
       <c r="BR183" s="35">
-        <v>988.45</v>
+        <v>64.89</v>
       </c>
       <c r="BS183" s="35">
-        <v>1308.8499999999999</v>
+        <v>121.19</v>
       </c>
       <c r="BT183" s="35">
-        <v>320.39999999999998</v>
+        <v>56.3</v>
       </c>
       <c r="BU183" s="35">
         <f t="shared" si="86"/>
-        <v>76.034615384615392</v>
+        <v>4.9915384615384619</v>
       </c>
       <c r="BV183" s="35">
         <f t="shared" si="87"/>
-        <v>100.68076923076923</v>
+        <v>9.3223076923076924</v>
       </c>
       <c r="BW183" s="35">
         <f t="shared" si="88"/>
-        <v>24.646153846153844</v>
+        <v>4.3307692307692305</v>
       </c>
       <c r="BX183" s="36">
         <f t="shared" si="89"/>
-        <v>276.90906968600444</v>
+        <v>18.178592272674216</v>
       </c>
       <c r="BY183" s="36">
         <f t="shared" si="90"/>
-        <v>366.66744484650405</v>
+        <v>33.950741216295086</v>
       </c>
       <c r="BZ183" s="36">
         <f t="shared" si="91"/>
-        <v>89.758375160499597</v>
+        <v>15.77214894362087</v>
       </c>
       <c r="CA183" s="50">
         <v>3</v>
@@ -50590,37 +50608,37 @@
         <v>255</v>
       </c>
       <c r="BR184" s="35">
-        <v>64.89</v>
+        <v>928.36</v>
       </c>
       <c r="BS184" s="35">
-        <v>121.19</v>
+        <v>1334.36</v>
       </c>
       <c r="BT184" s="35">
-        <v>56.3</v>
+        <v>406</v>
       </c>
       <c r="BU184" s="35">
         <f t="shared" si="86"/>
-        <v>1.62225</v>
+        <v>23.208999999999996</v>
       </c>
       <c r="BV184" s="35">
         <f t="shared" si="87"/>
-        <v>3.0297499999999999</v>
+        <v>33.358999999999995</v>
       </c>
       <c r="BW184" s="35">
         <f t="shared" si="88"/>
-        <v>1.4075</v>
+        <v>10.15</v>
       </c>
       <c r="BX184" s="36">
         <f t="shared" si="89"/>
-        <v>2.1860752386299835</v>
+        <v>31.275463222908474</v>
       </c>
       <c r="BY184" s="36">
         <f t="shared" si="90"/>
-        <v>4.0827624929814714</v>
+        <v>44.953172375070181</v>
       </c>
       <c r="BZ184" s="36">
         <f t="shared" si="91"/>
-        <v>1.8966872543514879</v>
+        <v>13.677709152161707</v>
       </c>
       <c r="CA184" s="48">
         <v>18</v>
@@ -50856,38 +50874,38 @@
       <c r="BQ185" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR185" s="35">
-        <v>928.36</v>
-      </c>
-      <c r="BS185" s="35">
-        <v>1334.36</v>
-      </c>
-      <c r="BT185" s="35">
-        <v>406</v>
+      <c r="BR185" s="57">
+        <v>699.43</v>
+      </c>
+      <c r="BS185" s="57">
+        <v>958.63</v>
+      </c>
+      <c r="BT185" s="57">
+        <v>259.2</v>
       </c>
       <c r="BU185" s="35">
         <f t="shared" si="86"/>
-        <v>18.203137254901957</v>
+        <v>13.714313725490197</v>
       </c>
       <c r="BV185" s="35">
         <f t="shared" si="87"/>
-        <v>26.163921568627448</v>
+        <v>18.796666666666667</v>
       </c>
       <c r="BW185" s="35">
         <f t="shared" si="88"/>
-        <v>7.9607843137254903</v>
+        <v>5.0823529411764703</v>
       </c>
       <c r="BX185" s="36">
         <f t="shared" si="89"/>
-        <v>46.724630386914122</v>
+        <v>35.202516514627241</v>
       </c>
       <c r="BY185" s="36">
         <f t="shared" si="90"/>
-        <v>67.158729160113239</v>
+        <v>48.248128342245991</v>
       </c>
       <c r="BZ185" s="36">
         <f t="shared" si="91"/>
-        <v>20.434098773199118</v>
+        <v>13.045611827618748</v>
       </c>
       <c r="CA185" s="50">
         <v>35</v>
@@ -51123,38 +51141,38 @@
       <c r="BQ186" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR186" s="35">
-        <v>699.43</v>
-      </c>
-      <c r="BS186" s="35">
-        <v>958.63</v>
-      </c>
-      <c r="BT186" s="35">
-        <v>259.2</v>
+      <c r="BR186" s="57">
+        <v>9.65</v>
+      </c>
+      <c r="BS186" s="57">
+        <v>10.55</v>
+      </c>
+      <c r="BT186" s="57">
+        <v>0.9</v>
       </c>
       <c r="BU186" s="35">
         <f t="shared" si="86"/>
-        <v>349.71500000000003</v>
+        <v>4.8250000000000002</v>
       </c>
       <c r="BV186" s="35">
         <f t="shared" si="87"/>
-        <v>479.315</v>
+        <v>5.2750000000000004</v>
       </c>
       <c r="BW186" s="35">
         <f t="shared" si="88"/>
-        <v>129.6</v>
+        <v>0.45</v>
       </c>
       <c r="BX186" s="36">
         <f t="shared" si="89"/>
-        <v>3411.853658536585</v>
+        <v>47.073170731707314</v>
       </c>
       <c r="BY186" s="36">
         <f t="shared" si="90"/>
-        <v>4676.2439024390242</v>
+        <v>51.463414634146339</v>
       </c>
       <c r="BZ186" s="36">
         <f t="shared" si="91"/>
-        <v>1264.3902439024391</v>
+        <v>4.3902439024390247</v>
       </c>
       <c r="CA186" s="48">
         <v>1</v>
@@ -51390,38 +51408,38 @@
       <c r="BQ187" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR187" s="35">
-        <v>9.65</v>
-      </c>
-      <c r="BS187" s="35">
-        <v>10.55</v>
-      </c>
-      <c r="BT187" s="35">
-        <v>0.9</v>
+      <c r="BR187" s="58">
+        <v>875.69</v>
+      </c>
+      <c r="BS187" s="58">
+        <v>1147.5899999999999</v>
+      </c>
+      <c r="BT187" s="58">
+        <v>271.89999999999998</v>
       </c>
       <c r="BU187" s="35">
         <f t="shared" si="86"/>
-        <v>0.17870370370370373</v>
+        <v>16.21648148148148</v>
       </c>
       <c r="BV187" s="35">
         <f t="shared" si="87"/>
-        <v>0.19537037037037039</v>
+        <v>21.251666666666665</v>
       </c>
       <c r="BW187" s="35">
         <f t="shared" si="88"/>
-        <v>1.6666666666666666E-2</v>
+        <v>5.0351851851851848</v>
       </c>
       <c r="BX187" s="36">
         <f t="shared" si="89"/>
-        <v>0.47654320987654325</v>
+        <v>43.24395061728395</v>
       </c>
       <c r="BY187" s="36">
         <f t="shared" si="90"/>
-        <v>0.5209876543209877</v>
+        <v>56.671111111111109</v>
       </c>
       <c r="BZ187" s="36">
         <f t="shared" si="91"/>
-        <v>4.4444444444444446E-2</v>
+        <v>13.427160493827161</v>
       </c>
       <c r="CA187" s="50">
         <v>36</v>
@@ -51657,38 +51675,38 @@
       <c r="BQ188" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR188" s="35">
-        <v>875.69</v>
-      </c>
-      <c r="BS188" s="35">
-        <v>1147.5899999999999</v>
-      </c>
-      <c r="BT188" s="35">
-        <v>271.89999999999998</v>
+      <c r="BR188" s="58">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="BS188" s="58">
+        <v>14.28</v>
+      </c>
+      <c r="BT188" s="58">
+        <v>4.9000000000000004</v>
       </c>
       <c r="BU188" s="35">
         <f t="shared" si="86"/>
-        <v>125.09857142857142</v>
+        <v>1.3399999999999999</v>
       </c>
       <c r="BV188" s="35">
         <f t="shared" si="87"/>
-        <v>163.94142857142856</v>
+        <v>2.04</v>
       </c>
       <c r="BW188" s="35">
         <f t="shared" si="88"/>
-        <v>38.842857142857142</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="BX188" s="36">
         <f t="shared" si="89"/>
-        <v>1830.7108013937284</v>
+        <v>19.609756097560975</v>
       </c>
       <c r="BY188" s="36">
         <f t="shared" si="90"/>
-        <v>2399.1428571428573</v>
+        <v>29.853658536585368</v>
       </c>
       <c r="BZ188" s="36">
         <f t="shared" si="91"/>
-        <v>568.43205574912895</v>
+        <v>10.24390243902439</v>
       </c>
       <c r="CA188" s="48">
         <v>4</v>
@@ -51924,38 +51942,38 @@
       <c r="BQ189" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR189" s="35">
-        <v>9.3800000000000008</v>
-      </c>
-      <c r="BS189" s="35">
-        <v>14.28</v>
-      </c>
-      <c r="BT189" s="35">
-        <v>4.9000000000000004</v>
+      <c r="BR189" s="58">
+        <v>219.06</v>
+      </c>
+      <c r="BS189" s="58">
+        <v>310.45999999999998</v>
+      </c>
+      <c r="BT189" s="58">
+        <v>91.4</v>
       </c>
       <c r="BU189" s="35">
         <f t="shared" si="86"/>
-        <v>0.28424242424242419</v>
+        <v>6.6381818181818169</v>
       </c>
       <c r="BV189" s="35">
         <f t="shared" si="87"/>
-        <v>0.43272727272727268</v>
+        <v>9.4078787878787864</v>
       </c>
       <c r="BW189" s="35">
         <f t="shared" si="88"/>
-        <v>0.1484848484848485</v>
+        <v>2.76969696969697</v>
       </c>
       <c r="BX189" s="36">
         <f t="shared" si="89"/>
-        <v>0.95812053115423901</v>
+        <v>22.375893769152199</v>
       </c>
       <c r="BY189" s="36">
         <f t="shared" si="90"/>
-        <v>1.4586312563840653</v>
+        <v>31.711950970377938</v>
       </c>
       <c r="BZ189" s="36">
         <f t="shared" si="91"/>
-        <v>0.50051072522982631</v>
+        <v>9.3360572012257403</v>
       </c>
       <c r="CA189" s="48">
         <v>19</v>
@@ -52191,38 +52209,38 @@
       <c r="BQ190" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR190" s="35">
-        <v>219.06</v>
-      </c>
-      <c r="BS190" s="35">
-        <v>310.45999999999998</v>
-      </c>
-      <c r="BT190" s="35">
-        <v>91.4</v>
+      <c r="BR190" s="58">
+        <v>1715.7</v>
+      </c>
+      <c r="BS190" s="58">
+        <v>2223</v>
+      </c>
+      <c r="BT190" s="58">
+        <v>507.3</v>
       </c>
       <c r="BU190" s="35">
         <f t="shared" si="86"/>
-        <v>4.0566666666666666</v>
+        <v>31.772222222222219</v>
       </c>
       <c r="BV190" s="35">
         <f t="shared" si="87"/>
-        <v>5.7492592592592588</v>
+        <v>41.166666666666664</v>
       </c>
       <c r="BW190" s="35">
         <f t="shared" si="88"/>
-        <v>1.6925925925925926</v>
+        <v>9.3944444444444439</v>
       </c>
       <c r="BX190" s="36">
         <f t="shared" si="89"/>
-        <v>6.5386165211551379</v>
+        <v>51.211103648981428</v>
       </c>
       <c r="BY190" s="36">
         <f t="shared" si="90"/>
-        <v>9.2667711364823528</v>
+        <v>66.353257219610484</v>
       </c>
       <c r="BZ190" s="36">
         <f t="shared" si="91"/>
-        <v>2.7281546153272145</v>
+        <v>15.142153570629057</v>
       </c>
       <c r="CA190" s="48">
         <v>36</v>
@@ -52458,38 +52476,38 @@
       <c r="BQ191" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="BR191" s="35">
-        <v>1715.7</v>
-      </c>
-      <c r="BS191" s="35">
-        <v>2223</v>
-      </c>
-      <c r="BT191" s="35">
-        <v>507.3</v>
+      <c r="BR191" s="58">
+        <v>86.56</v>
+      </c>
+      <c r="BS191" s="58">
+        <v>133.46</v>
+      </c>
+      <c r="BT191" s="58">
+        <v>46.9</v>
       </c>
       <c r="BU191" s="35">
         <f t="shared" si="86"/>
-        <v>95.316666666666663</v>
+        <v>4.8088888888888892</v>
       </c>
       <c r="BV191" s="35">
         <f t="shared" si="87"/>
-        <v>123.5</v>
+        <v>7.4144444444444453</v>
       </c>
       <c r="BW191" s="35">
         <f t="shared" si="88"/>
-        <v>28.183333333333334</v>
+        <v>2.6055555555555556</v>
       </c>
       <c r="BX191" s="36">
         <f t="shared" si="89"/>
-        <v>423.62962962962968</v>
+        <v>21.372839506172838</v>
       </c>
       <c r="BY191" s="36">
         <f t="shared" si="90"/>
-        <v>548.88888888888891</v>
+        <v>32.953086419753085</v>
       </c>
       <c r="BZ191" s="36">
         <f t="shared" si="91"/>
-        <v>125.25925925925925</v>
+        <v>11.580246913580247</v>
       </c>
       <c r="CA191" s="50">
         <v>12</v>
@@ -52725,38 +52743,38 @@
       <c r="BQ192" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR192" s="35">
-        <v>86.56</v>
-      </c>
-      <c r="BS192" s="35">
-        <v>133.46</v>
-      </c>
-      <c r="BT192" s="35">
-        <v>46.9</v>
+      <c r="BR192" s="57">
+        <v>665.05</v>
+      </c>
+      <c r="BS192" s="57">
+        <v>895.05</v>
+      </c>
+      <c r="BT192" s="57">
+        <v>230</v>
       </c>
       <c r="BU192" s="35">
         <f t="shared" si="86"/>
-        <v>1.6029629629629631</v>
+        <v>12.31574074074074</v>
       </c>
       <c r="BV192" s="35">
         <f t="shared" si="87"/>
-        <v>2.4714814814814816</v>
+        <v>16.574999999999999</v>
       </c>
       <c r="BW192" s="35">
         <f t="shared" si="88"/>
-        <v>0.86851851851851847</v>
+        <v>4.2592592592592595</v>
       </c>
       <c r="BX192" s="36">
         <f t="shared" si="89"/>
-        <v>2.5494440762830424</v>
+        <v>19.587659229806349</v>
       </c>
       <c r="BY192" s="36">
         <f t="shared" si="90"/>
-        <v>3.9307856564317798</v>
+        <v>26.36182902584493</v>
       </c>
       <c r="BZ192" s="36">
         <f t="shared" si="91"/>
-        <v>1.3813415801487372</v>
+        <v>6.7741697960385832</v>
       </c>
       <c r="CA192" s="48">
         <v>36</v>
@@ -52992,38 +53010,38 @@
       <c r="BQ193" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR193" s="35">
-        <v>665.05</v>
-      </c>
-      <c r="BS193" s="35">
-        <v>895.05</v>
-      </c>
-      <c r="BT193" s="35">
-        <v>230</v>
+      <c r="BR193" s="57">
+        <v>889.57</v>
+      </c>
+      <c r="BS193" s="57">
+        <v>1332.78</v>
+      </c>
+      <c r="BT193" s="57">
+        <v>443.2</v>
       </c>
       <c r="BU193" s="35">
         <f t="shared" si="86"/>
-        <v>12.31574074074074</v>
+        <v>16.473703703703706</v>
       </c>
       <c r="BV193" s="35">
         <f t="shared" si="87"/>
-        <v>16.574999999999999</v>
+        <v>24.681111111111111</v>
       </c>
       <c r="BW193" s="35">
         <f t="shared" si="88"/>
-        <v>4.2592592592592595</v>
+        <v>8.2074074074074073</v>
       </c>
       <c r="BX193" s="36">
         <f t="shared" si="89"/>
-        <v>19.957986345562311</v>
+        <v>26.696076224773051</v>
       </c>
       <c r="BY193" s="36">
         <f t="shared" si="90"/>
-        <v>26.860229574611751</v>
+        <v>39.996398829619629</v>
       </c>
       <c r="BZ193" s="36">
         <f t="shared" si="91"/>
-        <v>6.9022432290494411</v>
+        <v>13.300322604846576</v>
       </c>
       <c r="CA193" s="48">
         <v>36</v>
@@ -53259,38 +53277,38 @@
       <c r="BQ194" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR194" s="35">
-        <v>889.57</v>
-      </c>
-      <c r="BS194" s="35">
-        <v>1332.78</v>
-      </c>
-      <c r="BT194" s="35">
-        <v>443.2</v>
+      <c r="BR194" s="57">
+        <v>8.82</v>
+      </c>
+      <c r="BS194" s="57">
+        <v>11.52</v>
+      </c>
+      <c r="BT194" s="57">
+        <v>2.7</v>
       </c>
       <c r="BU194" s="35">
         <f t="shared" si="86"/>
-        <v>444.78999999999996</v>
+        <v>4.41</v>
       </c>
       <c r="BV194" s="35">
         <f t="shared" si="87"/>
-        <v>666.39</v>
+        <v>5.76</v>
       </c>
       <c r="BW194" s="35">
         <f t="shared" si="88"/>
-        <v>221.6</v>
+        <v>1.35</v>
       </c>
       <c r="BX194" s="36">
         <f t="shared" si="89"/>
-        <v>2210.1366459627329</v>
+        <v>21.913043478260871</v>
       </c>
       <c r="BY194" s="36">
         <f t="shared" si="90"/>
-        <v>3311.2546583850931</v>
+        <v>28.621118012422361</v>
       </c>
       <c r="BZ194" s="36">
         <f t="shared" si="91"/>
-        <v>1101.1180124223602</v>
+        <v>6.7080745341614909</v>
       </c>
       <c r="CA194" s="48">
         <v>1</v>
@@ -53526,38 +53544,38 @@
       <c r="BQ195" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR195" s="35">
-        <v>8.82</v>
-      </c>
-      <c r="BS195" s="35">
-        <v>11.52</v>
-      </c>
-      <c r="BT195" s="35">
-        <v>2.7</v>
+      <c r="BR195" s="58">
+        <v>263.47000000000003</v>
+      </c>
+      <c r="BS195" s="58">
+        <v>371.57</v>
+      </c>
+      <c r="BT195" s="58">
+        <v>108.1</v>
       </c>
       <c r="BU195" s="35">
         <f t="shared" si="86"/>
-        <v>0.3528</v>
+        <v>10.5388</v>
       </c>
       <c r="BV195" s="35">
         <f t="shared" si="87"/>
-        <v>0.46079999999999999</v>
+        <v>14.8628</v>
       </c>
       <c r="BW195" s="35">
         <f t="shared" si="88"/>
-        <v>0.10800000000000001</v>
+        <v>4.3239999999999998</v>
       </c>
       <c r="BX195" s="36">
         <f t="shared" si="89"/>
-        <v>0.91835140997830811</v>
+        <v>27.432885032537964</v>
       </c>
       <c r="BY195" s="36">
         <f t="shared" si="90"/>
-        <v>1.1994793926247289</v>
+        <v>38.68841648590022</v>
       </c>
       <c r="BZ195" s="36">
         <f t="shared" si="91"/>
-        <v>0.2811279826464208</v>
+        <v>11.255531453362256</v>
       </c>
       <c r="CA195" s="48">
         <v>16</v>
@@ -53793,38 +53811,38 @@
       <c r="BQ196" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR196" s="35">
-        <v>263.47000000000003</v>
-      </c>
-      <c r="BS196" s="35">
-        <v>371.57</v>
-      </c>
-      <c r="BT196" s="35">
-        <v>108.1</v>
+      <c r="BR196" s="58">
+        <v>0.87</v>
+      </c>
+      <c r="BS196" s="58">
+        <v>7.57</v>
+      </c>
+      <c r="BT196" s="58">
+        <v>6.7</v>
       </c>
       <c r="BU196" s="35">
         <f t="shared" si="86"/>
-        <v>263.47000000000003</v>
+        <v>0.87000000000000011</v>
       </c>
       <c r="BV196" s="35">
         <f t="shared" si="87"/>
-        <v>371.57</v>
+        <v>7.57</v>
       </c>
       <c r="BW196" s="35">
         <f t="shared" si="88"/>
-        <v>108.1</v>
+        <v>6.7</v>
       </c>
       <c r="BX196" s="36">
         <f t="shared" si="89"/>
-        <v>857.97557666214391</v>
+        <v>2.8331071913161487</v>
       </c>
       <c r="BY196" s="36">
         <f t="shared" si="90"/>
-        <v>1209.9972862957939</v>
+        <v>24.651289009497965</v>
       </c>
       <c r="BZ196" s="36">
         <f t="shared" si="91"/>
-        <v>352.02170963364995</v>
+        <v>21.818181818181817</v>
       </c>
       <c r="CA196" s="50">
         <v>0</v>
@@ -54060,38 +54078,38 @@
       <c r="BQ197" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="BR197" s="35">
-        <v>0.87</v>
-      </c>
-      <c r="BS197" s="35">
-        <v>7.57</v>
-      </c>
-      <c r="BT197" s="35">
-        <v>6.7</v>
+      <c r="BR197" s="57">
+        <v>1264.72</v>
+      </c>
+      <c r="BS197" s="57">
+        <v>1765.02</v>
+      </c>
+      <c r="BT197" s="57">
+        <v>500.3</v>
       </c>
       <c r="BU197" s="35">
         <f t="shared" si="86"/>
-        <v>1.6111111111111118E-2</v>
+        <v>23.42074074074074</v>
       </c>
       <c r="BV197" s="35">
         <f t="shared" si="87"/>
-        <v>0.14018518518518519</v>
+        <v>32.685555555555553</v>
       </c>
       <c r="BW197" s="35">
         <f t="shared" si="88"/>
-        <v>0.12407407407407407</v>
+        <v>9.2648148148148142</v>
       </c>
       <c r="BX197" s="36">
         <f t="shared" si="89"/>
-        <v>2.1245421245421253E-2</v>
+        <v>30.884493284493288</v>
       </c>
       <c r="BY197" s="36">
         <f t="shared" si="90"/>
-        <v>0.18485958485958487</v>
+        <v>43.101831501831505</v>
       </c>
       <c r="BZ197" s="36">
         <f t="shared" si="91"/>
-        <v>0.16361416361416362</v>
+        <v>12.217338217338217</v>
       </c>
       <c r="CA197" s="48">
         <v>36</v>
@@ -54327,6 +54345,9 @@
       <c r="BQ198" s="17" t="s">
         <v>255</v>
       </c>
+      <c r="BR198" s="58"/>
+      <c r="BS198" s="58"/>
+      <c r="BT198" s="58"/>
       <c r="CA198" s="56">
         <v>17</v>
       </c>
@@ -54561,38 +54582,38 @@
       <c r="BQ199" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR199" s="35">
-        <v>427.78</v>
-      </c>
-      <c r="BS199" s="35">
-        <v>571.98</v>
-      </c>
-      <c r="BT199" s="35">
-        <v>144.19999999999999</v>
+      <c r="BR199" s="58">
+        <v>493.23</v>
+      </c>
+      <c r="BS199" s="58">
+        <v>658.83</v>
+      </c>
+      <c r="BT199" s="58">
+        <v>165.6</v>
       </c>
       <c r="BU199" s="35">
         <f t="shared" si="86"/>
-        <v>9.7222727272727276</v>
+        <v>11.209772727272728</v>
       </c>
       <c r="BV199" s="35">
         <f t="shared" si="87"/>
-        <v>12.999545454545455</v>
+        <v>14.973409090909092</v>
       </c>
       <c r="BW199" s="35">
         <f t="shared" si="88"/>
-        <v>3.2772727272727269</v>
+        <v>3.7636363636363637</v>
       </c>
       <c r="BX199" s="36">
         <f t="shared" si="89"/>
-        <v>28.559919884277292</v>
+        <v>32.929564927116942</v>
       </c>
       <c r="BY199" s="36">
         <f t="shared" si="90"/>
-        <v>38.18715922999889</v>
+        <v>43.985534661177255</v>
       </c>
       <c r="BZ199" s="36">
         <f t="shared" si="91"/>
-        <v>9.6272393457215983</v>
+        <v>11.055969734060309</v>
       </c>
       <c r="CA199" s="50">
         <v>31</v>
@@ -54828,38 +54849,38 @@
       <c r="BQ200" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR200" s="35">
-        <v>493.23</v>
-      </c>
-      <c r="BS200" s="35">
-        <v>658.83</v>
-      </c>
-      <c r="BT200" s="35">
-        <v>165.6</v>
+      <c r="BR200" s="58">
+        <v>254.5</v>
+      </c>
+      <c r="BS200" s="58">
+        <v>330.4</v>
+      </c>
+      <c r="BT200" s="58">
+        <v>75.900000000000006</v>
       </c>
       <c r="BU200" s="35">
         <f t="shared" si="86"/>
-        <v>12.979736842105265</v>
+        <v>6.697368421052631</v>
       </c>
       <c r="BV200" s="35">
         <f t="shared" si="87"/>
-        <v>17.33763157894737</v>
+        <v>8.6947368421052627</v>
       </c>
       <c r="BW200" s="35">
         <f t="shared" si="88"/>
-        <v>4.3578947368421055</v>
+        <v>1.9973684210526317</v>
       </c>
       <c r="BX200" s="36">
         <f t="shared" si="89"/>
-        <v>39.482089253552132</v>
+        <v>20.372223334000402</v>
       </c>
       <c r="BY200" s="36">
         <f t="shared" si="90"/>
-        <v>52.738042825695416</v>
+        <v>26.447868721232741</v>
       </c>
       <c r="BZ200" s="36">
         <f t="shared" si="91"/>
-        <v>13.255953572143286</v>
+        <v>6.0756453872323393</v>
       </c>
       <c r="CA200" s="48">
         <v>27</v>
@@ -55095,38 +55116,38 @@
       <c r="BQ201" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR201" s="35">
-        <v>254.5</v>
-      </c>
-      <c r="BS201" s="35">
-        <v>330.4</v>
-      </c>
-      <c r="BT201" s="35">
-        <v>75.900000000000006</v>
+      <c r="BR201" s="57">
+        <v>596.33000000000004</v>
+      </c>
+      <c r="BS201" s="57">
+        <v>764.43</v>
+      </c>
+      <c r="BT201" s="57">
+        <v>168.1</v>
       </c>
       <c r="BU201" s="35">
         <f t="shared" ref="BU201:BU202" si="114">BV201-BW201</f>
-        <v>4.8018867924528301</v>
+        <v>11.251509433962262</v>
       </c>
       <c r="BV201" s="35">
         <f t="shared" ref="BV201:BV202" si="115">BS201/$D201</f>
-        <v>6.2339622641509429</v>
+        <v>14.42320754716981</v>
       </c>
       <c r="BW201" s="35">
         <f t="shared" ref="BW201:BW202" si="116">BT201/$D201</f>
-        <v>1.4320754716981132</v>
+        <v>3.171698113207547</v>
       </c>
       <c r="BX201" s="36">
         <f t="shared" ref="BX201:BX202" si="117">BY201-BZ201</f>
-        <v>10.790756836972651</v>
+        <v>25.284290862836546</v>
       </c>
       <c r="BY201" s="36">
         <f t="shared" ref="BY201:BY202" si="118">BS201*2400/$G201</f>
-        <v>14.008903964384142</v>
+        <v>32.411702353190584</v>
       </c>
       <c r="BZ201" s="36">
         <f t="shared" ref="BZ201:BZ202" si="119">BT201*2400/$G201</f>
-        <v>3.2181471274114903</v>
+        <v>7.1274114903540386</v>
       </c>
       <c r="CA201" s="48">
         <v>35</v>
@@ -55362,39 +55383,15 @@
       <c r="BQ202" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="BR202" s="35">
-        <v>596.33000000000004</v>
-      </c>
-      <c r="BS202" s="35">
-        <v>764.43</v>
-      </c>
-      <c r="BT202" s="35">
-        <v>168.1</v>
-      </c>
-      <c r="BU202" s="35">
-        <f t="shared" si="114"/>
-        <v>85.19</v>
-      </c>
-      <c r="BV202" s="35">
-        <f t="shared" si="115"/>
-        <v>109.2042857142857</v>
-      </c>
-      <c r="BW202" s="35">
-        <f t="shared" si="116"/>
-        <v>24.014285714285712</v>
-      </c>
-      <c r="BX202" s="36">
-        <f t="shared" si="117"/>
-        <v>908.69333333333316</v>
-      </c>
-      <c r="BY202" s="36">
-        <f t="shared" si="118"/>
-        <v>1164.8457142857142</v>
-      </c>
-      <c r="BZ202" s="36">
-        <f t="shared" si="119"/>
-        <v>256.15238095238095</v>
-      </c>
+      <c r="BR202" s="58"/>
+      <c r="BS202" s="58"/>
+      <c r="BT202" s="58"/>
+      <c r="BU202" s="35"/>
+      <c r="BV202" s="35"/>
+      <c r="BW202" s="35"/>
+      <c r="BX202" s="36"/>
+      <c r="BY202" s="36"/>
+      <c r="BZ202" s="36"/>
       <c r="CA202" s="27">
         <v>4</v>
       </c>
@@ -55629,13 +55626,13 @@
       <c r="BQ203" s="48" t="s">
         <v>255</v>
       </c>
-      <c r="BR203" s="35">
+      <c r="BR203" s="58">
         <v>137.43</v>
       </c>
-      <c r="BS203" s="35">
+      <c r="BS203" s="58">
         <v>179.63</v>
       </c>
-      <c r="BT203" s="35">
+      <c r="BT203" s="58">
         <v>42.2</v>
       </c>
       <c r="BU203" s="35">

--- a/22-23_KBL_stats.xlsx
+++ b/22-23_KBL_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Project\2026\KBL Stats Analyzer 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC32B80-7048-4826-ACB3-65D36B901D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C47306-7DF9-47CD-AF4D-E089EC1AE3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1785" windowWidth="29040" windowHeight="15720" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="302">
   <si>
     <t>Season</t>
   </si>
@@ -995,6 +995,10 @@
   <si>
     <t>외국인</t>
   </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2292,8 +2296,8 @@
         <v>189</v>
       </c>
       <c r="BP2" s="28"/>
-      <c r="BQ2" s="17" t="s">
-        <v>253</v>
+      <c r="BQ2" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR2" s="58">
         <v>137.43</v>
@@ -2538,8 +2542,8 @@
         <v>189</v>
       </c>
       <c r="BP3" s="28"/>
-      <c r="BQ3" s="17" t="s">
-        <v>253</v>
+      <c r="BQ3" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR3" s="35">
         <v>179.34</v>
@@ -2784,8 +2788,8 @@
         <v>189</v>
       </c>
       <c r="BP4" s="28"/>
-      <c r="BQ4" s="17" t="s">
-        <v>255</v>
+      <c r="BQ4" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR4" s="58">
         <v>427.78</v>
@@ -3030,8 +3034,8 @@
         <v>300</v>
       </c>
       <c r="BP5" s="28"/>
-      <c r="BQ5" s="17" t="s">
-        <v>253</v>
+      <c r="BQ5" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR5" s="58">
         <v>475.37</v>
@@ -3276,8 +3280,8 @@
         <v>189</v>
       </c>
       <c r="BP6" s="28"/>
-      <c r="BQ6" s="17" t="s">
-        <v>253</v>
+      <c r="BQ6" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR6" s="35">
         <v>365.88</v>
@@ -3543,7 +3547,7 @@
         <v>189</v>
       </c>
       <c r="BP7" s="28"/>
-      <c r="BQ7" s="17" t="s">
+      <c r="BQ7" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR7" s="57">
@@ -3810,8 +3814,8 @@
         <v>189</v>
       </c>
       <c r="BP8" s="28"/>
-      <c r="BQ8" s="17" t="s">
-        <v>253</v>
+      <c r="BQ8" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR8" s="57">
         <v>59.02</v>
@@ -4077,7 +4081,7 @@
         <v>189</v>
       </c>
       <c r="BP9" s="28"/>
-      <c r="BQ9" s="17" t="s">
+      <c r="BQ9" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR9" s="57">
@@ -4344,8 +4348,8 @@
         <v>189</v>
       </c>
       <c r="BP10" s="28"/>
-      <c r="BQ10" s="17" t="s">
-        <v>255</v>
+      <c r="BQ10" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR10" s="57">
         <v>129.87</v>
@@ -4611,8 +4615,8 @@
         <v>189</v>
       </c>
       <c r="BP11" s="28"/>
-      <c r="BQ11" s="17" t="s">
-        <v>254</v>
+      <c r="BQ11" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR11" s="58">
         <v>521.99</v>
@@ -4878,8 +4882,8 @@
         <v>232</v>
       </c>
       <c r="BP12" s="28"/>
-      <c r="BQ12" s="17" t="s">
-        <v>255</v>
+      <c r="BQ12" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR12" s="57">
         <v>337.23</v>
@@ -5145,8 +5149,8 @@
         <v>232</v>
       </c>
       <c r="BP13" s="28"/>
-      <c r="BQ13" s="17" t="s">
-        <v>254</v>
+      <c r="BQ13" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR13" s="57">
         <v>68.86</v>
@@ -5412,8 +5416,8 @@
         <v>232</v>
       </c>
       <c r="BP14" s="28"/>
-      <c r="BQ14" s="17" t="s">
-        <v>255</v>
+      <c r="BQ14" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR14" s="57">
         <v>1740.33</v>
@@ -5679,8 +5683,8 @@
         <v>233</v>
       </c>
       <c r="BP15" s="28"/>
-      <c r="BQ15" s="17" t="s">
-        <v>254</v>
+      <c r="BQ15" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR15" s="57">
         <v>89.93</v>
@@ -5946,8 +5950,8 @@
         <v>189</v>
       </c>
       <c r="BP16" s="27"/>
-      <c r="BQ16" s="17" t="s">
-        <v>253</v>
+      <c r="BQ16" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR16" s="58">
         <v>188.93</v>
@@ -6213,7 +6217,7 @@
         <v>189</v>
       </c>
       <c r="BP17" s="28"/>
-      <c r="BQ17" s="17" t="s">
+      <c r="BQ17" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR17" s="57">
@@ -6480,8 +6484,8 @@
         <v>189</v>
       </c>
       <c r="BP18" s="27"/>
-      <c r="BQ18" s="17" t="s">
-        <v>255</v>
+      <c r="BQ18" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR18" s="57">
         <v>6.54</v>
@@ -6747,8 +6751,8 @@
         <v>189</v>
       </c>
       <c r="BP19" s="28"/>
-      <c r="BQ19" s="17" t="s">
-        <v>254</v>
+      <c r="BQ19" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR19" s="57">
         <v>1361.76</v>
@@ -7014,9 +7018,7 @@
         <v>189</v>
       </c>
       <c r="BP20" s="28"/>
-      <c r="BQ20" s="17" t="s">
-        <v>253</v>
-      </c>
+      <c r="BQ20" s="57"/>
       <c r="BR20" s="57"/>
       <c r="BS20" s="57"/>
       <c r="BT20" s="57"/>
@@ -7275,8 +7277,8 @@
         <v>189</v>
       </c>
       <c r="BP21" s="28"/>
-      <c r="BQ21" s="17" t="s">
-        <v>254</v>
+      <c r="BQ21" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR21" s="57">
         <v>28.29</v>
@@ -7542,8 +7544,8 @@
         <v>189</v>
       </c>
       <c r="BP22" s="28"/>
-      <c r="BQ22" s="17" t="s">
-        <v>255</v>
+      <c r="BQ22" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR22" s="58">
         <v>1049.3599999999999</v>
@@ -7809,8 +7811,8 @@
         <v>189</v>
       </c>
       <c r="BP23" s="28"/>
-      <c r="BQ23" s="17" t="s">
-        <v>255</v>
+      <c r="BQ23" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR23" s="58">
         <v>4.54</v>
@@ -8076,8 +8078,8 @@
         <v>232</v>
       </c>
       <c r="BP24" s="28"/>
-      <c r="BQ24" s="17" t="s">
-        <v>253</v>
+      <c r="BQ24" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR24" s="58"/>
       <c r="BS24" s="58"/>
@@ -8313,8 +8315,8 @@
         <v>189</v>
       </c>
       <c r="BP25" s="28"/>
-      <c r="BQ25" s="17" t="s">
-        <v>253</v>
+      <c r="BQ25" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR25" s="58">
         <v>11.49</v>
@@ -8580,8 +8582,8 @@
         <v>189</v>
       </c>
       <c r="BP26" s="27"/>
-      <c r="BQ26" s="17" t="s">
-        <v>254</v>
+      <c r="BQ26" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR26" s="57">
         <v>464.42</v>
@@ -8847,8 +8849,8 @@
         <v>189</v>
       </c>
       <c r="BP27" s="28"/>
-      <c r="BQ27" s="17" t="s">
-        <v>254</v>
+      <c r="BQ27" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR27" s="57">
         <v>545.66999999999996</v>
@@ -9114,8 +9116,8 @@
         <v>189</v>
       </c>
       <c r="BP28" s="28"/>
-      <c r="BQ28" s="17" t="s">
-        <v>253</v>
+      <c r="BQ28" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR28" s="57">
         <v>420.94</v>
@@ -9381,7 +9383,7 @@
         <v>189</v>
       </c>
       <c r="BP29" s="28"/>
-      <c r="BQ29" s="17" t="s">
+      <c r="BQ29" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR29" s="57">
@@ -9648,8 +9650,8 @@
         <v>232</v>
       </c>
       <c r="BP30" s="28"/>
-      <c r="BQ30" s="17" t="s">
-        <v>255</v>
+      <c r="BQ30" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR30" s="57">
         <v>609.5</v>
@@ -9915,7 +9917,7 @@
         <v>232</v>
       </c>
       <c r="BP31" s="28"/>
-      <c r="BQ31" s="17" t="s">
+      <c r="BQ31" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR31" s="57">
@@ -10182,7 +10184,7 @@
         <v>189</v>
       </c>
       <c r="BP32" s="28"/>
-      <c r="BQ32" s="17" t="s">
+      <c r="BQ32" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR32" s="58">
@@ -10449,7 +10451,7 @@
         <v>189</v>
       </c>
       <c r="BP33" s="28"/>
-      <c r="BQ33" s="17" t="s">
+      <c r="BQ33" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR33" s="58">
@@ -10716,8 +10718,8 @@
         <v>189</v>
       </c>
       <c r="BP34" s="28"/>
-      <c r="BQ34" s="17" t="s">
-        <v>253</v>
+      <c r="BQ34" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR34" s="57">
         <v>7.0000000000000007E-2</v>
@@ -10983,8 +10985,8 @@
         <v>233</v>
       </c>
       <c r="BP35" s="28"/>
-      <c r="BQ35" s="17" t="s">
-        <v>253</v>
+      <c r="BQ35" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR35" s="57">
         <v>669.98</v>
@@ -11250,8 +11252,8 @@
         <v>189</v>
       </c>
       <c r="BP36" s="28"/>
-      <c r="BQ36" s="17" t="s">
-        <v>254</v>
+      <c r="BQ36" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR36" s="57">
         <v>476.73</v>
@@ -11517,7 +11519,7 @@
         <v>189</v>
       </c>
       <c r="BP37" s="27"/>
-      <c r="BQ37" s="17" t="s">
+      <c r="BQ37" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR37" s="58">
@@ -11784,8 +11786,8 @@
         <v>189</v>
       </c>
       <c r="BP38" s="28"/>
-      <c r="BQ38" s="17" t="s">
-        <v>253</v>
+      <c r="BQ38" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR38" s="57">
         <v>44.55</v>
@@ -12051,7 +12053,7 @@
         <v>189</v>
       </c>
       <c r="BP39" s="28"/>
-      <c r="BQ39" s="17" t="s">
+      <c r="BQ39" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR39" s="57">
@@ -12318,8 +12320,8 @@
         <v>232</v>
       </c>
       <c r="BP40" s="28"/>
-      <c r="BQ40" s="17" t="s">
-        <v>255</v>
+      <c r="BQ40" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR40" s="58">
         <v>389.56</v>
@@ -12585,7 +12587,7 @@
         <v>189</v>
       </c>
       <c r="BP41" s="27"/>
-      <c r="BQ41" s="17" t="s">
+      <c r="BQ41" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR41" s="57">
@@ -12852,8 +12854,8 @@
         <v>189</v>
       </c>
       <c r="BP42" s="28"/>
-      <c r="BQ42" s="17" t="s">
-        <v>254</v>
+      <c r="BQ42" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR42" s="57">
         <v>953.57</v>
@@ -13119,7 +13121,7 @@
         <v>189</v>
       </c>
       <c r="BP43" s="28"/>
-      <c r="BQ43" s="17" t="s">
+      <c r="BQ43" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR43" s="58">
@@ -13386,7 +13388,7 @@
         <v>189</v>
       </c>
       <c r="BP44" s="27"/>
-      <c r="BQ44" s="17" t="s">
+      <c r="BQ44" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR44" s="57">
@@ -13653,8 +13655,8 @@
         <v>189</v>
       </c>
       <c r="BP45" s="28"/>
-      <c r="BQ45" s="17" t="s">
-        <v>255</v>
+      <c r="BQ45" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR45" s="58">
         <v>666.28</v>
@@ -13920,8 +13922,8 @@
         <v>189</v>
       </c>
       <c r="BP46" s="28"/>
-      <c r="BQ46" s="17" t="s">
-        <v>253</v>
+      <c r="BQ46" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR46" s="57">
         <v>324.27</v>
@@ -14187,7 +14189,7 @@
         <v>189</v>
       </c>
       <c r="BP47" s="27"/>
-      <c r="BQ47" s="17" t="s">
+      <c r="BQ47" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR47" s="58">
@@ -14454,7 +14456,7 @@
         <v>189</v>
       </c>
       <c r="BP48" s="28"/>
-      <c r="BQ48" s="17" t="s">
+      <c r="BQ48" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR48" s="35">
@@ -14721,8 +14723,8 @@
         <v>189</v>
       </c>
       <c r="BP49" s="28"/>
-      <c r="BQ49" s="17" t="s">
-        <v>253</v>
+      <c r="BQ49" s="58" t="s">
+        <v>301</v>
       </c>
       <c r="BR49" s="35"/>
       <c r="BS49" s="35"/>
@@ -14982,8 +14984,8 @@
         <v>189</v>
       </c>
       <c r="BP50" s="28"/>
-      <c r="BQ50" s="17" t="s">
-        <v>254</v>
+      <c r="BQ50" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR50" s="35">
         <v>152.78</v>
@@ -15249,7 +15251,7 @@
         <v>232</v>
       </c>
       <c r="BP51" s="28"/>
-      <c r="BQ51" s="17" t="s">
+      <c r="BQ51" s="57" t="s">
         <v>254</v>
       </c>
       <c r="BR51" s="35">
@@ -15516,8 +15518,8 @@
         <v>189</v>
       </c>
       <c r="BP52" s="28"/>
-      <c r="BQ52" s="17" t="s">
-        <v>253</v>
+      <c r="BQ52" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR52" s="35">
         <v>33.03</v>
@@ -15783,8 +15785,8 @@
         <v>189</v>
       </c>
       <c r="BP53" s="28"/>
-      <c r="BQ53" s="17" t="s">
-        <v>255</v>
+      <c r="BQ53" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR53" s="35">
         <v>140.66</v>
@@ -16050,7 +16052,7 @@
         <v>189</v>
       </c>
       <c r="BP54" s="28"/>
-      <c r="BQ54" s="17" t="s">
+      <c r="BQ54" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR54" s="35">
@@ -16317,8 +16319,8 @@
         <v>189</v>
       </c>
       <c r="BP55" s="28"/>
-      <c r="BQ55" s="17" t="s">
-        <v>253</v>
+      <c r="BQ55" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR55" s="35">
         <v>711.93</v>
@@ -16584,8 +16586,8 @@
         <v>189</v>
       </c>
       <c r="BP56" s="28"/>
-      <c r="BQ56" s="17" t="s">
-        <v>254</v>
+      <c r="BQ56" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR56" s="35">
         <v>0.53</v>
@@ -16851,8 +16853,8 @@
         <v>232</v>
       </c>
       <c r="BP57" s="28"/>
-      <c r="BQ57" s="17" t="s">
-        <v>253</v>
+      <c r="BQ57" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR57" s="35">
         <v>2083.98</v>
@@ -17118,8 +17120,8 @@
         <v>189</v>
       </c>
       <c r="BP58" s="28"/>
-      <c r="BQ58" s="17" t="s">
-        <v>255</v>
+      <c r="BQ58" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR58" s="57">
         <v>37.85</v>
@@ -17385,7 +17387,7 @@
         <v>189</v>
       </c>
       <c r="BP59" s="28"/>
-      <c r="BQ59" s="17" t="s">
+      <c r="BQ59" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR59" s="57">
@@ -17652,7 +17654,7 @@
         <v>189</v>
       </c>
       <c r="BP60" s="28"/>
-      <c r="BQ60" s="17" t="s">
+      <c r="BQ60" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR60" s="57">
@@ -17919,7 +17921,7 @@
         <v>189</v>
       </c>
       <c r="BP61" s="28"/>
-      <c r="BQ61" s="17" t="s">
+      <c r="BQ61" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR61" s="57">
@@ -18186,7 +18188,7 @@
         <v>189</v>
       </c>
       <c r="BP62" s="27"/>
-      <c r="BQ62" s="17" t="s">
+      <c r="BQ62" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR62" s="57">
@@ -18453,7 +18455,7 @@
         <v>189</v>
       </c>
       <c r="BP63" s="28"/>
-      <c r="BQ63" s="17" t="s">
+      <c r="BQ63" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR63" s="58">
@@ -18720,7 +18722,7 @@
         <v>189</v>
       </c>
       <c r="BP64" s="28"/>
-      <c r="BQ64" s="17" t="s">
+      <c r="BQ64" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR64" s="58">
@@ -18987,7 +18989,7 @@
         <v>189</v>
       </c>
       <c r="BP65" s="28"/>
-      <c r="BQ65" s="17" t="s">
+      <c r="BQ65" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR65" s="35">
@@ -19254,7 +19256,7 @@
         <v>189</v>
       </c>
       <c r="BP66" s="27"/>
-      <c r="BQ66" s="17" t="s">
+      <c r="BQ66" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR66" s="35">
@@ -19521,7 +19523,7 @@
         <v>189</v>
       </c>
       <c r="BP67" s="27"/>
-      <c r="BQ67" s="17" t="s">
+      <c r="BQ67" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR67" s="35">
@@ -19788,7 +19790,7 @@
         <v>189</v>
       </c>
       <c r="BP68" s="27"/>
-      <c r="BQ68" s="17" t="s">
+      <c r="BQ68" s="58" t="s">
         <v>254</v>
       </c>
       <c r="CA68" s="55">
@@ -20022,7 +20024,7 @@
         <v>189</v>
       </c>
       <c r="BP69" s="28"/>
-      <c r="BQ69" s="17" t="s">
+      <c r="BQ69" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR69" s="35">
@@ -20289,7 +20291,7 @@
         <v>189</v>
       </c>
       <c r="BP70" s="27"/>
-      <c r="BQ70" s="17" t="s">
+      <c r="BQ70" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR70" s="35">
@@ -20556,7 +20558,7 @@
         <v>189</v>
       </c>
       <c r="BP71" s="27"/>
-      <c r="BQ71" s="17" t="s">
+      <c r="BQ71" s="58" t="s">
         <v>254</v>
       </c>
       <c r="BR71" s="35">
@@ -20823,7 +20825,7 @@
         <v>189</v>
       </c>
       <c r="BP72" s="27"/>
-      <c r="BQ72" s="17" t="s">
+      <c r="BQ72" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR72" s="35">
@@ -21090,7 +21092,7 @@
         <v>232</v>
       </c>
       <c r="BP73" s="28"/>
-      <c r="BQ73" s="17" t="s">
+      <c r="BQ73" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR73" s="35">
@@ -21357,7 +21359,7 @@
         <v>232</v>
       </c>
       <c r="BP74" s="28"/>
-      <c r="BQ74" s="17" t="s">
+      <c r="BQ74" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR74" s="35">
@@ -21624,7 +21626,7 @@
         <v>189</v>
       </c>
       <c r="BP75" s="28"/>
-      <c r="BQ75" s="17" t="s">
+      <c r="BQ75" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR75" s="35">
@@ -21891,7 +21893,7 @@
         <v>189</v>
       </c>
       <c r="BP76" s="28"/>
-      <c r="BQ76" s="17" t="s">
+      <c r="BQ76" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR76" s="35">
@@ -22158,7 +22160,7 @@
         <v>232</v>
       </c>
       <c r="BP77" s="27"/>
-      <c r="BQ77" s="17" t="s">
+      <c r="BQ77" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR77" s="35">
@@ -22425,7 +22427,7 @@
         <v>189</v>
       </c>
       <c r="BP78" s="28"/>
-      <c r="BQ78" s="17" t="s">
+      <c r="BQ78" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR78" s="35">
@@ -22692,7 +22694,7 @@
         <v>232</v>
       </c>
       <c r="BP79" s="28"/>
-      <c r="BQ79" s="17" t="s">
+      <c r="BQ79" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR79" s="35">
@@ -22959,7 +22961,7 @@
         <v>189</v>
       </c>
       <c r="BP80" s="28"/>
-      <c r="BQ80" s="17" t="s">
+      <c r="BQ80" s="57" t="s">
         <v>254</v>
       </c>
       <c r="BR80" s="35">
@@ -23226,7 +23228,7 @@
         <v>189</v>
       </c>
       <c r="BP81" s="28"/>
-      <c r="BQ81" s="17" t="s">
+      <c r="BQ81" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR81" s="35">
@@ -23493,7 +23495,7 @@
         <v>189</v>
       </c>
       <c r="BP82" s="28"/>
-      <c r="BQ82" s="17" t="s">
+      <c r="BQ82" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR82" s="35">
@@ -23760,8 +23762,8 @@
         <v>189</v>
       </c>
       <c r="BP83" s="28"/>
-      <c r="BQ83" s="17" t="s">
-        <v>254</v>
+      <c r="BQ83" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR83" s="35"/>
       <c r="BS83" s="35"/>
@@ -24003,7 +24005,7 @@
         <v>189</v>
       </c>
       <c r="BP84" s="28"/>
-      <c r="BQ84" s="48" t="s">
+      <c r="BQ84" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR84" s="35">
@@ -24270,7 +24272,7 @@
         <v>232</v>
       </c>
       <c r="BP85" s="28"/>
-      <c r="BQ85" s="50" t="s">
+      <c r="BQ85" s="57" t="s">
         <v>254</v>
       </c>
       <c r="BR85" s="35"/>
@@ -24513,7 +24515,7 @@
         <v>189</v>
       </c>
       <c r="BP86" s="28"/>
-      <c r="BQ86" s="50" t="s">
+      <c r="BQ86" s="57" t="s">
         <v>254</v>
       </c>
       <c r="BR86" s="35">
@@ -24780,7 +24782,7 @@
         <v>189</v>
       </c>
       <c r="BP87" s="28"/>
-      <c r="BQ87" s="48" t="s">
+      <c r="BQ87" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR87" s="35">
@@ -25281,7 +25283,7 @@
         <v>189</v>
       </c>
       <c r="BP89" s="28"/>
-      <c r="BQ89" s="17" t="s">
+      <c r="BQ89" s="58" t="s">
         <v>254</v>
       </c>
       <c r="BR89" s="35">
@@ -25548,7 +25550,7 @@
         <v>189</v>
       </c>
       <c r="BP90" s="28"/>
-      <c r="BQ90" s="17" t="s">
+      <c r="BQ90" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR90" s="35">
@@ -25815,7 +25817,7 @@
         <v>189</v>
       </c>
       <c r="BP91" s="27"/>
-      <c r="BQ91" s="17" t="s">
+      <c r="BQ91" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR91" s="35">
@@ -26082,7 +26084,7 @@
         <v>189</v>
       </c>
       <c r="BP92" s="28"/>
-      <c r="BQ92" s="17" t="s">
+      <c r="BQ92" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR92" s="35">
@@ -26349,7 +26351,7 @@
         <v>189</v>
       </c>
       <c r="BP93" s="28"/>
-      <c r="BQ93" s="17" t="s">
+      <c r="BQ93" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR93" s="35">
@@ -26616,7 +26618,7 @@
         <v>232</v>
       </c>
       <c r="BP94" s="28"/>
-      <c r="BQ94" s="17" t="s">
+      <c r="BQ94" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR94" s="35">
@@ -26883,7 +26885,7 @@
         <v>232</v>
       </c>
       <c r="BP95" s="28"/>
-      <c r="BQ95" s="17" t="s">
+      <c r="BQ95" s="58" t="s">
         <v>254</v>
       </c>
       <c r="BR95" s="35">
@@ -27150,7 +27152,7 @@
         <v>189</v>
       </c>
       <c r="BP96" s="28"/>
-      <c r="BQ96" s="17" t="s">
+      <c r="BQ96" s="57" t="s">
         <v>254</v>
       </c>
       <c r="BR96" s="35">
@@ -27417,7 +27419,7 @@
         <v>233</v>
       </c>
       <c r="BP97" s="28"/>
-      <c r="BQ97" s="17" t="s">
+      <c r="BQ97" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR97" s="35">
@@ -27684,7 +27686,7 @@
         <v>189</v>
       </c>
       <c r="BP98" s="27"/>
-      <c r="BQ98" s="17" t="s">
+      <c r="BQ98" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR98" s="35">
@@ -27951,7 +27953,7 @@
         <v>189</v>
       </c>
       <c r="BP99" s="28"/>
-      <c r="BQ99" s="17" t="s">
+      <c r="BQ99" s="58" t="s">
         <v>254</v>
       </c>
       <c r="BR99" s="35">
@@ -28218,7 +28220,7 @@
         <v>232</v>
       </c>
       <c r="BP100" s="28"/>
-      <c r="BQ100" s="17" t="s">
+      <c r="BQ100" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR100" s="35">
@@ -28485,7 +28487,7 @@
         <v>189</v>
       </c>
       <c r="BP101" s="28"/>
-      <c r="BQ101" s="17" t="s">
+      <c r="BQ101" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR101" s="35">
@@ -28752,7 +28754,7 @@
         <v>232</v>
       </c>
       <c r="BP102" s="28"/>
-      <c r="BQ102" s="17" t="s">
+      <c r="BQ102" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR102" s="35">
@@ -29019,7 +29021,7 @@
         <v>189</v>
       </c>
       <c r="BP103" s="27"/>
-      <c r="BQ103" s="17" t="s">
+      <c r="BQ103" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR103" s="35">
@@ -29286,7 +29288,7 @@
         <v>189</v>
       </c>
       <c r="BP104" s="28"/>
-      <c r="BQ104" s="17" t="s">
+      <c r="BQ104" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR104" s="35">
@@ -29553,7 +29555,7 @@
         <v>189</v>
       </c>
       <c r="BP105" s="28"/>
-      <c r="BQ105" s="17" t="s">
+      <c r="BQ105" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR105" s="35">
@@ -29820,7 +29822,7 @@
         <v>189</v>
       </c>
       <c r="BP106" s="28"/>
-      <c r="BQ106" s="17" t="s">
+      <c r="BQ106" s="58" t="s">
         <v>254</v>
       </c>
       <c r="BR106" s="35">
@@ -30087,7 +30089,7 @@
         <v>189</v>
       </c>
       <c r="BP107" s="28"/>
-      <c r="BQ107" s="17" t="s">
+      <c r="BQ107" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR107" s="35">
@@ -30354,7 +30356,7 @@
         <v>189</v>
       </c>
       <c r="BP108" s="28"/>
-      <c r="BQ108" s="17" t="s">
+      <c r="BQ108" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR108" s="35">
@@ -30621,7 +30623,7 @@
         <v>189</v>
       </c>
       <c r="BP109" s="28"/>
-      <c r="BQ109" s="17" t="s">
+      <c r="BQ109" s="58" t="s">
         <v>254</v>
       </c>
       <c r="BR109" s="35">
@@ -30888,7 +30890,7 @@
         <v>189</v>
       </c>
       <c r="BP110" s="28"/>
-      <c r="BQ110" s="17" t="s">
+      <c r="BQ110" s="58" t="s">
         <v>254</v>
       </c>
       <c r="BR110" s="35">
@@ -31155,7 +31157,7 @@
         <v>232</v>
       </c>
       <c r="BP111" s="28"/>
-      <c r="BQ111" s="17" t="s">
+      <c r="BQ111" s="57" t="s">
         <v>254</v>
       </c>
       <c r="BR111" s="35">
@@ -31422,7 +31424,7 @@
         <v>233</v>
       </c>
       <c r="BP112" s="27"/>
-      <c r="BQ112" s="17" t="s">
+      <c r="BQ112" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR112" s="35">
@@ -31689,7 +31691,7 @@
         <v>189</v>
       </c>
       <c r="BP113" s="27"/>
-      <c r="BQ113" s="17" t="s">
+      <c r="BQ113" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR113" s="35">
@@ -31956,7 +31958,7 @@
         <v>189</v>
       </c>
       <c r="BP114" s="28"/>
-      <c r="BQ114" s="17" t="s">
+      <c r="BQ114" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR114" s="35">
@@ -32223,7 +32225,7 @@
         <v>189</v>
       </c>
       <c r="BP115" s="28"/>
-      <c r="BQ115" s="17" t="s">
+      <c r="BQ115" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR115" s="35">
@@ -32490,7 +32492,7 @@
         <v>189</v>
       </c>
       <c r="BP116" s="28"/>
-      <c r="BQ116" s="17" t="s">
+      <c r="BQ116" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR116" s="35">
@@ -32757,7 +32759,7 @@
         <v>189</v>
       </c>
       <c r="BP117" s="28"/>
-      <c r="BQ117" s="17" t="s">
+      <c r="BQ117" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR117" s="35">
@@ -33024,7 +33026,7 @@
         <v>232</v>
       </c>
       <c r="BP118" s="28"/>
-      <c r="BQ118" s="17" t="s">
+      <c r="BQ118" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR118" s="35">
@@ -33291,7 +33293,7 @@
         <v>189</v>
       </c>
       <c r="BP119" s="28"/>
-      <c r="BQ119" s="17" t="s">
+      <c r="BQ119" s="58" t="s">
         <v>254</v>
       </c>
       <c r="BR119" s="35">
@@ -33558,7 +33560,7 @@
         <v>189</v>
       </c>
       <c r="BP120" s="28"/>
-      <c r="BQ120" s="17" t="s">
+      <c r="BQ120" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR120" s="35">
@@ -33825,7 +33827,7 @@
         <v>189</v>
       </c>
       <c r="BP121" s="28"/>
-      <c r="BQ121" s="17" t="s">
+      <c r="BQ121" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR121" s="35">
@@ -34092,7 +34094,7 @@
         <v>189</v>
       </c>
       <c r="BP122" s="27"/>
-      <c r="BQ122" s="17" t="s">
+      <c r="BQ122" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR122" s="35">
@@ -34359,7 +34361,7 @@
         <v>189</v>
       </c>
       <c r="BP123" s="27"/>
-      <c r="BQ123" s="17" t="s">
+      <c r="BQ123" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR123" s="35">
@@ -34626,7 +34628,7 @@
         <v>189</v>
       </c>
       <c r="BP124" s="28"/>
-      <c r="BQ124" s="17" t="s">
+      <c r="BQ124" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR124" s="35">
@@ -34893,8 +34895,8 @@
         <v>232</v>
       </c>
       <c r="BP125" s="28"/>
-      <c r="BQ125" s="17" t="s">
-        <v>255</v>
+      <c r="BQ125" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR125" s="35">
         <v>1846.56</v>
@@ -35142,8 +35144,8 @@
         <v>189</v>
       </c>
       <c r="BP126" s="28"/>
-      <c r="BQ126" s="17" t="s">
-        <v>254</v>
+      <c r="BQ126" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR126" s="35">
         <v>118.21</v>
@@ -35409,8 +35411,8 @@
         <v>189</v>
       </c>
       <c r="BP127" s="28"/>
-      <c r="BQ127" s="17" t="s">
-        <v>253</v>
+      <c r="BQ127" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR127" s="35">
         <v>122.88</v>
@@ -35676,7 +35678,7 @@
         <v>189</v>
       </c>
       <c r="BP128" s="28"/>
-      <c r="BQ128" s="17" t="s">
+      <c r="BQ128" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR128" s="35">
@@ -35943,7 +35945,7 @@
         <v>189</v>
       </c>
       <c r="BP129" s="27"/>
-      <c r="BQ129" s="17" t="s">
+      <c r="BQ129" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR129" s="35">
@@ -36210,7 +36212,7 @@
         <v>189</v>
       </c>
       <c r="BP130" s="28"/>
-      <c r="BQ130" s="17" t="s">
+      <c r="BQ130" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR130" s="35">
@@ -36477,8 +36479,8 @@
         <v>189</v>
       </c>
       <c r="BP131" s="27"/>
-      <c r="BQ131" s="17" t="s">
-        <v>255</v>
+      <c r="BQ131" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR131" s="35">
         <v>91.9</v>
@@ -36744,8 +36746,8 @@
         <v>233</v>
       </c>
       <c r="BP132" s="27"/>
-      <c r="BQ132" s="17" t="s">
-        <v>254</v>
+      <c r="BQ132" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR132" s="35">
         <v>1167.83</v>
@@ -37011,7 +37013,7 @@
         <v>189</v>
       </c>
       <c r="BP133" s="28"/>
-      <c r="BQ133" s="17" t="s">
+      <c r="BQ133" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR133" s="35">
@@ -37278,8 +37280,8 @@
         <v>189</v>
       </c>
       <c r="BP134" s="28"/>
-      <c r="BQ134" s="17" t="s">
-        <v>255</v>
+      <c r="BQ134" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR134" s="35">
         <v>0.1</v>
@@ -37545,8 +37547,8 @@
         <v>189</v>
       </c>
       <c r="BP135" s="28"/>
-      <c r="BQ135" s="17" t="s">
-        <v>253</v>
+      <c r="BQ135" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR135" s="35">
         <v>967.3</v>
@@ -37812,8 +37814,8 @@
         <v>189</v>
       </c>
       <c r="BP136" s="27"/>
-      <c r="BQ136" s="17" t="s">
-        <v>255</v>
+      <c r="BQ136" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR136" s="35">
         <v>418.86</v>
@@ -38079,7 +38081,7 @@
         <v>189</v>
       </c>
       <c r="BP137" s="28"/>
-      <c r="BQ137" s="17" t="s">
+      <c r="BQ137" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR137" s="35">
@@ -38346,8 +38348,8 @@
         <v>189</v>
       </c>
       <c r="BP138" s="28"/>
-      <c r="BQ138" s="17" t="s">
-        <v>253</v>
+      <c r="BQ138" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR138" s="35">
         <v>629.29999999999995</v>
@@ -38613,8 +38615,8 @@
         <v>232</v>
       </c>
       <c r="BP139" s="28"/>
-      <c r="BQ139" s="17" t="s">
-        <v>254</v>
+      <c r="BQ139" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR139" s="35">
         <v>371</v>
@@ -38880,8 +38882,8 @@
         <v>189</v>
       </c>
       <c r="BP140" s="28"/>
-      <c r="BQ140" s="17" t="s">
-        <v>253</v>
+      <c r="BQ140" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR140" s="35">
         <v>1.99</v>
@@ -39147,8 +39149,8 @@
         <v>189</v>
       </c>
       <c r="BP141" s="28"/>
-      <c r="BQ141" s="17" t="s">
-        <v>254</v>
+      <c r="BQ141" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR141" s="35">
         <v>270.64999999999998</v>
@@ -39414,7 +39416,7 @@
         <v>189</v>
       </c>
       <c r="BP142" s="28"/>
-      <c r="BQ142" s="17" t="s">
+      <c r="BQ142" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR142" s="35">
@@ -39681,8 +39683,8 @@
         <v>232</v>
       </c>
       <c r="BP143" s="28"/>
-      <c r="BQ143" s="17" t="s">
-        <v>253</v>
+      <c r="BQ143" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR143" s="35">
         <v>262.52</v>
@@ -39948,8 +39950,8 @@
         <v>189</v>
       </c>
       <c r="BP144" s="28"/>
-      <c r="BQ144" s="17" t="s">
-        <v>254</v>
+      <c r="BQ144" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR144" s="35">
         <v>791.75</v>
@@ -40215,8 +40217,8 @@
         <v>189</v>
       </c>
       <c r="BP145" s="28"/>
-      <c r="BQ145" s="17" t="s">
-        <v>253</v>
+      <c r="BQ145" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR145" s="35">
         <v>1027.77</v>
@@ -40482,8 +40484,8 @@
         <v>189</v>
       </c>
       <c r="BP146" s="28"/>
-      <c r="BQ146" s="17" t="s">
-        <v>254</v>
+      <c r="BQ146" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR146" s="35">
         <v>472.77</v>
@@ -40749,8 +40751,8 @@
         <v>189</v>
       </c>
       <c r="BP147" s="27"/>
-      <c r="BQ147" s="17" t="s">
-        <v>255</v>
+      <c r="BQ147" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR147" s="35">
         <v>1.23</v>
@@ -41016,8 +41018,8 @@
         <v>189</v>
       </c>
       <c r="BP148" s="28"/>
-      <c r="BQ148" s="17" t="s">
-        <v>253</v>
+      <c r="BQ148" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR148" s="35">
         <v>469.11</v>
@@ -41283,8 +41285,8 @@
         <v>232</v>
       </c>
       <c r="BP149" s="28"/>
-      <c r="BQ149" s="17" t="s">
-        <v>255</v>
+      <c r="BQ149" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR149" s="35">
         <v>594.35</v>
@@ -41550,8 +41552,8 @@
         <v>232</v>
       </c>
       <c r="BP150" s="28"/>
-      <c r="BQ150" s="17" t="s">
-        <v>254</v>
+      <c r="BQ150" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR150" s="35">
         <v>158.66999999999999</v>
@@ -41817,8 +41819,8 @@
         <v>232</v>
       </c>
       <c r="BP151" s="27"/>
-      <c r="BQ151" s="17" t="s">
-        <v>253</v>
+      <c r="BQ151" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR151" s="35">
         <v>1158.8599999999999</v>
@@ -42084,8 +42086,8 @@
         <v>232</v>
       </c>
       <c r="BP152" s="28"/>
-      <c r="BQ152" s="17" t="s">
-        <v>254</v>
+      <c r="BQ152" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR152" s="35">
         <v>68.72</v>
@@ -42351,7 +42353,7 @@
         <v>189</v>
       </c>
       <c r="BP153" s="28"/>
-      <c r="BQ153" s="17" t="s">
+      <c r="BQ153" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR153" s="35">
@@ -42618,7 +42620,7 @@
         <v>189</v>
       </c>
       <c r="BP154" s="28"/>
-      <c r="BQ154" s="17" t="s">
+      <c r="BQ154" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR154" s="35">
@@ -42885,8 +42887,8 @@
         <v>189</v>
       </c>
       <c r="BP155" s="28"/>
-      <c r="BQ155" s="17" t="s">
-        <v>253</v>
+      <c r="BQ155" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR155" s="35">
         <v>293.89999999999998</v>
@@ -43152,7 +43154,7 @@
         <v>189</v>
       </c>
       <c r="BP156" s="28"/>
-      <c r="BQ156" s="17" t="s">
+      <c r="BQ156" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR156" s="35">
@@ -43419,8 +43421,8 @@
         <v>189</v>
       </c>
       <c r="BP157" s="27"/>
-      <c r="BQ157" s="17" t="s">
-        <v>255</v>
+      <c r="BQ157" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR157" s="35">
         <v>128.01</v>
@@ -43686,7 +43688,7 @@
         <v>189</v>
       </c>
       <c r="BP158" s="28"/>
-      <c r="BQ158" s="17" t="s">
+      <c r="BQ158" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR158" s="35">
@@ -43953,8 +43955,8 @@
         <v>189</v>
       </c>
       <c r="BP159" s="28"/>
-      <c r="BQ159" s="17" t="s">
-        <v>253</v>
+      <c r="BQ159" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR159" s="35">
         <v>38.840000000000003</v>
@@ -44220,7 +44222,7 @@
         <v>233</v>
       </c>
       <c r="BP160" s="28"/>
-      <c r="BQ160" s="17" t="s">
+      <c r="BQ160" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR160" s="35">
@@ -44487,8 +44489,8 @@
         <v>189</v>
       </c>
       <c r="BP161" s="28"/>
-      <c r="BQ161" s="17" t="s">
-        <v>255</v>
+      <c r="BQ161" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR161" s="35">
         <v>7.2</v>
@@ -44754,8 +44756,8 @@
         <v>189</v>
       </c>
       <c r="BP162" s="28"/>
-      <c r="BQ162" s="17" t="s">
-        <v>254</v>
+      <c r="BQ162" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR162" s="35">
         <v>151.38999999999999</v>
@@ -45021,8 +45023,8 @@
         <v>189</v>
       </c>
       <c r="BP163" s="28"/>
-      <c r="BQ163" s="17" t="s">
-        <v>255</v>
+      <c r="BQ163" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR163" s="35">
         <v>48.28</v>
@@ -45288,8 +45290,8 @@
         <v>189</v>
       </c>
       <c r="BP164" s="27"/>
-      <c r="BQ164" s="17" t="s">
-        <v>253</v>
+      <c r="BQ164" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR164" s="35">
         <v>284.41000000000003</v>
@@ -45555,8 +45557,8 @@
         <v>189</v>
       </c>
       <c r="BP165" s="28"/>
-      <c r="BQ165" s="17" t="s">
-        <v>255</v>
+      <c r="BQ165" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR165" s="35">
         <v>713.65</v>
@@ -45822,7 +45824,7 @@
         <v>189</v>
       </c>
       <c r="BP166" s="28"/>
-      <c r="BQ166" s="17" t="s">
+      <c r="BQ166" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR166" s="35">
@@ -46089,8 +46091,8 @@
         <v>189</v>
       </c>
       <c r="BP167" s="27"/>
-      <c r="BQ167" s="17" t="s">
-        <v>253</v>
+      <c r="BQ167" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR167" s="35">
         <v>100.7</v>
@@ -46356,8 +46358,8 @@
         <v>189</v>
       </c>
       <c r="BP168" s="27"/>
-      <c r="BQ168" s="17" t="s">
-        <v>255</v>
+      <c r="BQ168" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR168" s="35">
         <v>176.25</v>
@@ -46623,8 +46625,8 @@
         <v>189</v>
       </c>
       <c r="BP169" s="28"/>
-      <c r="BQ169" s="17" t="s">
-        <v>253</v>
+      <c r="BQ169" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR169" s="35">
         <v>473.88</v>
@@ -46890,8 +46892,8 @@
         <v>232</v>
       </c>
       <c r="BP170" s="28"/>
-      <c r="BQ170" s="17" t="s">
-        <v>255</v>
+      <c r="BQ170" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR170" s="35">
         <v>191.33</v>
@@ -47157,7 +47159,7 @@
         <v>232</v>
       </c>
       <c r="BP171" s="28"/>
-      <c r="BQ171" s="17" t="s">
+      <c r="BQ171" s="58" t="s">
         <v>254</v>
       </c>
       <c r="BR171" s="35">
@@ -47424,8 +47426,8 @@
         <v>232</v>
       </c>
       <c r="BP172" s="28"/>
-      <c r="BQ172" s="17" t="s">
-        <v>254</v>
+      <c r="BQ172" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR172" s="35">
         <v>503.84</v>
@@ -47691,8 +47693,8 @@
         <v>189</v>
       </c>
       <c r="BP173" s="28"/>
-      <c r="BQ173" s="17" t="s">
-        <v>253</v>
+      <c r="BQ173" s="57" t="s">
+        <v>255</v>
       </c>
       <c r="BR173" s="35">
         <v>388.95</v>
@@ -47958,8 +47960,8 @@
         <v>189</v>
       </c>
       <c r="BP174" s="27"/>
-      <c r="BQ174" s="17" t="s">
-        <v>255</v>
+      <c r="BQ174" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR174" s="35">
         <v>34.29</v>
@@ -48225,8 +48227,8 @@
         <v>189</v>
       </c>
       <c r="BP175" s="28"/>
-      <c r="BQ175" s="17" t="s">
-        <v>254</v>
+      <c r="BQ175" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR175" s="35">
         <v>235</v>
@@ -48492,7 +48494,7 @@
         <v>189</v>
       </c>
       <c r="BP176" s="28"/>
-      <c r="BQ176" s="17" t="s">
+      <c r="BQ176" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR176" s="35">
@@ -48759,8 +48761,8 @@
         <v>189</v>
       </c>
       <c r="BP177" s="27"/>
-      <c r="BQ177" s="17" t="s">
-        <v>255</v>
+      <c r="BQ177" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR177" s="35">
         <v>498.88</v>
@@ -49026,7 +49028,7 @@
         <v>189</v>
       </c>
       <c r="BP178" s="28"/>
-      <c r="BQ178" s="17" t="s">
+      <c r="BQ178" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR178" s="35">
@@ -49293,17 +49295,8 @@
         <v>189</v>
       </c>
       <c r="BP179" s="28"/>
-      <c r="BQ179" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="BR179">
-        <v>365.88</v>
-      </c>
-      <c r="BS179">
-        <v>448.88</v>
-      </c>
-      <c r="BT179">
-        <v>83</v>
+      <c r="BQ179" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="CA179" s="55">
         <v>7</v>
@@ -49536,8 +49529,8 @@
         <v>189</v>
       </c>
       <c r="BP180" s="27"/>
-      <c r="BQ180" s="17" t="s">
-        <v>254</v>
+      <c r="BQ180" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR180" s="35">
         <v>144.16</v>
@@ -49803,8 +49796,8 @@
         <v>189</v>
       </c>
       <c r="BP181" s="28"/>
-      <c r="BQ181" s="17" t="s">
-        <v>255</v>
+      <c r="BQ181" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR181" s="35">
         <v>311.06</v>
@@ -50070,8 +50063,8 @@
         <v>189</v>
       </c>
       <c r="BP182" s="28"/>
-      <c r="BQ182" s="17" t="s">
-        <v>253</v>
+      <c r="BQ182" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR182" s="35">
         <v>988.45</v>
@@ -50337,7 +50330,7 @@
         <v>233</v>
       </c>
       <c r="BP183" s="27"/>
-      <c r="BQ183" s="17" t="s">
+      <c r="BQ183" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR183" s="35">
@@ -50604,7 +50597,7 @@
         <v>189</v>
       </c>
       <c r="BP184" s="28"/>
-      <c r="BQ184" s="17" t="s">
+      <c r="BQ184" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR184" s="35">
@@ -50871,8 +50864,8 @@
         <v>189</v>
       </c>
       <c r="BP185" s="28"/>
-      <c r="BQ185" s="17" t="s">
-        <v>255</v>
+      <c r="BQ185" s="57" t="s">
+        <v>254</v>
       </c>
       <c r="BR185" s="57">
         <v>699.43</v>
@@ -51138,8 +51131,8 @@
         <v>189</v>
       </c>
       <c r="BP186" s="28"/>
-      <c r="BQ186" s="17" t="s">
-        <v>254</v>
+      <c r="BQ186" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR186" s="57">
         <v>9.65</v>
@@ -51405,8 +51398,8 @@
         <v>232</v>
       </c>
       <c r="BP187" s="28"/>
-      <c r="BQ187" s="17" t="s">
-        <v>253</v>
+      <c r="BQ187" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR187" s="58">
         <v>875.69</v>
@@ -51672,7 +51665,7 @@
         <v>189</v>
       </c>
       <c r="BP188" s="28"/>
-      <c r="BQ188" s="17" t="s">
+      <c r="BQ188" s="58" t="s">
         <v>254</v>
       </c>
       <c r="BR188" s="58">
@@ -51939,8 +51932,8 @@
         <v>189</v>
       </c>
       <c r="BP189" s="28"/>
-      <c r="BQ189" s="17" t="s">
-        <v>254</v>
+      <c r="BQ189" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR189" s="58">
         <v>219.06</v>
@@ -52206,8 +52199,8 @@
         <v>232</v>
       </c>
       <c r="BP190" s="28"/>
-      <c r="BQ190" s="17" t="s">
-        <v>253</v>
+      <c r="BQ190" s="58" t="s">
+        <v>254</v>
       </c>
       <c r="BR190" s="58">
         <v>1715.7</v>
@@ -52473,8 +52466,8 @@
         <v>189</v>
       </c>
       <c r="BP191" s="28"/>
-      <c r="BQ191" s="17" t="s">
-        <v>254</v>
+      <c r="BQ191" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR191" s="58">
         <v>86.56</v>
@@ -52740,7 +52733,7 @@
         <v>189</v>
       </c>
       <c r="BP192" s="28"/>
-      <c r="BQ192" s="17" t="s">
+      <c r="BQ192" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR192" s="57">
@@ -53007,7 +53000,7 @@
         <v>189</v>
       </c>
       <c r="BP193" s="27"/>
-      <c r="BQ193" s="17" t="s">
+      <c r="BQ193" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR193" s="57">
@@ -53274,8 +53267,8 @@
         <v>189</v>
       </c>
       <c r="BP194" s="28"/>
-      <c r="BQ194" s="17" t="s">
-        <v>255</v>
+      <c r="BQ194" s="57" t="s">
+        <v>253</v>
       </c>
       <c r="BR194" s="57">
         <v>8.82</v>
@@ -53541,7 +53534,7 @@
         <v>189</v>
       </c>
       <c r="BP195" s="28"/>
-      <c r="BQ195" s="17" t="s">
+      <c r="BQ195" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR195" s="58">
@@ -53808,8 +53801,8 @@
         <v>189</v>
       </c>
       <c r="BP196" s="28"/>
-      <c r="BQ196" s="17" t="s">
-        <v>253</v>
+      <c r="BQ196" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR196" s="58">
         <v>0.87</v>
@@ -54075,7 +54068,7 @@
         <v>189</v>
       </c>
       <c r="BP197" s="28"/>
-      <c r="BQ197" s="17" t="s">
+      <c r="BQ197" s="57" t="s">
         <v>255</v>
       </c>
       <c r="BR197" s="57">
@@ -54342,8 +54335,8 @@
         <v>189</v>
       </c>
       <c r="BP198" s="28"/>
-      <c r="BQ198" s="17" t="s">
-        <v>255</v>
+      <c r="BQ198" s="58" t="s">
+        <v>253</v>
       </c>
       <c r="BR198" s="58"/>
       <c r="BS198" s="58"/>
@@ -54579,7 +54572,7 @@
         <v>233</v>
       </c>
       <c r="BP199" s="28"/>
-      <c r="BQ199" s="17" t="s">
+      <c r="BQ199" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR199" s="58">
@@ -54846,7 +54839,7 @@
         <v>189</v>
       </c>
       <c r="BP200" s="28"/>
-      <c r="BQ200" s="17" t="s">
+      <c r="BQ200" s="58" t="s">
         <v>253</v>
       </c>
       <c r="BR200" s="58">
@@ -55113,7 +55106,7 @@
         <v>189</v>
       </c>
       <c r="BP201" s="28"/>
-      <c r="BQ201" s="17" t="s">
+      <c r="BQ201" s="57" t="s">
         <v>253</v>
       </c>
       <c r="BR201" s="57">
@@ -55126,27 +55119,27 @@
         <v>168.1</v>
       </c>
       <c r="BU201" s="35">
-        <f t="shared" ref="BU201:BU202" si="114">BV201-BW201</f>
+        <f t="shared" ref="BU201" si="114">BV201-BW201</f>
         <v>11.251509433962262</v>
       </c>
       <c r="BV201" s="35">
-        <f t="shared" ref="BV201:BV202" si="115">BS201/$D201</f>
+        <f t="shared" ref="BV201" si="115">BS201/$D201</f>
         <v>14.42320754716981</v>
       </c>
       <c r="BW201" s="35">
-        <f t="shared" ref="BW201:BW202" si="116">BT201/$D201</f>
+        <f t="shared" ref="BW201" si="116">BT201/$D201</f>
         <v>3.171698113207547</v>
       </c>
       <c r="BX201" s="36">
-        <f t="shared" ref="BX201:BX202" si="117">BY201-BZ201</f>
+        <f t="shared" ref="BX201" si="117">BY201-BZ201</f>
         <v>25.284290862836546</v>
       </c>
       <c r="BY201" s="36">
-        <f t="shared" ref="BY201:BY202" si="118">BS201*2400/$G201</f>
+        <f t="shared" ref="BY201" si="118">BS201*2400/$G201</f>
         <v>32.411702353190584</v>
       </c>
       <c r="BZ201" s="36">
-        <f t="shared" ref="BZ201:BZ202" si="119">BT201*2400/$G201</f>
+        <f t="shared" ref="BZ201" si="119">BT201*2400/$G201</f>
         <v>7.1274114903540386</v>
       </c>
       <c r="CA201" s="48">
@@ -55380,8 +55373,8 @@
         <v>189</v>
       </c>
       <c r="BP202" s="28"/>
-      <c r="BQ202" s="17" t="s">
-        <v>253</v>
+      <c r="BQ202" s="58" t="s">
+        <v>255</v>
       </c>
       <c r="BR202" s="58"/>
       <c r="BS202" s="58"/>
@@ -55623,7 +55616,7 @@
         <v>189</v>
       </c>
       <c r="BP203" s="28"/>
-      <c r="BQ203" s="48" t="s">
+      <c r="BQ203" s="58" t="s">
         <v>255</v>
       </c>
       <c r="BR203" s="58">
